--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -566,7 +566,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,7 +633,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -694,7 +702,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -757,7 +769,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -820,7 +836,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -883,7 +903,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -948,7 +972,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1013,7 +1041,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1076,7 +1108,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1139,7 +1175,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1202,7 +1242,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1265,7 +1309,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1328,7 +1376,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1391,7 +1443,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1454,7 +1510,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1519,7 +1579,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1584,7 +1648,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1647,7 +1715,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1710,7 +1782,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1773,7 +1849,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1836,7 +1916,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1899,7 +1983,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1962,7 +2050,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2025,7 +2117,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2088,7 +2184,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2153,7 +2253,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2218,7 +2322,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2283,7 +2391,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2346,7 +2458,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2409,7 +2525,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2472,7 +2592,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2535,7 +2659,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2600,7 +2728,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2663,7 +2795,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2726,7 +2862,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2791,7 +2931,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2854,7 +2998,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2917,7 +3065,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2980,7 +3132,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3043,7 +3199,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3106,7 +3266,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3169,7 +3333,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3232,7 +3400,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3295,7 +3467,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3358,7 +3534,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3421,7 +3601,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3484,7 +3668,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3549,7 +3737,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3612,7 +3804,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3675,7 +3871,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3738,7 +3938,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3801,7 +4005,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3864,7 +4072,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3927,7 +4139,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3990,7 +4206,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4053,7 +4273,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4116,7 +4340,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4179,7 +4407,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4242,7 +4474,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4305,7 +4541,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4368,7 +4608,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4431,7 +4675,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4494,7 +4742,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4557,7 +4809,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4620,7 +4876,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4683,7 +4943,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4746,7 +5010,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4809,7 +5077,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4874,7 +5146,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4937,7 +5213,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4998,7 +5278,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5059,7 +5343,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5122,7 +5410,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5180,8 +5472,16 @@
           <t>LP-056480</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5239,8 +5539,16 @@
           <t>LP-056492</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5298,8 +5606,16 @@
           <t>LP-056483</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5359,8 +5675,16 @@
           <t>LP-056402</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5420,8 +5744,16 @@
           <t>LP-056401</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5481,8 +5813,16 @@
           <t>LP-056403</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5542,8 +5882,16 @@
           <t>LP-056404</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5603,8 +5951,16 @@
           <t>LP-056405</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5664,8 +6020,16 @@
           <t>LP-056407</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5725,8 +6089,16 @@
           <t>LP-056406</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5784,8 +6156,16 @@
           <t>LP-056408</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5843,8 +6223,16 @@
           <t>LP-056409</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5902,8 +6290,16 @@
           <t>LP-056324</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5961,8 +6357,16 @@
           <t>LP-056323</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6020,8 +6424,16 @@
           <t>LP-056410</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6079,8 +6491,16 @@
           <t>LP-056322</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6140,8 +6560,16 @@
           <t>LP-056321</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6199,8 +6627,16 @@
           <t>LP-056481</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6258,8 +6694,16 @@
           <t>LP-056411</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6317,8 +6761,16 @@
           <t>LP-056412</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6376,8 +6828,16 @@
           <t>LP-056389</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6435,8 +6895,16 @@
           <t>LP-056413</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6494,8 +6962,16 @@
           <t>LP-056414</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6553,8 +7029,16 @@
           <t>LP-056387</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6612,8 +7096,16 @@
           <t>LP-056415</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6671,8 +7163,16 @@
           <t>LP-056505</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6730,8 +7230,16 @@
           <t>LP-056507</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6789,8 +7297,16 @@
           <t>LP-056482</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6848,8 +7364,16 @@
           <t>LP-056386</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6907,8 +7431,16 @@
           <t>LP-056508</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6966,8 +7498,16 @@
           <t>LP-056510</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7025,8 +7565,16 @@
           <t>LP-056511</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7084,8 +7632,16 @@
           <t>LP-056489</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7143,8 +7699,16 @@
           <t>LP-056512</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7202,8 +7766,16 @@
           <t>LP-056513</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7261,8 +7833,16 @@
           <t>LP-056203</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7320,8 +7900,16 @@
           <t>LP-056516</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7379,8 +7967,16 @@
           <t>LP-056519</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7438,8 +8034,16 @@
           <t>LP-056521</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7497,8 +8101,16 @@
           <t>LP-056522</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7519,10 +8131,8 @@
           <t>Rodrigo Melo</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>4716505582-0023</t>
-        </is>
+      <c r="E115" t="n">
+        <v>685401</v>
       </c>
       <c r="F115" t="n">
         <v>4</v>
@@ -7558,8 +8168,16 @@
           <t>LP-056523</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7617,8 +8235,16 @@
           <t>LP-056454</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7676,8 +8302,16 @@
           <t>LP-056453</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7735,8 +8369,16 @@
           <t>LP-056525</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7796,8 +8438,16 @@
           <t>LP-056452</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7855,8 +8505,16 @@
           <t>LP-056496</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7914,8 +8572,16 @@
           <t>LP-056390</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7973,8 +8639,16 @@
           <t>LP-056528</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8032,8 +8706,16 @@
           <t>LP-056529</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8091,8 +8773,16 @@
           <t>LP-056495</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8152,8 +8842,16 @@
           <t>LP-056494</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8213,8 +8911,16 @@
           <t>LP-056493</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8272,8 +8978,16 @@
           <t>LP-056488</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8331,8 +9045,16 @@
           <t>LP-056487</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8390,8 +9112,16 @@
           <t>LP-056484</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -568,7 +568,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,7 +635,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -694,7 +702,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,7 +771,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -822,7 +838,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -887,7 +907,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -952,7 +976,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1013,7 +1041,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1076,7 +1108,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1139,7 +1175,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1200,7 +1240,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1263,7 +1307,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1326,7 +1374,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1389,7 +1441,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1454,7 +1510,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1519,7 +1579,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1584,7 +1648,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1647,7 +1715,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1710,7 +1782,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1773,7 +1849,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1836,7 +1916,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1899,7 +1983,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1960,7 +2048,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2023,7 +2115,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2086,7 +2182,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2149,7 +2249,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2212,7 +2316,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2277,7 +2385,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2342,7 +2454,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2405,7 +2521,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2468,7 +2588,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2531,7 +2655,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2594,7 +2722,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2657,7 +2789,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2720,7 +2856,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2781,7 +2921,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2846,7 +2990,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2909,7 +3057,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2972,7 +3124,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3035,7 +3191,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3098,7 +3258,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3161,7 +3325,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3224,7 +3392,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3287,7 +3459,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3350,7 +3526,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3413,7 +3593,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3476,7 +3660,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3539,7 +3727,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3602,7 +3794,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3665,7 +3861,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3728,7 +3928,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3789,7 +3993,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3852,7 +4060,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3913,7 +4125,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3976,7 +4192,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4039,7 +4259,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4097,8 +4321,16 @@
           <t>LP-056418</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4156,8 +4388,16 @@
           <t>LP-056419</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4215,8 +4455,16 @@
           <t>LP-056416</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4272,8 +4520,16 @@
           <t>LP-056331</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4331,8 +4587,16 @@
           <t>LP-056315</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4390,8 +4654,16 @@
           <t>LP-056338</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4449,8 +4721,16 @@
           <t>LP-056444</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4506,8 +4786,16 @@
           <t>LP-056429</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4563,8 +4851,16 @@
           <t>LP-056430</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4620,8 +4916,16 @@
           <t>LP-056431</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4677,8 +4981,16 @@
           <t>LP-056432</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4734,8 +5046,16 @@
           <t>LP-056433</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4791,8 +5111,16 @@
           <t>LP-056434</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4848,8 +5176,16 @@
           <t>LP-056435</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4905,8 +5241,16 @@
           <t>LP-056436</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4964,8 +5308,16 @@
           <t>LP-056437</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5023,8 +5375,16 @@
           <t>LP-056461</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5080,8 +5440,16 @@
           <t>LP-056459</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5137,8 +5505,16 @@
           <t>LP-056458</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5198,8 +5574,16 @@
           <t>LP-056428</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5257,8 +5641,16 @@
           <t>LP-056514</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5314,8 +5706,16 @@
           <t>LP-056448</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5371,8 +5771,16 @@
           <t>LP-056449</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5430,8 +5838,16 @@
           <t>LP-056447</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5489,8 +5905,16 @@
           <t>LP-056457</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,16 +508,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14191173</v>
+        <v>14199774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -525,22 +525,20 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>685605</v>
+        <v>685615</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4729111967POS1</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4729107112</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dispositivo DMAX GM</t>
+          <t>Separador Universal - Fabricação</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,12 +553,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3 630,00</t>
+          <t>16 000,00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LP-056782</t>
+          <t>LP-056783</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -577,16 +575,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11.03.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14219758</v>
+        <v>14204315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -600,14 +598,14 @@
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>4710800317</v>
+        <v>4711400664</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Contra Ponto Móvel BH</t>
+          <t>Castanhas CRIN 1/2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +620,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3 000,00</t>
+          <t>5 130,00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LP-056601</t>
+          <t>LP-056784</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -644,16 +642,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14237081</v>
+        <v>14210022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -661,25 +659,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>685485</v>
+        <v>685609</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>4710101560</v>
+        <v>4711202111</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IP 685485 Pinça CIL P7/P8 ⌀12 Zema 4593</t>
+          <t>Garra lateral - Blaichach</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -689,12 +687,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6 600,00</t>
+          <t>8 480,00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LP-056725</t>
+          <t>LP-056786</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -711,16 +709,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30.03.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14231208</v>
+        <v>14210076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -728,25 +726,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>685401</v>
+        <v>685615</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>4729111969</v>
+        <v>4728701143</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Pino Mikron</t>
+          <t>Pino de Alimentação CRIN1/2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -756,12 +754,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2 150,00</t>
+          <t>6 720,00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>LP-056734</t>
+          <t>LP-056785</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -778,16 +776,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30.03.2026</t>
+          <t>05.03.2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14231456</v>
+        <v>14216174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -795,25 +793,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>685421</v>
+        <v>685615</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>4730500051</v>
+        <v>4729110765</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DU 685421 Arruela de Vedação da Liebig</t>
+          <t>Trava borboleta</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -823,12 +821,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1 050,00</t>
+          <t>10 000,00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LP-056595</t>
+          <t>LP-056791</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -845,16 +843,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15.04.2026</t>
+          <t>05.03.2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14240773</v>
+        <v>14216263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -862,40 +860,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>685434</v>
+        <v>685615</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>4729108240</v>
+        <v>4710201038</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DU 685434 Encosto Fluxo Hidraulico acab.</t>
+          <t>Pino de Fixação ATMO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OrgId-ZERO</t>
+          <t>CtP/TEF11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1 260,00</t>
+          <t>8 800,00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>LP-057018</t>
+          <t>LP-056787</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -912,16 +910,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01.04.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14233070</v>
+        <v>14221652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -929,25 +927,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>685552</v>
+        <v>685616</v>
       </c>
       <c r="F8" t="n">
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>4710800241</v>
+        <v>4711401152</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Conta ponto</t>
+          <t>Garra de Alimentação</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -955,12 +953,14 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>600</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7 380,00</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>LP-056706</t>
+          <t>LP-056794</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -977,16 +977,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14234522</v>
+        <v>14221657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -994,25 +994,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>685484</v>
+        <v>685616</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>4719270019</v>
+        <v>4711401153</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IP 685484 Rebolo borazon Pistão A/P</t>
+          <t>Garra de Alimentação</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1020,12 +1020,14 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>220</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7 380,00</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LP-056709</t>
+          <t>LP-056795</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1042,16 +1044,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14234522</v>
+        <v>14221663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1059,25 +1061,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>685484</v>
+        <v>685616</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>4719266003</v>
+        <v>4712003296</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IP 685484 Rebolo borazon Pistão A/P</t>
+          <t>Suporte Castanhas da Placa</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1085,12 +1087,14 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>550</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6 800,00</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>LP-056710</t>
+          <t>LP-056796</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1107,16 +1111,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14234522</v>
+        <v>14221667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1124,25 +1128,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>685484</v>
+        <v>685616</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>4304800262</v>
+        <v>4718301652</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IP 685484 Rebolo borazon Pistão A/P</t>
+          <t>Prolongador Micro Rebolo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1150,12 +1154,14 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>550</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7 680,00</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>LP-056711</t>
+          <t>LP-056797</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1172,16 +1178,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14234522</v>
+        <v>14222163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1189,25 +1195,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>685484</v>
+        <v>685616</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>4304800434</v>
+        <v>4718301685</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IP 685484 Rebolo borazon Pistão A/P</t>
+          <t>Mordente Braço BH</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1215,12 +1221,14 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>550</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4 920,00</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>LP-056712</t>
+          <t>LP-056798</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1237,16 +1245,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>18.03.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14234770</v>
+        <v>14223596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1254,25 +1262,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>685434</v>
+        <v>685616</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>4728701263</v>
+        <v>4712002644</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DU 685434 Encosto Supfinas acabamento.</t>
+          <t>Batente de entrada de peça</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1282,12 +1290,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3 600,00</t>
+          <t>6 000,00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LP-056864</t>
+          <t>LP-056800</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1304,16 +1312,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05.03.2026</t>
+          <t>18.03.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14216157</v>
+        <v>14223604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1327,14 +1335,14 @@
         <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>4718301647</v>
+        <v>4712003012</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pino desalimentador</t>
+          <t>DANFOSS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1349,12 +1357,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5 200,00</t>
+          <t>4 800,00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>LP-056792</t>
+          <t>LP-056801</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1371,16 +1379,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11.04.2026</t>
+          <t>25.03.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14238285</v>
+        <v>14227679</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1388,25 +1396,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>685487</v>
+        <v>685616</v>
       </c>
       <c r="F15" t="n">
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>4729400390</v>
+        <v>4711400961</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IP 685487 Buchas ZL CIL A 7498 (Lino)</t>
+          <t>Castanha da Placa Voumard</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>FERNANDA A</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1416,12 +1424,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10 200,00</t>
+          <t>6 120,00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>LP-056888</t>
+          <t>LP-056802</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1438,16 +1446,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11.04.2026</t>
+          <t>27.03.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14238305</v>
+        <v>14230338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1455,7 +1463,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>685412</v>
+        <v>685868</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
@@ -1463,17 +1471,15 @@
       <c r="G16" t="n">
         <v>10</v>
       </c>
-      <c r="H16" t="n">
-        <v>4728701270</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DU 685412 Disp. "jacaré" Bahmuller POS 1</t>
+          <t>Parafuso do mandril espanado</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>AOKI</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1483,12 +1489,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3 300,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>LP-056893</t>
+          <t>LP-056551</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1505,16 +1511,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>30.03.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14241307</v>
+        <v>14231153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1522,25 +1528,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>685411</v>
+        <v>685553</v>
       </c>
       <c r="F17" t="n">
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>4712004723</v>
+        <v>4729105687</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DU 685411 Pino alimentador UVA Bico S60</t>
+          <t>Cone da montagem</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>REGIMARA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1548,14 +1554,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2 550,00</t>
-        </is>
+      <c r="L17" t="n">
+        <v>600</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>LP-057026</t>
+          <t>LP-056570</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1572,16 +1576,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17.03.2026</t>
+          <t>30.03.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14222770</v>
+        <v>14231154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1589,25 +1593,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>685616</v>
+        <v>685553</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>4729110830</v>
+        <v>4729105958</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Contra ponto fixo de desalimentação - BH</t>
+          <t>Cone da montagem</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FERNANDA A</t>
+          <t>REGIMARA</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1615,14 +1619,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>3 060,00</t>
-        </is>
+      <c r="L18" t="n">
+        <v>600</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>LP-056602</t>
+          <t>LP-056572</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1639,16 +1641,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>30.03.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14222176</v>
+        <v>14231160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1656,25 +1658,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>685616</v>
+        <v>685553</v>
       </c>
       <c r="F19" t="n">
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>4718301687</v>
+        <v>4729105684</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Guia de entrada de peças</t>
+          <t>Cone da montagem</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FERNANDA A</t>
+          <t>REGIMARA</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1682,14 +1684,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>4 160,00</t>
-        </is>
+      <c r="L19" t="n">
+        <v>400</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>LP-056799</t>
+          <t>LP-056562</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1706,16 +1706,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12.03.2026</t>
+          <t>30.03.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14220157</v>
+        <v>14231163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1723,25 +1723,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>685616</v>
+        <v>685553</v>
       </c>
       <c r="F20" t="n">
         <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>4730502750</v>
+        <v>4729105685</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pino Descarregador</t>
+          <t>Cone da montagem</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FERNANDA A</t>
+          <t>REGIMARA</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1749,14 +1749,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>11 440,00</t>
-        </is>
+      <c r="L20" t="n">
+        <v>430</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>LP-056793</t>
+          <t>LP-056571</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1773,16 +1771,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14237764</v>
+        <v>14232959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1790,20 +1788,20 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>685434</v>
+        <v>685412</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4712002037</v>
+        <v>4728701079</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DU 685434 Bico de refrigeração/rebarbar</t>
+          <t>DU 685412 Roldanas Retíficas Bahmuller.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1818,12 +1816,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3 520,00</t>
+          <t>1 000,00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>LP-056863</t>
+          <t>LP-056594</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1840,7 +1838,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02.04.2026</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1849,7 +1847,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14233562</v>
+        <v>14233039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1857,25 +1855,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>685436</v>
+        <v>685541</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>4711300649</v>
+        <v>4729401707</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DU 685436 Garra retífica Zema 7779 Bico</t>
+          <t>Disp. Nagel</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>DOUGLAS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1883,14 +1881,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>3 560,00</t>
-        </is>
+      <c r="L22" t="n">
+        <v>600</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LP-056733</t>
+          <t>LP-056704</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1907,16 +1903,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13.04.2026</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14238834</v>
+        <v>14233047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1930,14 +1926,14 @@
         <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>4729401968</v>
+        <v>4729401706</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bucha guia</t>
+          <t>Disp. Nagel</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1950,14 +1946,12 @@
           <t>CtP/TEF11</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>4 400,00</t>
-        </is>
+      <c r="L23" t="n">
+        <v>300</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LP-056926</t>
+          <t>LP-056705</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1974,16 +1968,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>02.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14233538</v>
+        <v>14235483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1991,25 +1985,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>685411</v>
+        <v>685610</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>4710800193</v>
+        <v>4710900949</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DU 685411 Contra ponto Haste Cheia U.D</t>
+          <t>Soquete</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>DOUGLAS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2019,12 +2013,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4 000,00</t>
+          <t>3 330,00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>LP-056731</t>
+          <t>LP-056766</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2041,16 +2035,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05.03.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14216259</v>
+        <v>14235485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2058,25 +2052,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>685615</v>
+        <v>685610</v>
       </c>
       <c r="F25" t="n">
         <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>4710101050</v>
+        <v>4710900765</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pinça 3,68 ATMO</t>
+          <t>Soquete</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FERNANDA A</t>
+          <t>DOUGLAS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2086,12 +2080,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13 600,00</t>
+          <t>3 000,00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>LP-056790</t>
+          <t>LP-056764</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2108,16 +2102,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14238754</v>
+        <v>14235503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2125,20 +2119,20 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>685541</v>
+        <v>685610</v>
       </c>
       <c r="F26" t="n">
         <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4729401241</v>
+        <v>4710900839</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Bucha guia</t>
+          <t>Soquete</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2153,12 +2147,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>11 200,00</t>
+          <t>3 150,00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>LP-056927</t>
+          <t>LP-056765</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2175,16 +2169,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14239016</v>
+        <v>14235507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2192,25 +2186,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>685008</v>
+        <v>685610</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>4728603405</v>
+        <v>4729110891</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BERÇO HPC Pos. 01</t>
+          <t>Soquete</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>REGIMARA</t>
+          <t>DOUGLAS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2220,12 +2214,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1 980,00</t>
+          <t>3 090,00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>LP-056915</t>
+          <t>LP-056745</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2242,16 +2236,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.04.2026</t>
+          <t>11.04.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12.06.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14239016</v>
+        <v>14238328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2259,25 +2253,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>685008</v>
+        <v>685421</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>4728603405</v>
+        <v>4729110119</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BERÇO HPC Pos. 02</t>
+          <t>DU 685421 Conector ∅4/4 (AGIEs)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>REGIMARA</t>
+          <t>DONI- 2803</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2287,12 +2281,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1 980,00</t>
+          <t>1 100,00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>LP-056916</t>
+          <t>LP-056875</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2318,7 +2312,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14238792</v>
+        <v>14238730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2332,10 +2326,10 @@
         <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>4729401197</v>
+        <v>4729401595</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2354,12 +2348,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8 800,00</t>
+          <t>5 480,00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>LP-056921</t>
+          <t>LP-056930</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2372,6 +2366,3527 @@
           <t>Cadastrada</t>
         </is>
       </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>14238802</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>685541</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4729401967</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Bucha guia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4 400,00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>LP-056931</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14238854</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>685433</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4718300100</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DU 685433 Base d Lepadora montagem bico</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1 600,00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>LP-056937</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>14238899</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>685606</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>4710900857-POS.4</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ponteira est.40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PGU3CT</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>CtP/MFW32-A</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>LP-056906</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>14238923</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>685541</v>
+      </c>
+      <c r="F33" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4727501440</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Posição 4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>480</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>LP-056925</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14239037</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4729110011</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DU 685434 Pino centralizador das lavador</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>LP-056940</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>14239194</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F35" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4711202072</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Régua</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2 000,00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>LP-056922</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14239241</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F36" t="n">
+        <v>19</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4710800241</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Contra ponto</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1 320,00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>LP-056929</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>14239245</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F37" t="n">
+        <v>19</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4710800277</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Contra ponto</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1 980,00</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>LP-056924</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14239248</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F38" t="n">
+        <v>19</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4710800350</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Contra ponto</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>660</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>LP-056923</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>13.04.2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>14239255</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>685556</v>
+      </c>
+      <c r="F39" t="n">
+        <v>19</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4729106992</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Encosto da placa</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>DOUGLAS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>LP-056928</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14239567</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F40" t="n">
+        <v>19</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4730502592</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>DU 685421 Pino de fixação Q1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3 500,00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>LP-056939</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>14239668</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F41" t="n">
+        <v>19</v>
+      </c>
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4729111171</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>DU 685421 Suporte de parafuso radial Q1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2 100,00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>LP-056938</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>14239767</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F42" t="n">
+        <v>19</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4711201790</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>DU 685411 Pino  Nomyline ∅3,5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1 500,00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LP-056914</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>14239772</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>685606</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4729107661</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bico de lavagem de peças Montagem</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FERNANDA A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2 200,00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LP-057012</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>14239779</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>685606</v>
+      </c>
+      <c r="F44" t="n">
+        <v>19</v>
+      </c>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4728602302_041A</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Haste de torque</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FERNANDA A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3 700,00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>LP-057045</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>14239819</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>685433</v>
+      </c>
+      <c r="F45" t="n">
+        <v>19</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4729110280</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>DU 685433 Mandril garra robo Pako</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4 400,00</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>LP-056935</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>14239819</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>685433</v>
+      </c>
+      <c r="F46" t="n">
+        <v>19</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4729110280</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>DU 685433 Mandril garra robo POSIÇÃO 2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1 100,00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>LP-056936</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>14239855</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>685438</v>
+      </c>
+      <c r="F47" t="n">
+        <v>19</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4712004560</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>DU 685438 Prisma peça acabada - ZEMA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2 300,00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>LP-056934</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>14240297</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>685432</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>4728603152-POS25</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>POSIÇÃO 25 DO ROBO da embalagem</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2 560,00</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>LP-056956</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>14240800</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F49" t="n">
+        <v>20</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4712001958</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>DU 685434 Garra lavadora Gluth Estaç.1/8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2 400,00</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>LP-056955</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>14241327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F50" t="n">
+        <v>19</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4711200727</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>DU 685434 Chapa d alimentação acabamen.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2 640,00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>LP-057109</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>14241351</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4712001959</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>DU 685434 Garra lavadora Gluth Estação 1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>3 000,00</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>LP-057102</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>14241372</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F52" t="n">
+        <v>19</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4729109958</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>DU 685434 Anel de vedação de placa</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LP-057110</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>14241513</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>685868</v>
+      </c>
+      <c r="F53" t="n">
+        <v>19</v>
+      </c>
+      <c r="G53" t="n">
+        <v>21</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4710301092</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CONSERTO MANDRIS DRAG FINISH</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>SOG5CT</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2 940,00</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>LP-057088</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>14241552</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F54" t="n">
+        <v>19</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4711401009</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>DU 685434 Dedo garra supfina direito</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1 400,00</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>LP-057104</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>14241552</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F55" t="n">
+        <v>19</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4711401010</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>DU 685434 Dedo garra supfina esquerdo</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1 400,00</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>LP-057105</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>14241557</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4729110120</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>DU 685421 Conector ∅4/6 AGIEs</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1 640,00</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>LP-057103</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>14241569</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>685412</v>
+      </c>
+      <c r="F57" t="n">
+        <v>19</v>
+      </c>
+      <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4728701264</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>DU 685412 Haste de retorno BAHMULLER</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2 300,00</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>LP-057106</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>14241569</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>685412</v>
+      </c>
+      <c r="F58" t="n">
+        <v>19</v>
+      </c>
+      <c r="G58" t="n">
+        <v>20</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4728701082</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>DU 685412 Haste de retorno BAHMULLER</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2 500,00</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>LP-057107</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>14241569</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>685412</v>
+      </c>
+      <c r="F59" t="n">
+        <v>19</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4712003920</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DU 685412 Suporte de apoio Agul. Bahmull</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2 700,00</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>LP-057108</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>14241591</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>685485</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4710800183</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IP 685485 Contra ponto zemas Cilindro P</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2 640,00</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>LP-057063</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>14241630</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>685614</v>
+      </c>
+      <c r="F61" t="n">
+        <v>19</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4712002909</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Pino</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SLV7CT</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>CtP/ETS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2 140,00</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LP-057090</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>14242047</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F62" t="n">
+        <v>19</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4729105209</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>DU 685434 Garra da pinça rotativa curta</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>5 660,00</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>LP-057100</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14242081</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F63" t="n">
+        <v>19</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4730502517</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>DU 685434 Pino lança lavadora rotatória</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>3 100,00</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>LP-057096</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>14242088</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F64" t="n">
+        <v>19</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4730502874</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DU 685434 Pino Centralizador Lavador.Glu</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>880</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>LP-057097</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>14242201</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F65" t="n">
+        <v>19</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4711202126</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>DU 685411 POS 1 Régua alimentadora UVA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2 350,00</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>LP-057150</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>14242201</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F66" t="n">
+        <v>19</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4711202126</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>DU 685411 POS 3 Régua alimentadora UVA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1 320,00</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>LP-057151</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>14242268</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F67" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4728701223</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>DU 685434 Vareta retífica curso(acabamen</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>880</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>LP-057098</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>14242268</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4728701030</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>DU 685434 Vareta retífica curso(acabamen</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>880</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>LP-057099</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>14242268</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4729106548</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>DU 685434 Vareta retífica curso(acabamen</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>880</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>LP-057101</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>14242284</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4711301136</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DU 685411 Chapa da retífica externa HTT</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1 560,00</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>LP-057113</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>14243433</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4710800192</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DU 685411 Contra P. Haste Rebaixada U.D</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>4 800,00</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>LP-057081</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>14243629</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F72" t="n">
+        <v>19</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4729111137 POS1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>DU 685421 POSIÇÃO 1 da Bucha roscada</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1 650,00</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>LP-057152</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>14243733</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F73" t="n">
+        <v>19</v>
+      </c>
+      <c r="G73" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4727500865</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>DU 685421 Presilha Q1 Bico P AGIE</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>LP-057153</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>14243767</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>685491</v>
+      </c>
+      <c r="F74" t="n">
+        <v>19</v>
+      </c>
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4711202060</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>IP-685491 POSIÇÃO 9 Folha 10/14 (Mola)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>500</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>LP-057118</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14243921</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>685541</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4727501151</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>PORTA BUCHA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1 400,00</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>LP-057139</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>14243923</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>685541</v>
+      </c>
+      <c r="F76" t="n">
+        <v>19</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4727501155</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PORTA BUCHA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>400</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>LP-057124</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>14243929</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>685553</v>
+      </c>
+      <c r="F77" t="n">
+        <v>19</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4729105685</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Cone da montagem</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>480</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>LP-057135</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>14244021</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>685553</v>
+      </c>
+      <c r="F78" t="n">
+        <v>19</v>
+      </c>
+      <c r="G78" t="n">
+        <v>10</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4730500932</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Arruela filtro bastão</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2 800,00</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>LP-057131</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>14244347</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>685434</v>
+      </c>
+      <c r="F79" t="n">
+        <v>19</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4711200733</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DU 685434 Pino de medição curva supfina</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2 960,00</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>LP-057154</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>14244635</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F80" t="n">
+        <v>19</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4718301625</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Régua de apoio</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2 200,00</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>LP-057136</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>14244637</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F81" t="n">
+        <v>19</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4710800277</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>CONTRAPONTO</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1 320,00</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>LP-057122</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>14244639</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>685552</v>
+      </c>
+      <c r="F82" t="n">
+        <v>19</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4710800184</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CONTRAPONTO</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>660</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LP-057123</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>14244641</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>685556</v>
+      </c>
+      <c r="F83" t="n">
+        <v>19</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4729106992</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Encosto da placa</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>REGIMARA</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1 000,00</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LP-057138</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>14245095</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>685421</v>
+      </c>
+      <c r="F84" t="n">
+        <v>19</v>
+      </c>
+      <c r="G84" t="n">
+        <v>30</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4729110321</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DU 685421 Dummy bico Agie</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>3 000,00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>LP-057163</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -568,7 +568,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,7 +635,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,7 +704,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,7 +771,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -822,7 +838,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,7 +905,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -948,7 +972,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1011,7 +1039,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1074,7 +1106,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1139,7 +1175,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1202,7 +1242,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1265,7 +1309,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1328,7 +1376,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1391,7 +1443,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1454,7 +1510,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1517,7 +1577,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1580,7 +1644,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1643,7 +1711,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1708,7 +1780,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1771,7 +1847,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1834,7 +1914,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1897,7 +1981,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1960,7 +2048,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9953,7 +10045,11 @@
           <t>LP-057115</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -10012,7 +10108,11 @@
           <t>LP-057114</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -10071,7 +10171,11 @@
           <t>LP-057142</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -10130,7 +10234,11 @@
           <t>LP-057141</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -10189,7 +10297,11 @@
           <t>LP-057140</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
@@ -10248,7 +10360,11 @@
           <t>LP-057137</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -10307,7 +10423,11 @@
           <t>LP-057134</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
@@ -10368,7 +10488,11 @@
           <t>LP-057133</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -10427,7 +10551,11 @@
           <t>LP-057132</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -10486,7 +10614,11 @@
           <t>LP-057128</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -10547,7 +10679,11 @@
           <t>LP-057130</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -10608,7 +10744,11 @@
           <t>LP-057129</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -10669,7 +10809,11 @@
           <t>LP-057126</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
@@ -10728,7 +10872,11 @@
           <t>LP-057125</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -10789,7 +10937,11 @@
           <t>LP-057164</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
@@ -10848,7 +11000,11 @@
           <t>LP-057047</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr"/>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -2115,7 +2115,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2178,7 +2182,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2241,7 +2249,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2306,7 +2318,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2369,7 +2385,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2432,7 +2452,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2495,7 +2519,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2558,7 +2586,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2621,7 +2653,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2684,7 +2720,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2747,7 +2787,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2810,7 +2854,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2873,7 +2921,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2936,7 +2988,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2997,7 +3053,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3060,7 +3120,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3123,7 +3187,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3184,7 +3252,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3247,7 +3319,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3310,7 +3386,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3375,7 +3455,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3440,7 +3524,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3505,7 +3593,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3568,7 +3660,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3633,7 +3729,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3696,7 +3796,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3761,7 +3865,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3824,7 +3932,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3887,7 +3999,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3950,7 +4066,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4013,7 +4133,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4076,7 +4200,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4139,7 +4267,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4204,7 +4336,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4267,7 +4403,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4330,7 +4470,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4393,7 +4537,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4456,7 +4604,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4521,7 +4673,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4586,7 +4742,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4649,7 +4809,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4712,7 +4876,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4775,7 +4943,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4838,7 +5010,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4901,7 +5077,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4964,7 +5144,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5027,7 +5211,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5092,7 +5280,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5157,7 +5349,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5222,7 +5418,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5287,7 +5487,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5352,7 +5556,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5417,7 +5625,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5482,7 +5694,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5547,7 +5763,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5608,7 +5828,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5671,7 +5895,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5734,7 +5962,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5797,7 +6029,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5860,7 +6096,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5923,7 +6163,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5986,7 +6230,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6049,7 +6297,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6112,7 +6364,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6177,7 +6433,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6240,7 +6500,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6305,7 +6569,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6370,7 +6638,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6433,7 +6705,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6496,7 +6772,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6559,7 +6839,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6622,7 +6906,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6685,7 +6973,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6748,7 +7040,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6811,7 +7107,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6874,7 +7174,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6939,7 +7243,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7002,7 +7310,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7065,7 +7377,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7128,7 +7444,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7193,7 +7513,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7256,7 +7580,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7319,7 +7647,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7382,7 +7714,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7445,7 +7781,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7508,7 +7848,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7571,7 +7915,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7634,7 +7982,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7697,7 +8049,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7760,7 +8116,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7825,7 +8185,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7890,7 +8254,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7955,7 +8323,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8018,7 +8390,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8081,7 +8457,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8146,7 +8526,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8209,7 +8593,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8272,7 +8660,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8337,7 +8729,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8402,7 +8798,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8467,7 +8867,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8532,7 +8936,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8595,7 +9003,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8658,7 +9070,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8721,7 +9137,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8786,7 +9206,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8849,7 +9273,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8914,7 +9342,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8977,7 +9409,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9040,7 +9476,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9103,7 +9543,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9166,7 +9610,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9229,7 +9677,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9292,7 +9744,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9355,7 +9811,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9418,7 +9878,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9481,7 +9945,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9544,7 +10012,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9607,7 +10079,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9670,7 +10146,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9733,7 +10213,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9798,7 +10282,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9861,7 +10349,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9924,7 +10416,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9987,7 +10483,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10050,7 +10550,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10113,7 +10617,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10176,7 +10684,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10239,7 +10751,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10302,7 +10818,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10365,7 +10885,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10428,7 +10952,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10493,7 +11021,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10556,7 +11088,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10619,7 +11155,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10684,7 +11224,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10749,7 +11293,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10814,7 +11362,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10877,7 +11429,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10942,7 +11498,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11005,7 +11565,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,7 +635,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,7 +704,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -757,7 +769,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -818,7 +834,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,7 +899,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -940,7 +964,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1003,7 +1031,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1063,8 +1095,16 @@
           <t>LP-057166</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1122,8 +1162,16 @@
           <t>LP-057277</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1181,8 +1229,16 @@
           <t>LP-057278</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1240,8 +1296,16 @@
           <t>LP-057279</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1301,8 +1365,16 @@
           <t>LP-057201</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1360,8 +1432,16 @@
           <t>LP-057167</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1419,8 +1499,16 @@
           <t>LP-057165</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1478,8 +1566,16 @@
           <t>LP-057168</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1539,8 +1635,16 @@
           <t>LP-057200</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1600,8 +1704,16 @@
           <t>LP-057199</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1659,8 +1771,16 @@
           <t>LP-057218</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1718,8 +1838,16 @@
           <t>LP-057216</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1777,8 +1905,16 @@
           <t>LP-057215</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1836,8 +1972,16 @@
           <t>LP-057214</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1897,8 +2041,16 @@
           <t>LP-057213</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1958,8 +2110,16 @@
           <t>LP-057242</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2019,8 +2179,16 @@
           <t>LP-057239</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2080,8 +2248,16 @@
           <t>LP-057237</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2141,8 +2317,16 @@
           <t>LP-057238</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2163,22 +2347,20 @@
           <t>Rodrigo Melo</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>685433</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>4738360434-0082</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>4738360434-0082</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>OGIVA</t>
@@ -2204,8 +2386,16 @@
           <t>LP-057240</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2265,8 +2455,16 @@
           <t>LP-057236</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2326,8 +2524,16 @@
           <t>LP-057241</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2337,11 +2543,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14245093</v>
+        <v>14245099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2349,20 +2555,20 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>685485</v>
+        <v>685541</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>4738361126</v>
+        <v>4713400000</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Novos séries 0002 e 0003</t>
+          <t>Novo - serie 0210</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2372,26 +2578,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>PS/QMM7-CtP</t>
+          <t>OrgId-ZERO</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4 000,00</t>
+          <t>4 200,00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>LP-057169</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>LP-057301</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>27.04.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2400,7 +2614,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14245099</v>
+        <v>14247250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2408,7 +2622,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>685541</v>
+        <v>685531</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -2416,12 +2630,14 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="n">
-        <v>4713400000</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4716404232-0004</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Novo - serie 0210</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2431,21 +2647,29 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>OrgId-ZERO</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4 200,00</t>
+          <t>1 800,00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>LP-057301</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+          <t>LP-057299</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2459,7 +2683,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14247250</v>
+        <v>14247311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2467,7 +2691,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>685531</v>
+        <v>685700</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -2477,7 +2701,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4716404232-0004</t>
+          <t>4716405492-0001</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2502,16 +2726,24 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>LP-057299</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>LP-057308</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>27.04.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2520,7 +2752,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14247311</v>
+        <v>14247739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2528,7 +2760,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>685700</v>
+        <v>685546</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -2536,14 +2768,12 @@
       <c r="G35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4716405492-0001</t>
-        </is>
+      <c r="H35" t="n">
+        <v>4715400088</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LX - Conserto</t>
+          <t>Novo - serie 0015</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2553,26 +2783,34 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>PS/QMM7-CtP</t>
+          <t>OrgId-ZERO</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1 800,00</t>
+          <t>4 000,00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>LP-057308</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>LP-057300</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28.04.2026</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2581,7 +2819,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14247739</v>
+        <v>14250587</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2589,7 +2827,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>685546</v>
+        <v>685554</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -2597,12 +2835,14 @@
       <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
-        <v>4715400088</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4715301059-0001</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Novo - serie 0015</t>
+          <t>LO - conserto</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2612,35 +2852,43 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>OrgId-ZERO</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4 000,00</t>
+          <t>1 000,00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>LP-057300</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>LP-057314</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14250587</v>
+        <v>14251760</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2648,22 +2896,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>685554</v>
+        <v>685606</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4715301059-0001</t>
+          <t>DISP. ST05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LO - conserto</t>
+          <t>Disp. ST05 (Alexandre)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2683,72 +2931,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>LP-057314</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>04.05.2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>14251760</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Rodrigo Melo</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>685606</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>DISP. ST05</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Disp. ST05 (Alexandre)</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>QMM</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>PS/QMM7-CtP</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1 000,00</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
           <t>LP-057195</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -508,69 +508,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14279841</v>
+        <v>14283867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rodrigo Melo</t>
+          <t>Yesica Gonzalez</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>685553</v>
+        <v>685482</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4716506891-0015</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4702500235</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LY - conserto</t>
+          <t>IP 685482 Pino de contato EMC Usinag.Mol</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>QMM</t>
+          <t>DONI- 2803</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PS/QMM7-CtP</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>300</v>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>11 500,00</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LP-057630</t>
+          <t>LP-057752</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
+          <t>Erro</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22.05.2026</t>
+          <t>18.05.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14283867</v>
+        <v>14281263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -525,25 +525,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>685482</v>
+        <v>685552</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>4702500235</v>
+        <v>4711400652</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IP 685482 Pino de contato EMC Usinag.Mol</t>
+          <t>Jogo de garra</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>DOUGLAS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -553,20 +553,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11 500,00</t>
+          <t>4 350,00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LP-057752</t>
+          <t>LP-057669</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Erro</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,60 +508,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04.05.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14251586</v>
+        <v>14245076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>685421</v>
+        <v>685433</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4729500344</v>
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4738360388-0026</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DU 685421 Bucha de vedação hidráulico</t>
+          <t>OGIVA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>800</v>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2 500,00</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LP-057596</t>
+          <t>LP-057621</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cadastrada</t>
+          <t>Erro</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -573,55 +577,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05.05.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14252522</v>
+        <v>14245081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>685412</v>
+        <v>685433</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4728701079</v>
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4738360388-0026</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DU 685412 Roldanas Retíf.Bahmuller Agulh</t>
+          <t>OGIVA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>800</v>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2 500,00</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LP-057592</t>
+          <t>LP-057622</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -638,57 +646,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14252955</v>
+        <v>14245085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>685433</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4721900217</v>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4738360388-0047</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DU 685433 Pino fixação de pano escovação</t>
+          <t>OGIVA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1 960,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LP-057594</t>
+          <t>LP-057623</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -705,57 +715,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14253042</v>
+        <v>14245087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>685433</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>4729105899</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4738360388-0001</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DU 685433 Tampa de lavadora (Ederson aj.</t>
+          <t>OGIVA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>9 680,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>LP-057593</t>
+          <t>LP-057624</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -772,57 +784,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14253065</v>
+        <v>14245459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>685438</v>
+        <v>685541</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>4729106548</v>
+        <v>4716600095</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DU 685438 Vareta copiadora Bico S</t>
+          <t>Novos - serie 0004 ao 0011</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2 640,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LP-057595</t>
+          <t>LP-057625</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -839,57 +851,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14253732</v>
+        <v>14245483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>685421</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>4729111119</v>
+        <v>4716509989</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DU 685421 Bico direcionador de lubrific.</t>
+          <t>Novos - serie 0020 ao 0029</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 400,00</t>
+          <t>3 000,00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>LP-057603</t>
+          <t>LP-057626</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -906,55 +918,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>27.04.2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14253740</v>
+        <v>14247320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>685421</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>4712004263</v>
+        <v>4716402796</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DU 685421 Guia de eletrodo AGIEs</t>
+          <t>Novo - serie 0020</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>950</v>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2 500,00</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>LP-057598</t>
+          <t>LP-057711</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -971,57 +985,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14253919</v>
+        <v>14247889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>685433</v>
+        <v>685421</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>4718300100</v>
+        <v>4716406262</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DU 685433 Base d Lepadora montagem bico</t>
+          <t>Novo - Posição 236</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1 600,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>500</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LP-057597</t>
+          <t>LP-057684</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1038,47 +1050,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14276504</v>
+        <v>14247896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>685434</v>
+        <v>685421</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>4720100025</v>
+        <v>4716406262</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DU 685434 Pedra Óleo ø7.95 (acabamento)</t>
+          <t>Novo - Posição 236</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1086,7 +1098,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>LP-057599</t>
+          <t>LP-057685</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1103,57 +1115,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14277583</v>
+        <v>14248039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>685434</v>
+        <v>685411</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>4710101380</v>
+        <v>4716406386</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DU 685434 Garra de fixação estação 2</t>
+          <t>Novo - serie 0004</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3 040,00</t>
+          <t>2 000,00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>LP-057600</t>
+          <t>LP-057683</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1170,57 +1182,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14277662</v>
+        <v>14248597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>685434</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4729110011</v>
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4716506424-0020</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DU 685434 Pino centralizador das lavador</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6 720,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>500</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>LP-057601</t>
+          <t>LP-057686</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1237,59 +1249,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14278186</v>
+        <v>14248628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>685401</v>
+        <v>685434</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4729109898/BB8118</t>
+          <t>4716506424-0026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Disp. ECM</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>17 360,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>500</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LP-057724</t>
+          <t>LP-057687</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1306,57 +1316,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14279062</v>
+        <v>14248718</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>685434</v>
+        <v>685411</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4729111741</v>
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4716404843-1041</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DU 685434 Garra linha automática acabam.</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2 100,00</t>
+          <t>1 200,00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>LP-057604</t>
+          <t>LP-057712</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1373,57 +1385,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14279126</v>
+        <v>14248719</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>685411</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4710800192</v>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4716406205-0005</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DU 685411 Contra P. Haste Rebaixada U.D</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>4 800,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>800</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>LP-057646</t>
+          <t>LP-057688</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1440,57 +1452,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14279130</v>
+        <v>14248764</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>685411</v>
+        <v>685401</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4710800193</v>
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4716403614-0001</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DU 685411 Contra P. Haste Cheia U.D</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>4 000,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>800</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>LP-057645</t>
+          <t>LP-057689</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1507,57 +1519,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14279700</v>
+        <v>14249649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>685434</v>
+        <v>685411</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4729109419</v>
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4316400347-0016</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DU 685434 POSIÇÃO 11 Base exame visual</t>
+          <t>LY - conserto</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1 000,00</t>
-        </is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>900</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>LP-057605</t>
+          <t>LP-057709</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1574,57 +1586,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>30.04.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14279700</v>
+        <v>14250613</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>685434</v>
+        <v>685401</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4729109419</v>
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4316400347-0031</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DU 685434 POSIÇÃO 12 Base exame visual</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1 000,00</t>
-        </is>
+          <t>OrgId-ZERO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>900</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>LP-057606</t>
+          <t>LP-057710</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1641,57 +1653,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14280095</v>
+        <v>14251638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>685438</v>
+        <v>685433</v>
       </c>
       <c r="F19" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>4729106549</v>
+        <v>4716600096</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DU 685438 Bucha guia de curso ∅6 (Bico S</t>
+          <t>Novos - series 0006 ao 0013</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2 200,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>LP-057607</t>
+          <t>LP-057713</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1708,57 +1720,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14280142</v>
+        <v>14251726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>685487</v>
+        <v>685421</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>4729400390</v>
+        <v>4716510049</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IP 685487 POSIÇÃO 1 Bucha Cil A ZL-7498</t>
+          <t>Novos - series 0015 ao 0022</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1 500,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>LP-057734</t>
+          <t>LP-057714</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1775,57 +1787,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14280197</v>
+        <v>14251751</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>685485</v>
+        <v>685411</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>4729401011</v>
+        <v>4716506796</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IP 685485 POSIção 1 Bucha Cil P3 ZL30842</t>
+          <t>Novos - series 0057 ao 0065</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2 000,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>LP-057735</t>
+          <t>LP-057715</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1842,59 +1854,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14280265</v>
+        <v>14251802</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>685704</v>
+        <v>685412</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4710900878-002</t>
+          <t>4716405933-0024</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PUNÇÃO DE PRENSAGEM - UIN2</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>JHEYMIS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SO/OPM-TS23-BR</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>6 000,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>500</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LP-057632</t>
+          <t>LP-057716</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1911,57 +1921,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14280378</v>
+        <v>14251807</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>685411</v>
+        <v>685435</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4711401379</v>
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4716404682-0002</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DU 685411 Garra do robô da Nomyline U.d</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>3 180,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>600</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LP-057815</t>
+          <t>LP-057717</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1978,55 +1988,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>05.05.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14280766</v>
+        <v>14252293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>685552</v>
+        <v>685412</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="n">
-        <v>4710800350</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4716506412-0138</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Contra ponto</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>660</v>
+        <v>400</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>LP-057661</t>
+          <t>LP-057718</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2043,55 +2055,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>05.05.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14280767</v>
+        <v>14252298</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>685552</v>
+        <v>685434</v>
       </c>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="n">
-        <v>4710800349</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4716506412-0157</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Contra ponto</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>660</v>
+        <v>500</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>LP-057660</t>
+          <t>LP-057719</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2108,57 +2122,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>05.05.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14281168</v>
+        <v>14252370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>685411</v>
+        <v>685401</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4710101475</v>
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4716507090-0016</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DU 685411 Garra d Pinça H.Rebaixada HTT</t>
+          <t>LY - conserto</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2 360,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>500</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>LP-057647</t>
+          <t>LP-057756</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2175,57 +2189,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14281264</v>
+        <v>14253168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>685412</v>
+        <v>685421</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4712004543</v>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4716505611-0005</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 3,5mm HTT Agu.</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2 640,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>500</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>LP-057649</t>
+          <t>LP-057757</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2242,57 +2256,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14281264</v>
+        <v>14253171</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>685412</v>
+        <v>685434</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4711401168</v>
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4716506417-0019</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DU 685412 Garra do robô HTT 2...23351</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>4 620,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>500</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>LP-057650</t>
+          <t>LP-057758</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2309,57 +2323,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14281264</v>
+        <v>14253182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>685412</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4711401169</v>
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>4716406331-0001</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 3,5mm HTT Agu.</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1 650,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>500</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>LP-057651</t>
+          <t>LP-057759</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2376,57 +2390,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14281264</v>
+        <v>14253187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>685412</v>
+        <v>685433</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4711401170</v>
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4738360388-0036</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 3,5mm HTT Agu.</t>
+          <t>OGIVA - conserto</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1 650,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>LP-057652</t>
+          <t>LP-057760</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2443,57 +2459,59 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14281264</v>
+        <v>14253191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>685412</v>
+        <v>685433</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>4711401171</v>
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>4738360434-0075</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 3,5mm HTT Agu.</t>
+          <t>OGIVA - conserto</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4 470,00</t>
+          <t>2 500,00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>LP-057653</t>
+          <t>LP-057761</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2510,57 +2528,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14281280</v>
+        <v>14276434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>685412</v>
+        <v>685401</v>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>4712004544</v>
+        <v>4716511971</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 4,0mm HTT Agu.</t>
+          <t>Novos - series 0002 e 0003</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2 640,00</t>
+          <t>3 500,00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>LP-057635</t>
+          <t>LP-057767</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2577,57 +2595,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14281280</v>
+        <v>14276636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>685412</v>
+        <v>685435</v>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>4711401172</v>
+        <v>4716400356</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 4,0mm HTT Agu.</t>
+          <t>Novo - serie 0364</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1 650,00</t>
+          <t>2 000,00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>LP-057636</t>
+          <t>LP-057768</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2644,57 +2662,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14281280</v>
+        <v>14276670</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>685412</v>
+        <v>685433</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>4711401173</v>
+        <v>4716404252</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 4,0mm HTT Agu.</t>
+          <t>Novo - Posição 45</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1 650,00</t>
+          <t>1 200,00</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>LP-057637</t>
+          <t>LP-057766</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2711,57 +2729,57 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14281280</v>
+        <v>14277283</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>685412</v>
+        <v>685401</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4711401174</v>
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>4312400046-0324</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DU 685412 Conjunto garras 4,0mm HTT Agu.</t>
+          <t>Base de Medição - conserto</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4 470,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>400</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>LP-057639</t>
+          <t>LP-057762</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2778,57 +2796,57 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14281754</v>
+        <v>14277366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>685411</v>
+        <v>685434</v>
       </c>
       <c r="F36" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4711201792</v>
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4716507918-0035</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DU 685411 Pino de desalimentação U.dura</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1 800,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>400</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>LP-057697</t>
+          <t>LP-057763</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2845,57 +2863,57 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14281764</v>
+        <v>14277411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>685486</v>
+        <v>685434</v>
       </c>
       <c r="F37" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4710101505</v>
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4716507918-0046</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IP 685486 Pinça CIL H ⌀12 Zema 4593</t>
+          <t>Conex</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>5 500,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>400</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>LP-057737</t>
+          <t>LP-057764</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2912,57 +2930,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14281960</v>
+        <v>14277422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>685412</v>
+        <v>685401</v>
       </c>
       <c r="F38" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4718301706</v>
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4716402770-0005</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DU 685412 Anel arrastador Bhamuller agul</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1 100,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>900</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>LP-057634</t>
+          <t>LP-057765</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2979,59 +2997,57 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>12.05.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14281980</v>
+        <v>14278486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>685491</v>
+        <v>685546</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>4712004487_POS 2</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4716404106</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IP 685491 POSIÇÃO 2 FOLHA 3/5 ∅12mm</t>
+          <t>Novo - serie 0009</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1 240,00</t>
+          <t>4 700,00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>LP-057738</t>
+          <t>LP-057731</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3048,57 +3064,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>14.05.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14282011</v>
+        <v>14279605</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>685541</v>
+        <v>685914</v>
       </c>
       <c r="F40" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>4727501442</v>
+        <v>4716512215</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Posição 3</t>
+          <t>Novo - serie 0001</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>4 800,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>300</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>LP-057743</t>
+          <t>LP-057729</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3115,57 +3129,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>14.05.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14282043</v>
+        <v>14279607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>685545</v>
+        <v>685914</v>
       </c>
       <c r="F41" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>4729105151</v>
+        <v>4716512243</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Eletrodo</t>
+          <t>Novos - series 0001 e 0002</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>4 400,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>600</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>LP-057742</t>
+          <t>LP-057730</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3182,57 +3194,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>14.05.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>14282051</v>
+        <v>14279632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>685545</v>
+        <v>685485</v>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>4729104946</v>
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4738360844-0002</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Eletrodo</t>
+          <t>Pino - conserto</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4 400,00</t>
+          <t>3 000,00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>LP-057663</t>
+          <t>LP-057736</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3249,57 +3263,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14282076</v>
+        <v>14280178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>685552</v>
+        <v>685551</v>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
-      </c>
-      <c r="H43" t="n">
-        <v>4729109634</v>
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4715900616-0009</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Posição 2 + 105</t>
+          <t>LS -  conserto</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3 000,00</t>
+          <t>3 400,00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>LP-057667</t>
+          <t>LP-057775</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3316,57 +3332,59 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>19.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14282079</v>
+        <v>14280359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>685557</v>
+        <v>685700</v>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>10</v>
-      </c>
-      <c r="H44" t="n">
-        <v>4710101227</v>
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4714200975-0002</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Garra tucho</t>
+          <t>LG - conserto</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2 100,00</t>
+          <t>1 100,00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>LP-057662</t>
+          <t>LP-057668</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3388,52 +3406,52 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>14282081</v>
+        <v>14281690</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>685553</v>
+        <v>685546</v>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4712003897</v>
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4716510593-0004</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Posição 2</t>
+          <t>LY - conserto</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>3 125,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>500</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>LP-057665</t>
+          <t>LP-057745</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3455,52 +3473,52 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>14282084</v>
+        <v>14281717</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>685552</v>
+        <v>685700</v>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4728701187</v>
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4737990011-0009</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Disco de arraste</t>
+          <t>Prisma  - conserto</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>3 520,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>400</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>LP-057666</t>
+          <t>LP-057700</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3522,52 +3540,52 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14282089</v>
+        <v>14281721</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>685557</v>
+        <v>685700</v>
       </c>
       <c r="F47" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="n">
-        <v>4729110395</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4737990011-0014</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Régua</t>
+          <t>Prisma  - conserto</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>3 300,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>400</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>LP-057664</t>
+          <t>LP-057699</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3584,57 +3602,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.05.2026</t>
+          <t>19.05.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14282497</v>
+        <v>14281900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>685401</v>
+        <v>685551</v>
       </c>
       <c r="F48" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>30</v>
-      </c>
-      <c r="H48" t="n">
-        <v>4729111134</v>
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>4716404958-0007</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Posição 101</t>
+          <t>LX - Conserto</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5 400,00</t>
+          <t>1 500,00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>LP-057816</t>
+          <t>LP-057701</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3651,57 +3671,57 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.05.2026</t>
+          <t>19.05.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>14282522</v>
+        <v>14281911</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>685434</v>
+        <v>685482</v>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>4712004474</v>
+        <v>4716511903</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DU 685434 POSIÇÃO 1 da garra ret.supfina</t>
+          <t>Novo - serie 0005</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1 540,00</t>
+          <t>1 800,00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>LP-057682</t>
+          <t>LP-057746</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3723,50 +3743,52 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14282536</v>
+        <v>14282541</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>685421</v>
+        <v>685551</v>
       </c>
       <c r="F50" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>4729110119</v>
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4716404958-0903</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DU 685421 Conector ∅4/4 (AGIEs)</t>
+          <t>POSIÇÃO 21 - retrabalhar</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>LP-057680</t>
+          <t>LP-057800</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3788,50 +3810,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>14282536</v>
+        <v>14282573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>685421</v>
+        <v>685201</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>4729110120</v>
+        <v>4729106855</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DU 685421 Conector ∅4/6 (AGIEs)</t>
+          <t>Aval. dispos. conf. anexo</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>820</v>
+        <v>600</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>LP-057681</t>
+          <t>LP-057801</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3848,57 +3870,57 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>14282687</v>
+        <v>14283160</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>685702</v>
+        <v>685556</v>
       </c>
       <c r="F52" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CROQUI</t>
+          <t>4716510247-0003</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Garra</t>
+          <t>LY - conserto</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>DOUGLAS</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>LP-057693</t>
+          <t>LP-057802</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3915,59 +3937,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14283005</v>
+        <v>14283946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>685433</v>
+        <v>685700</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MODIF. 0_6328</t>
+          <t>4716509341-0003</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Modif. Lepadora (Base)</t>
+          <t>LY - conserto</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>IAP3CT</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SO/OPM-TS23-BR</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>14 600,00</t>
-        </is>
+          <t>PS/QMM7-CtP</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>600</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>LP-057677</t>
+          <t>LP-057803</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3984,57 +4004,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14283146</v>
+        <v>14287903</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Yesica Gonzalez</t>
+          <t>Rodrigo Melo</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>685485</v>
+        <v>685553</v>
       </c>
       <c r="F54" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>4710200914</v>
+        <v>4738360248</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>IP 685485 Pinça Ø13 CIL P3 (31152/31377)</t>
+          <t>Novo - series 0151 e 0152</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DONI- 2803</t>
+          <t>QMM</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>CtP/TEF11</t>
+          <t>PS/QMM7-CtP</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5 100,00</t>
+          <t>4 000,00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>LP-057750</t>
+          <t>LP-057804</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4043,1417 +4063,6 @@
         </is>
       </c>
       <c r="O54" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>14283153</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>685487</v>
-      </c>
-      <c r="F55" t="n">
-        <v>19</v>
-      </c>
-      <c r="G55" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" t="n">
-        <v>4310200086</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>IP 685587 Pino porta mandril ∅5 CIL A</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>1 800,00</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>LP-057748</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>14283182</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>685401</v>
-      </c>
-      <c r="F56" t="n">
-        <v>19</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" t="n">
-        <v>4711401119</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Jogo de castanha</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>3 510,00</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>LP-057819</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>14283190</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>685401</v>
-      </c>
-      <c r="F57" t="n">
-        <v>19</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>4711500231</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Posição 1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>3 300,00</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>LP-057820</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>14283236</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>685485</v>
-      </c>
-      <c r="F58" t="n">
-        <v>19</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4729401812</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>IP-685485 Bucha de recolhimento CiL P∅12</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>3 240,00</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>LP-057747</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>14283239</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>685434</v>
-      </c>
-      <c r="F59" t="n">
-        <v>19</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" t="n">
-        <v>4729105207</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>DU 685434 Berço retífica de curso acabam</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2 940,00</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>LP-057772</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>14283347</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>685557</v>
-      </c>
-      <c r="F60" t="n">
-        <v>19</v>
-      </c>
-      <c r="G60" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>4711201620</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Posição 1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>3 100,00</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>LP-057810</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>14283349</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>685552</v>
-      </c>
-      <c r="F61" t="n">
-        <v>19</v>
-      </c>
-      <c r="G61" t="n">
-        <v>15</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4728701186</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Posição 7</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>3 750,00</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>LP-057809</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>14283351</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>685552</v>
-      </c>
-      <c r="F62" t="n">
-        <v>19</v>
-      </c>
-      <c r="G62" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" t="n">
-        <v>4728701186</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Posição 3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2 730,00</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>LP-057808</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>14283352</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>685553</v>
-      </c>
-      <c r="F63" t="n">
-        <v>19</v>
-      </c>
-      <c r="G63" t="n">
-        <v>15</v>
-      </c>
-      <c r="H63" t="n">
-        <v>4729106006</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Bujão ZPD</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2 475,00</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>LP-057811</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>14283382</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>685553</v>
-      </c>
-      <c r="F64" t="n">
-        <v>19</v>
-      </c>
-      <c r="G64" t="n">
-        <v>10</v>
-      </c>
-      <c r="H64" t="n">
-        <v>4729109506</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Bujão PLD</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>5 500,00</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>LP-057812</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>14283816</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>685401</v>
-      </c>
-      <c r="F65" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" t="n">
-        <v>4750050008</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Confecção do dispositivo para ECM</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>VIM6CT</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>SO/OPM-TS23-BR</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>960</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>LP-057817</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>14283867</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>685482</v>
-      </c>
-      <c r="F66" t="n">
-        <v>19</v>
-      </c>
-      <c r="G66" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>4702500235</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>IP 685482 Pino de contato EMC Usinag.Mol</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>11 500,00</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>LP-057752</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>14283893</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>685421</v>
-      </c>
-      <c r="F67" t="n">
-        <v>19</v>
-      </c>
-      <c r="G67" t="n">
-        <v>10</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>4729111137_POS 1</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>DU 685421 POSIÇÃO 1 da Bucha roscada</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>1 100,00</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>LP-057769</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>14283921</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>685487</v>
-      </c>
-      <c r="F68" t="n">
-        <v>19</v>
-      </c>
-      <c r="G68" t="n">
-        <v>20</v>
-      </c>
-      <c r="H68" t="n">
-        <v>4729400390</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>IP 685487 Buchas ZL CIL A 7498 (Lino)</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>10 200,00</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>LP-057751</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>14284012</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>685421</v>
-      </c>
-      <c r="F69" t="n">
-        <v>19</v>
-      </c>
-      <c r="G69" t="n">
-        <v>10</v>
-      </c>
-      <c r="H69" t="n">
-        <v>4712003208</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>DU 685421 POSIÇÃO 1 - Terminal em latão</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>1 000,00</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>LP-057770</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>14284025</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>685704</v>
-      </c>
-      <c r="F70" t="n">
-        <v>19</v>
-      </c>
-      <c r="G70" t="n">
-        <v>10</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>4710900876 P3 F4</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>PUNÇÃO  DE PRENSAGEM DO N.R</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>ELCIO STIGAR</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>CtP/MFW13-A</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>6 000,00</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>LP-057806</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>14284029</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>685421</v>
-      </c>
-      <c r="F71" t="n">
-        <v>19</v>
-      </c>
-      <c r="G71" t="n">
-        <v>15</v>
-      </c>
-      <c r="H71" t="n">
-        <v>4712004652</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>DU 685421 POSIÇÃO 2 Pino de fixação AGIE</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>DONI- 2803</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>3 750,00</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>LP-057771</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>14284031</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>685704</v>
-      </c>
-      <c r="F72" t="n">
-        <v>19</v>
-      </c>
-      <c r="G72" t="n">
-        <v>10</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>4729109209 POS01</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>CONE DOS ANEIS DO CORPO, EST10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>ELCIO STIGAR</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>CtP/MFW13-A</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>3 300,00</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>LP-057805</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>22.05.2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>14284036</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>685704</v>
-      </c>
-      <c r="F73" t="n">
-        <v>19</v>
-      </c>
-      <c r="G73" t="n">
-        <v>10</v>
-      </c>
-      <c r="H73" t="n">
-        <v>4728603253</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>CONE VEDAÇÃO V.O.P EST.120</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>ELCIO STIGAR</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>CtP/MFW13-A</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>3 500,00</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>LP-057807</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>23.05.2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>14284438</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>685553</v>
-      </c>
-      <c r="F74" t="n">
-        <v>19</v>
-      </c>
-      <c r="G74" t="n">
-        <v>2</v>
-      </c>
-      <c r="H74" t="n">
-        <v>4729105685</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Cone</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2 960,00</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>LP-057814</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Cadastrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>23.05.2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>14284474</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Yesica Gonzalez</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>685553</v>
-      </c>
-      <c r="F75" t="n">
-        <v>19</v>
-      </c>
-      <c r="G75" t="n">
-        <v>10</v>
-      </c>
-      <c r="H75" t="n">
-        <v>4710900695</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Ponteira</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>DOUGLAS</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>CtP/TEF11</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>1 500,00</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>LP-057813</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Cadastrada</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
         <is>
           <t>Cadastrado</t>
         </is>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Cadastrado</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -832,7 +836,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -897,7 +905,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -962,7 +974,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1027,7 +1043,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1090,7 +1110,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1153,7 +1177,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1216,7 +1244,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1279,7 +1311,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1342,7 +1378,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,7 +1447,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1470,7 +1514,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1533,7 +1581,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1596,7 +1648,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1659,7 +1715,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1722,7 +1782,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1785,7 +1849,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1848,7 +1916,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1911,7 +1983,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1974,7 +2050,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2035,7 +2115,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2098,7 +2182,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2161,7 +2249,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2224,7 +2316,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2289,7 +2385,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2352,7 +2452,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2417,7 +2521,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2480,7 +2588,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2543,7 +2655,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2606,7 +2722,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2669,7 +2789,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2734,7 +2858,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2797,7 +2925,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2860,7 +2992,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2923,7 +3059,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2988,7 +3128,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3051,7 +3195,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3114,7 +3262,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3177,7 +3329,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3240,7 +3396,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3305,7 +3465,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3368,7 +3532,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3431,7 +3599,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3496,7 +3668,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3561,7 +3737,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3626,7 +3806,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3689,7 +3873,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3752,7 +3940,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3815,7 +4007,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3878,7 +4074,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3941,7 +4141,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4004,7 +4208,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4067,7 +4275,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4130,7 +4342,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4193,7 +4409,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4256,7 +4476,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4319,7 +4543,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4380,7 +4608,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4443,7 +4675,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4508,7 +4744,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4571,7 +4811,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924F5B94-CCC7-4930-BAB7-989F6D59B694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0611E39E-5562-4B2A-A2C1-52ECF9960C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="158">
   <si>
     <t>Data</t>
   </si>
@@ -61,433 +61,439 @@
     <t>Elemento PEP</t>
   </si>
   <si>
+    <t>Status CN21</t>
+  </si>
+  <si>
+    <t>Status CJ02</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>24.07.2026</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>4729109899/BB5504</t>
+  </si>
+  <si>
+    <t>Copo expulsor</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>21 250,00</t>
+  </si>
+  <si>
+    <t>LP-058037</t>
+  </si>
+  <si>
+    <t>Erro</t>
+  </si>
+  <si>
+    <t>4729109898/BB8119</t>
+  </si>
+  <si>
+    <t>Disp. BICO</t>
+  </si>
+  <si>
+    <t>3 500,00</t>
+  </si>
+  <si>
+    <t>LP-058038</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>Posição 5</t>
+  </si>
+  <si>
+    <t>8 400,00</t>
+  </si>
+  <si>
+    <t>LP-058040</t>
+  </si>
+  <si>
+    <t>Posição 6</t>
+  </si>
+  <si>
+    <t>11 640,00</t>
+  </si>
+  <si>
+    <t>LP-058039</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>Contra Ponto Garra</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>3 000,00</t>
+  </si>
+  <si>
+    <t>LP-058144</t>
+  </si>
+  <si>
+    <t>Parafuso da Garra</t>
+  </si>
+  <si>
+    <t>3 900,00</t>
+  </si>
+  <si>
+    <t>LP-058137</t>
+  </si>
+  <si>
+    <t>Mordente CR60</t>
+  </si>
+  <si>
+    <t>2 000,00</t>
+  </si>
+  <si>
+    <t>LP-058141</t>
+  </si>
+  <si>
+    <t>Parafuso Trava Rebolo</t>
+  </si>
+  <si>
+    <t>LP-058143</t>
+  </si>
+  <si>
+    <t>Braço Alimentador</t>
+  </si>
+  <si>
+    <t>3 300,00</t>
+  </si>
+  <si>
+    <t>LP-058140</t>
+  </si>
+  <si>
+    <t>LP-058139</t>
+  </si>
+  <si>
+    <t>Fixação do Carregador</t>
+  </si>
+  <si>
+    <t>LP-058142</t>
+  </si>
+  <si>
+    <t>RETIFICAR PRISMA POMBASIC</t>
+  </si>
+  <si>
+    <t>GUILHERME</t>
+  </si>
+  <si>
+    <t>LP-058030</t>
+  </si>
+  <si>
+    <t>01.06.2026</t>
+  </si>
+  <si>
+    <t>31.07.2026</t>
+  </si>
+  <si>
+    <t>IP 685482 Pino de contato ECM usinag.mol</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>6 000,00</t>
+  </si>
+  <si>
+    <t>LP-058100</t>
+  </si>
+  <si>
+    <t>DU 685421 Pino de fixação Q1 AGIEs</t>
+  </si>
+  <si>
+    <t>LP-057923</t>
+  </si>
+  <si>
+    <t>IP 685484 Rebolo borazon Pistão P</t>
+  </si>
+  <si>
+    <t>LP-058111</t>
+  </si>
+  <si>
+    <t>LP-058110</t>
+  </si>
+  <si>
+    <t>LP-058109</t>
+  </si>
+  <si>
+    <t>LP-058108</t>
+  </si>
+  <si>
+    <t>LP-058107</t>
+  </si>
+  <si>
+    <t>LP-058106</t>
+  </si>
+  <si>
+    <t>LP-058105</t>
+  </si>
+  <si>
+    <t>LP-058104</t>
+  </si>
+  <si>
+    <t>LP-058103</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra ponto Pistão P</t>
+  </si>
+  <si>
+    <t>1 980,00</t>
+  </si>
+  <si>
+    <t>LP-058102</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra ponto emparelhamento P</t>
+  </si>
+  <si>
+    <t>LP-058101</t>
+  </si>
+  <si>
+    <t>IP 685481 Chapa de alimentação válvula</t>
+  </si>
+  <si>
+    <t>LP-058117</t>
+  </si>
+  <si>
+    <t>IP 685485 Pinça CIL P7/P8/H ⌀12 Zem 4593</t>
+  </si>
+  <si>
+    <t>4 400,00</t>
+  </si>
+  <si>
+    <t>LP-058099</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t>Posição 2</t>
+  </si>
+  <si>
+    <t>LP-058031</t>
+  </si>
+  <si>
+    <t>Stop Spinner</t>
+  </si>
+  <si>
+    <t>LP-058032</t>
+  </si>
+  <si>
+    <t>4 100,00</t>
+  </si>
+  <si>
+    <t>LP-058035</t>
+  </si>
+  <si>
+    <t>Pino REMAN</t>
+  </si>
+  <si>
+    <t>2 750,00</t>
+  </si>
+  <si>
+    <t>LP-058034</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste cheia U.D</t>
+  </si>
+  <si>
+    <t>4 000,00</t>
+  </si>
+  <si>
+    <t>LP-058041</t>
+  </si>
+  <si>
+    <t>DU 685411 POSIÇÃO 1 da Placa silberhorn</t>
+  </si>
+  <si>
+    <t>2 200,00</t>
+  </si>
+  <si>
+    <t>LP-058042</t>
+  </si>
+  <si>
+    <t>47 120 02 368</t>
+  </si>
+  <si>
+    <t>Manipulador escova MPS</t>
+  </si>
+  <si>
+    <t>JEFFERSON</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>1 600,00</t>
+  </si>
+  <si>
+    <t>LP-058025</t>
+  </si>
+  <si>
+    <t>LP-058024</t>
+  </si>
+  <si>
+    <t>IP 685485 Contra ponto retífica zema P3</t>
+  </si>
+  <si>
+    <t>LP-058116</t>
+  </si>
+  <si>
+    <t>03.06.2026</t>
+  </si>
+  <si>
+    <t>IP 685482 POSIÇÃO 3 do Robo MIKRON</t>
+  </si>
+  <si>
+    <t>2 700,00</t>
+  </si>
+  <si>
+    <t>LP-058118</t>
+  </si>
+  <si>
+    <t>IP 685487 Arruela de vedação emparelha.</t>
+  </si>
+  <si>
+    <t>1 100,00</t>
+  </si>
+  <si>
+    <t>LP-058120</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>Base Retco</t>
+  </si>
+  <si>
+    <t>LP-058121</t>
+  </si>
+  <si>
+    <t>Disp. Nagel</t>
+  </si>
+  <si>
+    <t>LP-058122</t>
+  </si>
+  <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
+    <t>18.09.2026</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>4716403906-0007</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-058158</t>
+  </si>
+  <si>
+    <t>08.06.2026</t>
+  </si>
+  <si>
+    <t>Control Sytstem</t>
+  </si>
+  <si>
+    <t>1 500,00</t>
+  </si>
+  <si>
+    <t>LP-058166</t>
+  </si>
+  <si>
+    <t>LP-058165</t>
+  </si>
+  <si>
+    <t>25.09.2026</t>
+  </si>
+  <si>
+    <t>Novo - Posição 2/1</t>
+  </si>
+  <si>
+    <t>LP-058163</t>
+  </si>
+  <si>
+    <t>4715300761-0013</t>
+  </si>
+  <si>
+    <t>LO - Conserto</t>
+  </si>
+  <si>
+    <t>LP-058157</t>
+  </si>
+  <si>
+    <t>4716403967-0003</t>
+  </si>
+  <si>
+    <t>LP-058156</t>
+  </si>
+  <si>
+    <t>4716406321-0002</t>
+  </si>
+  <si>
+    <t>LP-058154</t>
+  </si>
+  <si>
+    <t>4716508429-0001</t>
+  </si>
+  <si>
+    <t>LY - Conserto</t>
+  </si>
+  <si>
+    <t>LP-058155</t>
+  </si>
+  <si>
+    <t>4716406356-0002</t>
+  </si>
+  <si>
+    <t>LP-058094</t>
+  </si>
+  <si>
+    <t>4716405569-0002</t>
+  </si>
+  <si>
+    <t>1 200,00</t>
+  </si>
+  <si>
+    <t>LP-058153</t>
+  </si>
+  <si>
     <t>26.05.2026</t>
   </si>
   <si>
-    <t>24.07.2026</t>
-  </si>
-  <si>
-    <t>Yesica Gonzalez</t>
-  </si>
-  <si>
     <t>4711401162_1 JOGO</t>
   </si>
   <si>
     <t>DU 685411 Castanha da placa Benzinger UD</t>
   </si>
   <si>
-    <t>DONI- 2803</t>
-  </si>
-  <si>
-    <t>CtP/TEF11</t>
-  </si>
-  <si>
     <t>2 310,00</t>
   </si>
   <si>
-    <t>LP058036</t>
-  </si>
-  <si>
-    <t>27.05.2026</t>
-  </si>
-  <si>
-    <t>4729109899/BB5504</t>
-  </si>
-  <si>
-    <t>Copo expulsor</t>
-  </si>
-  <si>
-    <t>DOUGLAS</t>
-  </si>
-  <si>
-    <t>21 250,00</t>
-  </si>
-  <si>
-    <t>LP058037</t>
-  </si>
-  <si>
-    <t>4729109898/BB8119</t>
-  </si>
-  <si>
-    <t>Disp. BICO</t>
-  </si>
-  <si>
-    <t>3 500,00</t>
-  </si>
-  <si>
-    <t>LP058038</t>
-  </si>
-  <si>
-    <t>29.05.2026</t>
-  </si>
-  <si>
-    <t>Posição 5</t>
-  </si>
-  <si>
-    <t>8 400,00</t>
-  </si>
-  <si>
-    <t>LP058040</t>
-  </si>
-  <si>
-    <t>Posição 6</t>
-  </si>
-  <si>
-    <t>11 640,00</t>
-  </si>
-  <si>
-    <t>LP058039</t>
-  </si>
-  <si>
-    <t>30.05.2026</t>
-  </si>
-  <si>
-    <t>Contra Ponto Garra</t>
-  </si>
-  <si>
-    <t>FERNANDA A</t>
-  </si>
-  <si>
-    <t>3 000,00</t>
-  </si>
-  <si>
-    <t>LP058144</t>
-  </si>
-  <si>
-    <t>Parafuso da Garra</t>
-  </si>
-  <si>
-    <t>3 900,00</t>
-  </si>
-  <si>
-    <t>LP058137</t>
-  </si>
-  <si>
-    <t>Mordente CR60</t>
-  </si>
-  <si>
-    <t>2 000,00</t>
-  </si>
-  <si>
-    <t>LP058141</t>
-  </si>
-  <si>
-    <t>Parafuso Trava Rebolo</t>
-  </si>
-  <si>
-    <t>LP058143</t>
-  </si>
-  <si>
-    <t>Braço Alimentador</t>
-  </si>
-  <si>
-    <t>3 300,00</t>
-  </si>
-  <si>
-    <t>LP058140</t>
-  </si>
-  <si>
-    <t>LP058139</t>
-  </si>
-  <si>
-    <t>Fixação do Carregador</t>
-  </si>
-  <si>
-    <t>LP058142</t>
-  </si>
-  <si>
-    <t>RETIFICAR PRISMA POMBASIC</t>
-  </si>
-  <si>
-    <t>GUILHERME</t>
-  </si>
-  <si>
-    <t>LP058030</t>
-  </si>
-  <si>
-    <t>01.06.2026</t>
-  </si>
-  <si>
-    <t>31.07.2026</t>
-  </si>
-  <si>
-    <t>IP 685482 Pino de contato ECM usinag.mol</t>
-  </si>
-  <si>
-    <t>6 000,00</t>
-  </si>
-  <si>
-    <t>LP058100</t>
-  </si>
-  <si>
-    <t>DU 685421 Pino de fixação Q1 AGIEs</t>
-  </si>
-  <si>
-    <t>LP057923</t>
-  </si>
-  <si>
-    <t>IP 685484 Rebolo borazon Pistão P</t>
-  </si>
-  <si>
-    <t>LP058111</t>
-  </si>
-  <si>
-    <t>LP058110</t>
-  </si>
-  <si>
-    <t>LP058109</t>
-  </si>
-  <si>
-    <t>LP058108</t>
-  </si>
-  <si>
-    <t>LP058107</t>
-  </si>
-  <si>
-    <t>LP058106</t>
-  </si>
-  <si>
-    <t>LP058105</t>
-  </si>
-  <si>
-    <t>LP058104</t>
-  </si>
-  <si>
-    <t>LP058103</t>
-  </si>
-  <si>
-    <t>IP 685484 Contra ponto Pistão P</t>
-  </si>
-  <si>
-    <t>1 980,00</t>
-  </si>
-  <si>
-    <t>LP058102</t>
-  </si>
-  <si>
-    <t>IP 685484 Contra ponto emparelhamento P</t>
-  </si>
-  <si>
-    <t>LP058101</t>
-  </si>
-  <si>
-    <t>IP 685481 Chapa de alimentação válvula</t>
-  </si>
-  <si>
-    <t>LP058117</t>
-  </si>
-  <si>
-    <t>IP 685485 Pinça CIL P7/P8/H ⌀12 Zem 4593</t>
-  </si>
-  <si>
-    <t>4 400,00</t>
-  </si>
-  <si>
-    <t>LP058099</t>
-  </si>
-  <si>
-    <t>02.06.2026</t>
-  </si>
-  <si>
-    <t>Posição 2</t>
-  </si>
-  <si>
-    <t>LP058031</t>
-  </si>
-  <si>
-    <t>Stop Spinner</t>
-  </si>
-  <si>
-    <t>LP058032</t>
-  </si>
-  <si>
-    <t>4 100,00</t>
-  </si>
-  <si>
-    <t>LP058035</t>
-  </si>
-  <si>
-    <t>Pino REMAN</t>
-  </si>
-  <si>
-    <t>2 750,00</t>
-  </si>
-  <si>
-    <t>LP058034</t>
-  </si>
-  <si>
-    <t>DU 685411 Contra ponto Haste cheia U.D</t>
-  </si>
-  <si>
-    <t>4 000,00</t>
-  </si>
-  <si>
-    <t>LP058041</t>
-  </si>
-  <si>
-    <t>DU 685411 POSIÇÃO 1 da Placa silberhorn</t>
-  </si>
-  <si>
-    <t>2 200,00</t>
-  </si>
-  <si>
-    <t>LP058042</t>
-  </si>
-  <si>
-    <t>47 120 02 368</t>
-  </si>
-  <si>
-    <t>Manipulador escova MPS</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS23-BR</t>
-  </si>
-  <si>
-    <t>1 600,00</t>
-  </si>
-  <si>
-    <t>LP058025</t>
-  </si>
-  <si>
-    <t>LP058024</t>
-  </si>
-  <si>
-    <t>IP 685485 Contra ponto retífica zema P3</t>
-  </si>
-  <si>
-    <t>LP058116</t>
-  </si>
-  <si>
-    <t>03.06.2026</t>
-  </si>
-  <si>
-    <t>IP 685482 POSIÇÃO 3 do Robo MIKRON</t>
-  </si>
-  <si>
-    <t>2 700,00</t>
-  </si>
-  <si>
-    <t>LP058118</t>
-  </si>
-  <si>
-    <t>IP 685487 Arruela de vedação emparelha.</t>
-  </si>
-  <si>
-    <t>1 100,00</t>
-  </si>
-  <si>
-    <t>LP058120</t>
-  </si>
-  <si>
-    <t>05.06.2026</t>
-  </si>
-  <si>
-    <t>Base Retco</t>
-  </si>
-  <si>
-    <t>LP058121</t>
-  </si>
-  <si>
-    <t>Disp. Nagel</t>
-  </si>
-  <si>
-    <t>LP058122</t>
-  </si>
-  <si>
-    <t>09.06.2026</t>
-  </si>
-  <si>
-    <t>18.09.2026</t>
-  </si>
-  <si>
-    <t>Rodrigo Melo</t>
-  </si>
-  <si>
-    <t>4716403906-0007</t>
-  </si>
-  <si>
-    <t>LX - Conserto</t>
-  </si>
-  <si>
-    <t>PS/QMM7-CtP</t>
-  </si>
-  <si>
-    <t>LP058158</t>
-  </si>
-  <si>
-    <t>08.06.2026</t>
-  </si>
-  <si>
-    <t>Control Sytstem</t>
-  </si>
-  <si>
-    <t>1 500,00</t>
-  </si>
-  <si>
-    <t>LP058166</t>
-  </si>
-  <si>
-    <t>LP058165</t>
-  </si>
-  <si>
-    <t>25.09.2026</t>
-  </si>
-  <si>
-    <t>Novo - Posição 2/1</t>
-  </si>
-  <si>
-    <t>LP058163</t>
-  </si>
-  <si>
-    <t>4715300761-0013</t>
-  </si>
-  <si>
-    <t>LO - Conserto</t>
-  </si>
-  <si>
-    <t>LP058157</t>
-  </si>
-  <si>
-    <t>4716403967-0003</t>
-  </si>
-  <si>
-    <t>LP058156</t>
-  </si>
-  <si>
-    <t>4716406321-0002</t>
-  </si>
-  <si>
-    <t>LP058154</t>
-  </si>
-  <si>
-    <t>4716508429-0001</t>
-  </si>
-  <si>
-    <t>LY - Conserto</t>
-  </si>
-  <si>
-    <t>LP058155</t>
-  </si>
-  <si>
-    <t>4716406356-0002</t>
-  </si>
-  <si>
-    <t>LP058094</t>
-  </si>
-  <si>
-    <t>4716405569-0002</t>
-  </si>
-  <si>
-    <t>1 200,00</t>
-  </si>
-  <si>
-    <t>LP058153</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>LP-058036</t>
   </si>
 </sst>
 </file>
@@ -543,12 +549,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -853,13 +856,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -900,77 +900,65 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>14285730</v>
+        <v>14287660</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>685411</v>
+        <v>685401</v>
       </c>
       <c r="F2">
         <v>19</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2">
+        <v>4750050007</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3">
-        <v>14286301</v>
+        <v>14287661</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>685401</v>
@@ -979,162 +967,162 @@
         <v>19</v>
       </c>
       <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>4750050007</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>14286302</v>
+        <v>14288202</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>685401</v>
+        <v>685615</v>
       </c>
       <c r="F4">
         <v>19</v>
       </c>
       <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>4710800250</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>14287660</v>
+        <v>14288203</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>685401</v>
+        <v>685615</v>
       </c>
       <c r="F5">
         <v>19</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>4750050007</v>
+        <v>4711201655</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>14287661</v>
+        <v>14288205</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>685401</v>
+        <v>685615</v>
       </c>
       <c r="F6">
         <v>19</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>4750050007</v>
+        <v>4712002801</v>
       </c>
       <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>14288202</v>
+        <v>14288206</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>685615</v>
@@ -1143,39 +1131,39 @@
         <v>19</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>4710800250</v>
+        <v>4712004545</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <v>450</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>14288203</v>
+        <v>14288216</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>685615</v>
@@ -1184,39 +1172,39 @@
         <v>19</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>4711201655</v>
+        <v>4728701255</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>14288205</v>
+        <v>14288217</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>685615</v>
@@ -1225,39 +1213,39 @@
         <v>19</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>4712002801</v>
+        <v>4728701255</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>14288206</v>
+        <v>14288218</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>685615</v>
@@ -1266,282 +1254,282 @@
         <v>19</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>4712004545</v>
+        <v>4729108727</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10">
-        <v>450</v>
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>14288216</v>
+        <v>14288241</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11">
-        <v>685615</v>
+        <v>685664</v>
       </c>
       <c r="F11">
         <v>19</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>4728701255</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" t="s">
-        <v>53</v>
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <v>500</v>
       </c>
       <c r="M11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C12">
-        <v>14288217</v>
+        <v>14288680</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <v>685615</v>
+        <v>685482</v>
       </c>
       <c r="F12">
         <v>19</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>4728701255</v>
+        <v>4712000573</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C13">
-        <v>14288218</v>
+        <v>14288708</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13">
-        <v>685615</v>
+        <v>685421</v>
       </c>
       <c r="F13">
         <v>19</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>4729108727</v>
+        <v>4730502592</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C14">
-        <v>14288241</v>
+        <v>14288727</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>685664</v>
+        <v>685484</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>4304800434</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14">
+        <v>550</v>
+      </c>
+      <c r="M14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15">
+        <v>14288727</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>685484</v>
+      </c>
+      <c r="F15">
+        <v>37</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="I14" t="s">
+      <c r="H15">
+        <v>4719270019</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>110</v>
+      </c>
+      <c r="M15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>58</v>
       </c>
-      <c r="J14" t="s">
+      <c r="B16" t="s">
         <v>59</v>
       </c>
-      <c r="K14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14">
-        <v>500</v>
-      </c>
-      <c r="M14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15">
-        <v>14288680</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15">
-        <v>685482</v>
-      </c>
-      <c r="F15">
-        <v>19</v>
-      </c>
-      <c r="G15">
-        <v>4</v>
-      </c>
-      <c r="H15">
-        <v>4712000573</v>
-      </c>
-      <c r="I15" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
       <c r="C16">
-        <v>14288708</v>
+        <v>14288727</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>685421</v>
+        <v>685484</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>4730502592</v>
+        <v>4719266062</v>
       </c>
       <c r="I16" t="s">
         <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>260</v>
       </c>
       <c r="M16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17">
         <v>14288727</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>685484</v>
@@ -1550,39 +1538,39 @@
         <v>37</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>4304800434</v>
+        <v>4719266004</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L17">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>14288727</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>685484</v>
@@ -1591,39 +1579,39 @@
         <v>37</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>4719270019</v>
+        <v>4719266003</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L18">
-        <v>110</v>
+        <v>440</v>
       </c>
       <c r="M18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>14288727</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>685484</v>
@@ -1632,39 +1620,39 @@
         <v>37</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>4719266062</v>
+        <v>4304800253</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L19">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="M19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>14288727</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>685484</v>
@@ -1676,36 +1664,36 @@
         <v>2</v>
       </c>
       <c r="H20">
-        <v>4719266004</v>
+        <v>4304800227</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L20">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="M20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>14288727</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>685484</v>
@@ -1714,39 +1702,39 @@
         <v>37</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>4719266003</v>
+        <v>4704800267</v>
       </c>
       <c r="I21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L21">
-        <v>440</v>
+        <v>660</v>
       </c>
       <c r="M21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22">
         <v>14288727</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>685484</v>
@@ -1758,531 +1746,531 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>4304800253</v>
+        <v>4304800281</v>
       </c>
       <c r="I22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L22">
         <v>130</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>14288727</v>
+        <v>14288771</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>685484</v>
       </c>
       <c r="F23">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>4304800227</v>
+        <v>4710800168</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L23">
-        <v>260</v>
+        <v>21</v>
+      </c>
+      <c r="L23" t="s">
+        <v>77</v>
       </c>
       <c r="M23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>14288727</v>
+        <v>14288771</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>685484</v>
       </c>
       <c r="F24">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>4704800267</v>
+        <v>4310800263</v>
       </c>
       <c r="I24" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24">
-        <v>660</v>
+        <v>21</v>
+      </c>
+      <c r="L24" t="s">
+        <v>77</v>
       </c>
       <c r="M24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25">
+        <v>14288844</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <v>685481</v>
+      </c>
+      <c r="F25">
+        <v>20</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>4729108742</v>
+      </c>
+      <c r="I25" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" t="s">
         <v>61</v>
       </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25">
-        <v>14288727</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25">
-        <v>685484</v>
-      </c>
-      <c r="F25">
-        <v>37</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>4304800281</v>
-      </c>
-      <c r="I25" t="s">
-        <v>68</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
-      </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L25">
-        <v>130</v>
+        <v>840</v>
       </c>
       <c r="M25" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26">
+        <v>14288851</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26">
+        <v>685486</v>
+      </c>
+      <c r="F26">
+        <v>19</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>4710101560</v>
+      </c>
+      <c r="I26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26">
-        <v>14288771</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26">
-        <v>685484</v>
-      </c>
-      <c r="F26">
-        <v>20</v>
-      </c>
-      <c r="G26">
-        <v>3</v>
-      </c>
-      <c r="H26">
-        <v>4710800168</v>
-      </c>
-      <c r="I26" t="s">
-        <v>78</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>14288771</v>
+        <v>14289300</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>685484</v>
+        <v>685554</v>
       </c>
       <c r="F27">
+        <v>19</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>4729110946</v>
+      </c>
+      <c r="I27" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" t="s">
         <v>20</v>
       </c>
-      <c r="G27">
-        <v>3</v>
-      </c>
-      <c r="H27">
-        <v>4310800263</v>
-      </c>
-      <c r="I27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
-      </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M27" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28">
-        <v>14288844</v>
+        <v>14289308</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>685481</v>
+        <v>685552</v>
       </c>
       <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>4712001868</v>
+      </c>
+      <c r="I28" t="s">
+        <v>89</v>
+      </c>
+      <c r="J28" t="s">
         <v>20</v>
       </c>
-      <c r="G28">
-        <v>3</v>
-      </c>
-      <c r="H28">
-        <v>4729108742</v>
-      </c>
-      <c r="I28" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" t="s">
-        <v>18</v>
-      </c>
       <c r="K28" t="s">
-        <v>19</v>
-      </c>
-      <c r="L28">
-        <v>840</v>
+        <v>21</v>
+      </c>
+      <c r="L28" t="s">
+        <v>84</v>
       </c>
       <c r="M28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29">
-        <v>14288851</v>
+        <v>14289319</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>685486</v>
+        <v>685555</v>
       </c>
       <c r="F29">
         <v>19</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>4710101560</v>
+        <v>4729110874</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="M29" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C30">
-        <v>14289300</v>
+        <v>14289355</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>685554</v>
+        <v>685555</v>
       </c>
       <c r="F30">
         <v>19</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>4729110946</v>
+        <v>4728602393</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C31">
-        <v>14289308</v>
+        <v>14289473</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>685552</v>
+        <v>685411</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>4712001868</v>
+        <v>4710800193</v>
       </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J31" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C32">
-        <v>14289319</v>
+        <v>14289486</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>685555</v>
+        <v>685411</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>4729110874</v>
+        <v>4729105567</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33">
-        <v>14289355</v>
+        <v>14289509</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>685555</v>
+        <v>685660</v>
       </c>
       <c r="F33">
         <v>19</v>
       </c>
       <c r="G33">
-        <v>5</v>
-      </c>
-      <c r="H33">
-        <v>4728602393</v>
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>102</v>
       </c>
       <c r="I33" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J33" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C34">
-        <v>14289473</v>
+        <v>14289589</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>685411</v>
+        <v>685660</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>4710800193</v>
+        <v>4712002369</v>
       </c>
       <c r="I34" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="M34" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C35">
-        <v>14289486</v>
+        <v>14289613</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>685411</v>
+        <v>685485</v>
       </c>
       <c r="F35">
         <v>20</v>
@@ -2291,162 +2279,162 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>4729105567</v>
+        <v>4718301582</v>
       </c>
       <c r="I35" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="K35" t="s">
-        <v>19</v>
-      </c>
-      <c r="L35" t="s">
-        <v>102</v>
+        <v>21</v>
+      </c>
+      <c r="L35">
+        <v>660</v>
       </c>
       <c r="M35" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C36">
-        <v>14289509</v>
+        <v>14289981</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>685660</v>
+        <v>685482</v>
       </c>
       <c r="F36">
         <v>19</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="s">
-        <v>104</v>
+        <v>2</v>
+      </c>
+      <c r="H36">
+        <v>4680300012</v>
       </c>
       <c r="I36" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="J36" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="K36" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="M36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C37">
-        <v>14289589</v>
+        <v>14290033</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>685660</v>
+        <v>685487</v>
       </c>
       <c r="F37">
         <v>19</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H37">
-        <v>4712002369</v>
+        <v>4705402984</v>
       </c>
       <c r="I37" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J37" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="K37" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M37" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C38">
-        <v>14289613</v>
+        <v>14290638</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E38">
-        <v>685485</v>
+        <v>685541</v>
       </c>
       <c r="F38">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>4727501584</v>
+      </c>
+      <c r="I38" t="s">
+        <v>119</v>
+      </c>
+      <c r="J38" t="s">
         <v>20</v>
       </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <v>4718301582</v>
-      </c>
-      <c r="I38" t="s">
-        <v>111</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
       <c r="K38" t="s">
-        <v>19</v>
-      </c>
-      <c r="L38">
-        <v>660</v>
+        <v>21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>45</v>
       </c>
       <c r="M38" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C39">
-        <v>14289981</v>
+        <v>14290641</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E39">
-        <v>685482</v>
+        <v>685541</v>
       </c>
       <c r="F39">
         <v>19</v>
@@ -2455,162 +2443,162 @@
         <v>2</v>
       </c>
       <c r="H39">
-        <v>4680300012</v>
+        <v>4727501154</v>
       </c>
       <c r="I39" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
-      </c>
-      <c r="L39" t="s">
-        <v>115</v>
+        <v>21</v>
+      </c>
+      <c r="L39">
+        <v>400</v>
       </c>
       <c r="M39" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C40">
-        <v>14290033</v>
+        <v>14291808</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="E40">
-        <v>685487</v>
+        <v>685551</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>10</v>
-      </c>
-      <c r="H40">
-        <v>4705402984</v>
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>126</v>
       </c>
       <c r="I40" t="s">
-        <v>117</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
+        <v>127</v>
+      </c>
+      <c r="J40">
+        <v>400</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
-      </c>
-      <c r="L40" t="s">
-        <v>118</v>
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>400</v>
       </c>
       <c r="M40" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C41">
-        <v>14290638</v>
+        <v>14291326</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="E41">
-        <v>685541</v>
+        <v>685411</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H41">
-        <v>4727501584</v>
+        <v>4716508124</v>
       </c>
       <c r="I41" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J41" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="L41" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="M41" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C42">
-        <v>14290641</v>
+        <v>14291320</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="E42">
-        <v>685541</v>
+        <v>685411</v>
       </c>
       <c r="F42">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H42">
-        <v>4727501154</v>
+        <v>4716508123</v>
       </c>
       <c r="I42" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J42" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42">
-        <v>400</v>
+        <v>128</v>
+      </c>
+      <c r="L42" t="s">
+        <v>132</v>
       </c>
       <c r="M42" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43">
+        <v>14291186</v>
+      </c>
+      <c r="D43" t="s">
         <v>125</v>
       </c>
-      <c r="B43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43">
-        <v>14291808</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
       <c r="E43">
-        <v>685551</v>
+        <v>685421</v>
       </c>
       <c r="F43">
         <v>4</v>
@@ -2618,122 +2606,122 @@
       <c r="G43">
         <v>1</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43">
+        <v>4716512092</v>
+      </c>
+      <c r="I43" t="s">
+        <v>136</v>
+      </c>
+      <c r="J43" t="s">
+        <v>116</v>
+      </c>
+      <c r="K43" t="s">
         <v>128</v>
       </c>
-      <c r="I43" t="s">
-        <v>129</v>
-      </c>
-      <c r="J43">
-        <v>400</v>
-      </c>
-      <c r="K43" t="s">
-        <v>130</v>
-      </c>
-      <c r="L43">
-        <v>400</v>
+      <c r="L43" t="s">
+        <v>116</v>
       </c>
       <c r="M43" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C44">
-        <v>14291326</v>
+        <v>14291124</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E44">
-        <v>685411</v>
+        <v>685551</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
       <c r="G44">
-        <v>61</v>
-      </c>
-      <c r="H44">
-        <v>4716508124</v>
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>138</v>
       </c>
       <c r="I44" t="s">
-        <v>133</v>
-      </c>
-      <c r="J44" t="s">
-        <v>134</v>
+        <v>139</v>
+      </c>
+      <c r="J44">
+        <v>400</v>
       </c>
       <c r="K44" t="s">
-        <v>130</v>
-      </c>
-      <c r="L44" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="L44">
+        <v>400</v>
       </c>
       <c r="M44" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C45">
-        <v>14291320</v>
+        <v>14291120</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E45">
-        <v>685411</v>
+        <v>685554</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45">
-        <v>61</v>
-      </c>
-      <c r="H45">
-        <v>4716508123</v>
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>141</v>
       </c>
       <c r="I45" t="s">
-        <v>133</v>
-      </c>
-      <c r="J45" t="s">
-        <v>134</v>
+        <v>127</v>
+      </c>
+      <c r="J45">
+        <v>500</v>
       </c>
       <c r="K45" t="s">
-        <v>130</v>
-      </c>
-      <c r="L45" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="L45">
+        <v>500</v>
       </c>
       <c r="M45" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C46">
-        <v>14291186</v>
+        <v>14291099</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E46">
-        <v>685421</v>
+        <v>685705</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -2741,40 +2729,40 @@
       <c r="G46">
         <v>1</v>
       </c>
-      <c r="H46">
-        <v>4716512092</v>
+      <c r="H46" t="s">
+        <v>143</v>
       </c>
       <c r="I46" t="s">
-        <v>138</v>
-      </c>
-      <c r="J46" t="s">
-        <v>118</v>
+        <v>127</v>
+      </c>
+      <c r="J46">
+        <v>400</v>
       </c>
       <c r="K46" t="s">
-        <v>130</v>
-      </c>
-      <c r="L46" t="s">
-        <v>118</v>
+        <v>128</v>
+      </c>
+      <c r="L46">
+        <v>400</v>
       </c>
       <c r="M46" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47">
-        <v>14291124</v>
+        <v>14291096</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E47">
-        <v>685551</v>
+        <v>685554</v>
       </c>
       <c r="F47">
         <v>4</v>
@@ -2783,39 +2771,39 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J47">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L47">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M47" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C48">
-        <v>14291120</v>
+        <v>14291025</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48">
-        <v>685554</v>
+        <v>685482</v>
       </c>
       <c r="F48">
         <v>4</v>
@@ -2824,39 +2812,39 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J48">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="K48" t="s">
+        <v>128</v>
+      </c>
+      <c r="L48">
+        <v>900</v>
+      </c>
+      <c r="M48" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>130</v>
       </c>
-      <c r="L48">
-        <v>500</v>
-      </c>
-      <c r="M48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>132</v>
-      </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C49">
-        <v>14291099</v>
+        <v>14291017</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E49">
-        <v>685705</v>
+        <v>685700</v>
       </c>
       <c r="F49">
         <v>4</v>
@@ -2865,145 +2853,151 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I49" t="s">
-        <v>129</v>
-      </c>
-      <c r="J49">
-        <v>400</v>
+        <v>127</v>
+      </c>
+      <c r="J49" t="s">
+        <v>151</v>
       </c>
       <c r="K49" t="s">
-        <v>130</v>
-      </c>
-      <c r="L49">
-        <v>400</v>
+        <v>128</v>
+      </c>
+      <c r="L49" t="s">
+        <v>151</v>
       </c>
       <c r="M49" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="C50">
-        <v>14291096</v>
+        <v>14285730</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="E50">
-        <v>685554</v>
+        <v>685411</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I50" t="s">
-        <v>148</v>
-      </c>
-      <c r="J50">
-        <v>500</v>
+        <v>155</v>
+      </c>
+      <c r="J50" t="s">
+        <v>61</v>
       </c>
       <c r="K50" t="s">
-        <v>130</v>
-      </c>
-      <c r="L50">
-        <v>500</v>
+        <v>21</v>
+      </c>
+      <c r="L50" t="s">
+        <v>156</v>
       </c>
       <c r="M50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="O50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="C51">
-        <v>14291025</v>
+        <v>14286301</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="E51">
-        <v>685482</v>
+        <v>685401</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>129</v>
-      </c>
-      <c r="J51">
-        <v>900</v>
+        <v>19</v>
+      </c>
+      <c r="J51" t="s">
+        <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>130</v>
-      </c>
-      <c r="L51">
-        <v>900</v>
+        <v>21</v>
+      </c>
+      <c r="L51" t="s">
+        <v>22</v>
       </c>
       <c r="M51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="O51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="C52">
-        <v>14291017</v>
+        <v>14286302</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="E52">
-        <v>685700</v>
+        <v>685401</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H52" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="I52" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="L52" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="M52" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -1,117 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A501F3C-2869-4860-BF70-A4560A1A5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Prazo Final</t>
-  </si>
-  <si>
-    <t>Nota PM</t>
-  </si>
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Objeto de Liquidação</t>
-  </si>
-  <si>
-    <t>Esquema de Alocação</t>
-  </si>
-  <si>
-    <t>Quantidade</t>
-  </si>
-  <si>
-    <t>Part Number</t>
-  </si>
-  <si>
-    <t>Denominação</t>
-  </si>
-  <si>
-    <t>Entregar para</t>
-  </si>
-  <si>
-    <t>Departamento Emissor</t>
-  </si>
-  <si>
-    <t>Custo estimado</t>
-  </si>
-  <si>
-    <t>Elemento PEP</t>
-  </si>
-  <si>
-    <t>Status CJ02</t>
-  </si>
-  <si>
-    <t>Status CN21</t>
-  </si>
-  <si>
-    <t>Yesica Gonzalez</t>
-  </si>
-  <si>
-    <t>CtP/TEF11</t>
-  </si>
-  <si>
-    <t>DONI- 2803</t>
-  </si>
-  <si>
-    <t>4 400,00</t>
-  </si>
-  <si>
-    <t>DU 685411 Pino Hommel forma externa</t>
-  </si>
-  <si>
-    <t>21.08.2026</t>
-  </si>
-  <si>
-    <t>25.06.2026</t>
-  </si>
-  <si>
-    <t>LP-058552</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -126,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -450,113 +420,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Prazo Final</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nota PM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Objeto de Liquidação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Esquema de Alocação</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Denominação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Entregar para</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Departamento Emissor</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Custo estimado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento PEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Status CJ02</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Status CN21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14300527</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>685411</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>14300527</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2">
-        <v>685411</v>
-      </c>
-      <c r="F2">
-        <v>19</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>4738360936</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DU 685411 Pino Hommel forma externa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DONI- 2803</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CtP/TEF11</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4 400,00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LP-058552</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D6692A-6F54-4866-B287-C828981813B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8816ECB-1245-4229-BF50-F4FABB75FB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="159">
   <si>
     <t>Data</t>
   </si>
@@ -67,370 +67,355 @@
     <t>Status CN21</t>
   </si>
   <si>
-    <t>30.01.2026</t>
+    <t>25.02.2026</t>
+  </si>
+  <si>
+    <t>Renato Meira</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>03.02.2026</t>
+  </si>
+  <si>
+    <t>685050</t>
+  </si>
+  <si>
+    <t>NORMA E DESENHO</t>
+  </si>
+  <si>
+    <t>Norma e Desenho</t>
+  </si>
+  <si>
+    <t>JULIANA MELO</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-055857</t>
+  </si>
+  <si>
+    <t>21.03.2026</t>
+  </si>
+  <si>
+    <t>Diego Vieira</t>
+  </si>
+  <si>
+    <t>685072</t>
+  </si>
+  <si>
+    <t>4729111575</t>
+  </si>
+  <si>
+    <t>Alterar desenho dispositivo</t>
+  </si>
+  <si>
+    <t>BRITO</t>
+  </si>
+  <si>
+    <t>CtP/COS-PMO</t>
+  </si>
+  <si>
+    <t>LP-056019</t>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t>30.03.2026</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Buchas de Usinagem ECM</t>
+  </si>
+  <si>
+    <t>VIM6CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE21</t>
+  </si>
+  <si>
+    <t>LP-055648</t>
+  </si>
+  <si>
+    <t>11.03.2026</t>
+  </si>
+  <si>
+    <t>02.04.2026</t>
+  </si>
+  <si>
+    <t>685122</t>
+  </si>
+  <si>
+    <t>Parafuso pinças Nakamura</t>
+  </si>
+  <si>
+    <t>BRA4CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE11</t>
+  </si>
+  <si>
+    <t>LP-056232</t>
+  </si>
+  <si>
+    <t>12.03.2026</t>
+  </si>
+  <si>
+    <t>08.04.2026</t>
+  </si>
+  <si>
+    <t>GARRA 24 E 25</t>
+  </si>
+  <si>
+    <t>Garra HTT</t>
+  </si>
+  <si>
+    <t>LP-056376</t>
+  </si>
+  <si>
+    <t>GARRA ROBÔ</t>
+  </si>
+  <si>
+    <t>LP-056375</t>
+  </si>
+  <si>
+    <t>23.03.2026</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>4729107175</t>
+  </si>
+  <si>
+    <t>Sacador de corpo porta eletrodo</t>
+  </si>
+  <si>
+    <t>LP-056266</t>
+  </si>
+  <si>
+    <t>27.03.2026</t>
+  </si>
+  <si>
+    <t>11.04.2026</t>
+  </si>
+  <si>
+    <t>685008</t>
+  </si>
+  <si>
+    <t>4727501901</t>
+  </si>
+  <si>
+    <t>Flange HPC</t>
+  </si>
+  <si>
+    <t>MFA9CT</t>
+  </si>
+  <si>
+    <t>LP-056311</t>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+  </si>
+  <si>
+    <t>4727500383</t>
+  </si>
+  <si>
+    <t>Contraponto do Romi do HPC</t>
+  </si>
+  <si>
+    <t>LP-056310</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>Rafael Nunes</t>
+  </si>
+  <si>
+    <t>685546</t>
+  </si>
+  <si>
+    <t>TPM - SUPORTE DE CALIBRADOR USM STH</t>
+  </si>
+  <si>
+    <t>STEPHANY</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-B</t>
+  </si>
+  <si>
+    <t>LP-057518</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>31.12.2026</t>
+  </si>
+  <si>
+    <t>Vitor Kostanecki</t>
+  </si>
+  <si>
+    <t>LP-007619-04-22</t>
+  </si>
+  <si>
+    <t>Desenho p/ retrabalho altura do suporte</t>
+  </si>
+  <si>
+    <t>JOSIANE OLIV</t>
+  </si>
+  <si>
+    <t>LP-057834</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>15.06.2026</t>
+  </si>
+  <si>
+    <t>Rafael Lima</t>
+  </si>
+  <si>
+    <t>685421</t>
+  </si>
+  <si>
+    <t>IMPRESSÃO 3D</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO MICROMETRO A LASER (ALEXANDR</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-058173</t>
+  </si>
+  <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
+    <t>29.06.2026</t>
+  </si>
+  <si>
+    <t>685664</t>
+  </si>
+  <si>
+    <t>SUPORTE REBOLO - 5S</t>
+  </si>
+  <si>
+    <t>GUSTAVO W.</t>
+  </si>
+  <si>
+    <t>CtP/ETS</t>
+  </si>
+  <si>
+    <t>LP-057978</t>
+  </si>
+  <si>
+    <t>03.07.2025</t>
+  </si>
+  <si>
+    <t>BM-00040171_002_00000015</t>
+  </si>
+  <si>
+    <t>DISP. AUX. PARA MEDIÇÃO INDUTÂNCIA - GM</t>
+  </si>
+  <si>
+    <t>RAIRA TOPA</t>
+  </si>
+  <si>
+    <t>PS-DC/ENP1-LA</t>
+  </si>
+  <si>
+    <t>LP-058494</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>25.06.2026</t>
+  </si>
+  <si>
+    <t>FABRICAÇÃO PROTOTIPO BATOQUE PRA BUCHA</t>
+  </si>
+  <si>
+    <t>BRUNO ARAUJO</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>LP-058092</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>26.06.2026</t>
+  </si>
+  <si>
+    <t>FABRICAÇÃO PROTOTIPO BUCHA</t>
+  </si>
+  <si>
+    <t>LP-058172</t>
+  </si>
+  <si>
+    <t>01.07.2026</t>
+  </si>
+  <si>
+    <t>685484</t>
+  </si>
+  <si>
+    <t>4725800179</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO APOIO SLEEVE TICS</t>
+  </si>
+  <si>
+    <t>SAL5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-A</t>
+  </si>
+  <si>
+    <t>LP-058182</t>
+  </si>
+  <si>
+    <t>4725800134</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE APOIO CILINDRO TICS</t>
+  </si>
+  <si>
+    <t>LP-058181</t>
+  </si>
+  <si>
+    <t>30.06.2026</t>
   </si>
   <si>
     <t>685101</t>
   </si>
   <si>
+    <t>CONFECÇÃO PINO P/ TRAVAR CHIP TAG</t>
+  </si>
+  <si>
     <t>MMA5CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW12-B</t>
-  </si>
-  <si>
-    <t>25.02.2026</t>
-  </si>
-  <si>
-    <t>Renato Meira</t>
-  </si>
-  <si>
-    <t>685622</t>
-  </si>
-  <si>
-    <t>Criação de desenho e norma</t>
-  </si>
-  <si>
-    <t>TKC1CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS21-BR</t>
-  </si>
-  <si>
-    <t>LP-054991</t>
-  </si>
-  <si>
-    <t>03.02.2026</t>
-  </si>
-  <si>
-    <t>685050</t>
-  </si>
-  <si>
-    <t>NORMA E DESENHO</t>
-  </si>
-  <si>
-    <t>Norma e Desenho</t>
-  </si>
-  <si>
-    <t>JULIANA MELO</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS23-BR</t>
-  </si>
-  <si>
-    <t>LP-055857</t>
-  </si>
-  <si>
-    <t>21.03.2026</t>
-  </si>
-  <si>
-    <t>Diego Vieira</t>
-  </si>
-  <si>
-    <t>685072</t>
-  </si>
-  <si>
-    <t>4729111575</t>
-  </si>
-  <si>
-    <t>Alterar desenho dispositivo</t>
-  </si>
-  <si>
-    <t>BRITO</t>
-  </si>
-  <si>
-    <t>CtP/COS-PMO</t>
-  </si>
-  <si>
-    <t>LP-056019</t>
-  </si>
-  <si>
-    <t>03.03.2026</t>
-  </si>
-  <si>
-    <t>30.03.2026</t>
-  </si>
-  <si>
-    <t>685401</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Buchas de Usinagem ECM</t>
-  </si>
-  <si>
-    <t>VIM6CT</t>
-  </si>
-  <si>
-    <t>CtP/MFE21</t>
-  </si>
-  <si>
-    <t>LP-055648</t>
-  </si>
-  <si>
-    <t>11.03.2026</t>
-  </si>
-  <si>
-    <t>02.04.2026</t>
-  </si>
-  <si>
-    <t>685122</t>
-  </si>
-  <si>
-    <t>Parafuso pinças Nakamura</t>
-  </si>
-  <si>
-    <t>BRA4CT</t>
-  </si>
-  <si>
-    <t>CtP/MFE11</t>
-  </si>
-  <si>
-    <t>LP-056232</t>
-  </si>
-  <si>
-    <t>12.03.2026</t>
-  </si>
-  <si>
-    <t>08.04.2026</t>
-  </si>
-  <si>
-    <t>GARRA 24 E 25</t>
-  </si>
-  <si>
-    <t>Garra HTT</t>
-  </si>
-  <si>
-    <t>LP-056376</t>
-  </si>
-  <si>
-    <t>GARRA ROBÔ</t>
-  </si>
-  <si>
-    <t>LP-056375</t>
-  </si>
-  <si>
-    <t>23.03.2026</t>
-  </si>
-  <si>
-    <t>17.04.2026</t>
-  </si>
-  <si>
-    <t>4729107175</t>
-  </si>
-  <si>
-    <t>Sacador de corpo porta eletrodo</t>
-  </si>
-  <si>
-    <t>LP-056266</t>
-  </si>
-  <si>
-    <t>27.03.2026</t>
-  </si>
-  <si>
-    <t>11.04.2026</t>
-  </si>
-  <si>
-    <t>685008</t>
-  </si>
-  <si>
-    <t>4727501901</t>
-  </si>
-  <si>
-    <t>Flange HPC</t>
-  </si>
-  <si>
-    <t>MFA9CT</t>
-  </si>
-  <si>
-    <t>LP-056311</t>
-  </si>
-  <si>
-    <t>10.04.2026</t>
-  </si>
-  <si>
-    <t>4727500383</t>
-  </si>
-  <si>
-    <t>Contraponto do Romi do HPC</t>
-  </si>
-  <si>
-    <t>LP-056310</t>
-  </si>
-  <si>
-    <t>15.05.2026</t>
-  </si>
-  <si>
-    <t>05.06.2026</t>
-  </si>
-  <si>
-    <t>Rafael Nunes</t>
-  </si>
-  <si>
-    <t>685546</t>
-  </si>
-  <si>
-    <t>TPM - SUPORTE DE CALIBRADOR USM STH</t>
-  </si>
-  <si>
-    <t>STEPHANY</t>
-  </si>
-  <si>
-    <t>LP-057518</t>
-  </si>
-  <si>
-    <t>20.05.2026</t>
-  </si>
-  <si>
-    <t>31.12.2026</t>
-  </si>
-  <si>
-    <t>Vitor Kostanecki</t>
-  </si>
-  <si>
-    <t>LP-007619-04-22</t>
-  </si>
-  <si>
-    <t>Desenho p/ retrabalho altura do suporte</t>
-  </si>
-  <si>
-    <t>JOSIANE OLIV</t>
-  </si>
-  <si>
-    <t>LP-057834</t>
-  </si>
-  <si>
-    <t>27.05.2026</t>
-  </si>
-  <si>
-    <t>15.06.2026</t>
-  </si>
-  <si>
-    <t>Rafael Lima</t>
-  </si>
-  <si>
-    <t>685421</t>
-  </si>
-  <si>
-    <t>IMPRESSÃO 3D</t>
-  </si>
-  <si>
-    <t>DISPOSITIVO MICROMETRO A LASER (ALEXANDR</t>
-  </si>
-  <si>
-    <t>QMM</t>
-  </si>
-  <si>
-    <t>PS/QMM7-CtP</t>
-  </si>
-  <si>
-    <t>LP-058173</t>
-  </si>
-  <si>
-    <t>09.06.2026</t>
-  </si>
-  <si>
-    <t>29.06.2026</t>
-  </si>
-  <si>
-    <t>685664</t>
-  </si>
-  <si>
-    <t>SUPORTE REBOLO - 5S</t>
-  </si>
-  <si>
-    <t>GUSTAVO W.</t>
-  </si>
-  <si>
-    <t>CtP/ETS</t>
-  </si>
-  <si>
-    <t>LP-057978</t>
-  </si>
-  <si>
-    <t>03.07.2025</t>
-  </si>
-  <si>
-    <t>BM-00040171_002_00000015</t>
-  </si>
-  <si>
-    <t>DISP. AUX. PARA MEDIÇÃO INDUTÂNCIA - GM</t>
-  </si>
-  <si>
-    <t>RAIRA TOPA</t>
-  </si>
-  <si>
-    <t>PS-DC/ENP1-LA</t>
-  </si>
-  <si>
-    <t>LP-058494</t>
-  </si>
-  <si>
-    <t>10.06.2026</t>
-  </si>
-  <si>
-    <t>25.06.2026</t>
-  </si>
-  <si>
-    <t>FABRICAÇÃO PROTOTIPO BATOQUE PRA BUCHA</t>
-  </si>
-  <si>
-    <t>BRUNO ARAUJO</t>
-  </si>
-  <si>
-    <t>CtP/TEF11</t>
-  </si>
-  <si>
-    <t>LP-058092</t>
-  </si>
-  <si>
-    <t>12.06.2026</t>
-  </si>
-  <si>
-    <t>26.06.2026</t>
-  </si>
-  <si>
-    <t>FABRICAÇÃO PROTOTIPO BUCHA</t>
-  </si>
-  <si>
-    <t>LP-058172</t>
-  </si>
-  <si>
-    <t>01.07.2026</t>
-  </si>
-  <si>
-    <t>685484</t>
-  </si>
-  <si>
-    <t>4725800179</t>
-  </si>
-  <si>
-    <t>DISPOSITIVO APOIO SLEEVE TICS</t>
-  </si>
-  <si>
-    <t>SAL5CT</t>
-  </si>
-  <si>
-    <t>CtP/MFW12-A</t>
-  </si>
-  <si>
-    <t>LP-058182</t>
-  </si>
-  <si>
-    <t>4725800134</t>
-  </si>
-  <si>
-    <t>DISPOSITIVO DE APOIO CILINDRO TICS</t>
-  </si>
-  <si>
-    <t>LP-058181</t>
-  </si>
-  <si>
-    <t>30.06.2026</t>
-  </si>
-  <si>
-    <t>CONFECÇÃO PINO P/ TRAVAR CHIP TAG</t>
   </si>
   <si>
     <t>CtP/MFW11-C</t>
@@ -874,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -943,60 +928,63 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>14198304</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="C2">
-        <v>14196214</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
       <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2">
+        <v>480</v>
+      </c>
+      <c r="M2" t="s">
         <v>24</v>
-      </c>
-      <c r="L2">
-        <v>730</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>14211468</v>
+      </c>
+      <c r="D3" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>14198304</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1014,7 +1002,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="M3" t="s">
         <v>32</v>
@@ -1022,16 +1010,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4">
-        <v>14211468</v>
+        <v>14214872</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
@@ -1055,7 +1043,7 @@
         <v>39</v>
       </c>
       <c r="L4">
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="M4" t="s">
         <v>40</v>
@@ -1069,92 +1057,92 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>14214872</v>
+        <v>14219586</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
         <v>43</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>46</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5">
+        <v>480</v>
+      </c>
+      <c r="M5" t="s">
         <v>47</v>
-      </c>
-      <c r="L5">
-        <v>720</v>
-      </c>
-      <c r="M5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
       <c r="C6">
-        <v>14219586</v>
+        <v>14220674</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
       <c r="I6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6">
+        <v>240</v>
+      </c>
+      <c r="M6" t="s">
         <v>52</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6">
-        <v>480</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>14220674</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>19</v>
@@ -1163,121 +1151,121 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>240</v>
       </c>
       <c r="M7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
       <c r="C8">
-        <v>14220674</v>
+        <v>14226213</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>360</v>
+      </c>
+      <c r="M8" t="s">
         <v>59</v>
-      </c>
-      <c r="J8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8">
-        <v>240</v>
-      </c>
-      <c r="M8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>14226213</v>
+        <v>14230429</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s">
         <v>65</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>240</v>
+      </c>
+      <c r="M9" t="s">
         <v>66</v>
-      </c>
-      <c r="J9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9">
-        <v>360</v>
-      </c>
-      <c r="M9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>14230429</v>
+        <v>14230434</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>19</v>
@@ -1286,60 +1274,57 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L10">
         <v>240</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>14230434</v>
+        <v>14280140</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11">
         <v>19</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" t="s">
         <v>76</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>77</v>
       </c>
-      <c r="J11" t="s">
-        <v>73</v>
-      </c>
-      <c r="K11" t="s">
-        <v>24</v>
-      </c>
       <c r="L11">
-        <v>240</v>
+        <v>1700</v>
       </c>
       <c r="M11" t="s">
         <v>78</v>
@@ -1353,7 +1338,7 @@
         <v>80</v>
       </c>
       <c r="C12">
-        <v>14280140</v>
+        <v>14282554</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
@@ -1362,10 +1347,10 @@
         <v>82</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
         <v>83</v>
@@ -1374,10 +1359,10 @@
         <v>84</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L12">
-        <v>1700</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
         <v>85</v>
@@ -1391,7 +1376,7 @@
         <v>87</v>
       </c>
       <c r="C13">
-        <v>14282554</v>
+        <v>14286462</v>
       </c>
       <c r="D13" t="s">
         <v>88</v>
@@ -1403,48 +1388,48 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="L13">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="M13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14">
-        <v>14286462</v>
+        <v>14291862</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G14">
-        <v>6</v>
-      </c>
-      <c r="H14" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
         <v>98</v>
@@ -1456,7 +1441,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="M14" t="s">
         <v>101</v>
@@ -1464,95 +1449,95 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
         <v>102</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15">
+        <v>14292024</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
         <v>103</v>
       </c>
-      <c r="C15">
-        <v>14291862</v>
-      </c>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>104</v>
-      </c>
       <c r="F15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" t="s">
         <v>105</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>106</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15">
+        <v>420</v>
+      </c>
+      <c r="M15" t="s">
         <v>107</v>
-      </c>
-      <c r="L15">
-        <v>400</v>
-      </c>
-      <c r="M15" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16">
-        <v>14292024</v>
+        <v>14292725</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="I16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" t="s">
         <v>111</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>112</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16">
+        <v>290</v>
+      </c>
+      <c r="M16" t="s">
         <v>113</v>
-      </c>
-      <c r="L16">
-        <v>420</v>
-      </c>
-      <c r="M16" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
-        <v>116</v>
-      </c>
       <c r="C17">
-        <v>14292725</v>
+        <v>14293824</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F17">
         <v>19</v>
@@ -1561,54 +1546,57 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17">
+        <v>250</v>
+      </c>
+      <c r="M17" t="s">
         <v>117</v>
-      </c>
-      <c r="J17" t="s">
-        <v>118</v>
-      </c>
-      <c r="K17" t="s">
-        <v>119</v>
-      </c>
-      <c r="L17">
-        <v>290</v>
-      </c>
-      <c r="M17" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C18">
-        <v>14293824</v>
+        <v>14294067</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
+      <c r="H18" t="s">
+        <v>120</v>
+      </c>
       <c r="I18" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18" t="s">
         <v>123</v>
       </c>
-      <c r="J18" t="s">
-        <v>118</v>
-      </c>
-      <c r="K18" t="s">
-        <v>119</v>
-      </c>
       <c r="L18">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="M18" t="s">
         <v>124</v>
@@ -1616,19 +1604,19 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C19">
         <v>14294067</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -1637,294 +1625,253 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="L19">
         <v>125</v>
       </c>
       <c r="M19" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C20">
-        <v>14294067</v>
+        <v>14294794</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" t="s">
+        <v>130</v>
+      </c>
+      <c r="J20" t="s">
+        <v>131</v>
+      </c>
+      <c r="K20" t="s">
         <v>132</v>
       </c>
-      <c r="I20" t="s">
+      <c r="L20">
+        <v>600</v>
+      </c>
+      <c r="M20" t="s">
         <v>133</v>
-      </c>
-      <c r="J20" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20">
-        <v>125</v>
-      </c>
-      <c r="M20" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21">
+        <v>14294975</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="I21" t="s">
         <v>135</v>
       </c>
-      <c r="C21">
-        <v>14294794</v>
-      </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21">
-        <v>19</v>
-      </c>
-      <c r="G21">
-        <v>50</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>136</v>
       </c>
-      <c r="J21" t="s">
-        <v>17</v>
-      </c>
       <c r="K21" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>300</v>
+      </c>
+      <c r="M21" t="s">
         <v>137</v>
-      </c>
-      <c r="L21">
-        <v>600</v>
-      </c>
-      <c r="M21" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C22">
-        <v>14294975</v>
+        <v>14295418</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K22" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="L22">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="M22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23">
-        <v>14295418</v>
+        <v>14296368</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L23">
-        <v>1500</v>
+        <v>650</v>
       </c>
       <c r="M23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
         <v>150</v>
       </c>
       <c r="C24">
-        <v>14296368</v>
+        <v>14298510</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
         <v>151</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
+        <v>152</v>
       </c>
       <c r="I24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="L24">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="M24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C25">
-        <v>14298510</v>
+        <v>14299293</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
         <v>157</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25">
+        <v>650</v>
+      </c>
+      <c r="M25" t="s">
         <v>158</v>
-      </c>
-      <c r="J25" t="s">
-        <v>159</v>
-      </c>
-      <c r="K25" t="s">
-        <v>119</v>
-      </c>
-      <c r="L25">
-        <v>400</v>
-      </c>
-      <c r="M25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26">
-        <v>14299293</v>
-      </c>
-      <c r="D26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" t="s">
-        <v>151</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="I26" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" t="s">
-        <v>153</v>
-      </c>
-      <c r="K26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26">
-        <v>650</v>
-      </c>
-      <c r="M26" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83724AB0-CFEA-4626-9092-CFB49AC4CD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097D7365-BA53-4EE0-9258-CAA7899A6ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1634,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1744,183 +1744,60 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>171</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4">
-        <v>6000</v>
-      </c>
-      <c r="M4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
-        <v>400</v>
-      </c>
-      <c r="M5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6">
-        <v>2450</v>
-      </c>
-      <c r="M6" t="s">
-        <v>81</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
         <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>52</v>
@@ -1929,51 +1806,51 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L7">
-        <v>780</v>
+        <v>500</v>
       </c>
       <c r="M7" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
         <v>47</v>
@@ -1982,171 +1859,174 @@
         <v>32</v>
       </c>
       <c r="L8">
-        <v>10650</v>
+        <v>6000</v>
       </c>
       <c r="M8" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
         <v>52</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L9">
-        <v>7280</v>
+        <v>400</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>52</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L10">
-        <v>9360</v>
+        <v>2450</v>
       </c>
       <c r="M10" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
         <v>52</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L11">
-        <v>3800</v>
+        <v>780</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
       </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
       <c r="D12" t="s">
         <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>52</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L12">
-        <v>4600</v>
+        <v>10650</v>
       </c>
       <c r="M12" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2157,7 +2037,7 @@
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
@@ -2169,13 +2049,13 @@
         <v>52</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s">
         <v>96</v>
@@ -2184,97 +2064,97 @@
         <v>37</v>
       </c>
       <c r="L13">
-        <v>4280</v>
+        <v>7280</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
         <v>52</v>
       </c>
       <c r="G14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I14" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L14">
-        <v>9120</v>
+        <v>9360</v>
       </c>
       <c r="M14" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
         <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
         <v>52</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L15">
-        <v>1140</v>
+        <v>3800</v>
       </c>
       <c r="M15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
@@ -2283,72 +2163,72 @@
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="I16" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L16">
-        <v>2040</v>
+        <v>4600</v>
       </c>
       <c r="M16" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
         <v>52</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L17">
-        <v>7540</v>
+        <v>4280</v>
       </c>
       <c r="M17" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -2359,7 +2239,7 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>50</v>
@@ -2371,13 +2251,13 @@
         <v>52</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J18" t="s">
         <v>47</v>
@@ -2386,80 +2266,77 @@
         <v>32</v>
       </c>
       <c r="L18">
-        <v>1800</v>
+        <v>9120</v>
       </c>
       <c r="M18" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
         <v>52</v>
       </c>
       <c r="G19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J19" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="K19" t="s">
         <v>32</v>
       </c>
       <c r="L19">
-        <v>2800</v>
+        <v>1140</v>
       </c>
       <c r="M19" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
         <v>52</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I20" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="J20" t="s">
         <v>47</v>
@@ -2468,174 +2345,174 @@
         <v>32</v>
       </c>
       <c r="L20">
-        <v>6520</v>
+        <v>2040</v>
       </c>
       <c r="M20" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="I21" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="J21" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="K21" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L21">
-        <v>3300</v>
+        <v>7540</v>
       </c>
       <c r="M21" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="I22" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="J22" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="K22" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L22">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="M22" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="J23" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L23">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
         <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="I24" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="J24" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L24">
-        <v>6000</v>
+        <v>6520</v>
       </c>
       <c r="M24" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -2646,37 +2523,37 @@
         <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
         <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L25">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="M25" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -2687,218 +2564,218 @@
         <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
         <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
       </c>
       <c r="L26">
-        <v>5100</v>
+        <v>3500</v>
       </c>
       <c r="M26" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="J27" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="L27">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="M27" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="J28" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L28">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="M28" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="I29" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L29">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="M29" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I30" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="J30" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L30">
-        <v>900</v>
+        <v>5100</v>
       </c>
       <c r="M30" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D31" t="s">
         <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s">
         <v>171</v>
@@ -2907,39 +2784,39 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="L31">
         <v>400</v>
       </c>
       <c r="M31" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
         <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="F32" t="s">
         <v>171</v>
@@ -2948,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="J32" t="s">
         <v>26</v>
@@ -2960,39 +2837,39 @@
         <v>27</v>
       </c>
       <c r="L32">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M32" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
         <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="F33" t="s">
         <v>171</v>
       </c>
       <c r="G33">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="I33" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="J33" t="s">
         <v>26</v>
@@ -3001,10 +2878,10 @@
         <v>27</v>
       </c>
       <c r="L33">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="M33" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -3015,25 +2892,25 @@
         <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
         <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F34" t="s">
         <v>171</v>
       </c>
       <c r="G34">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="I34" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="J34" t="s">
         <v>26</v>
@@ -3042,27 +2919,27 @@
         <v>27</v>
       </c>
       <c r="L34">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="M34" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
         <v>180</v>
       </c>
       <c r="C35" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
         <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="F35" t="s">
         <v>171</v>
@@ -3071,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I35" t="s">
         <v>189</v>
@@ -3086,24 +2963,24 @@
         <v>400</v>
       </c>
       <c r="M35" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
         <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="F36" t="s">
         <v>171</v>
@@ -3112,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="I36" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="J36" t="s">
         <v>26</v>
@@ -3124,21 +3001,21 @@
         <v>27</v>
       </c>
       <c r="L36">
-        <v>4300</v>
+        <v>500</v>
       </c>
       <c r="M36" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D37" t="s">
         <v>169</v>
@@ -3150,13 +3027,13 @@
         <v>171</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H37" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="J37" t="s">
         <v>26</v>
@@ -3165,39 +3042,39 @@
         <v>27</v>
       </c>
       <c r="L37">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="M37" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
         <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
         <v>171</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H38" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="J38" t="s">
         <v>26</v>
@@ -3206,21 +3083,21 @@
         <v>27</v>
       </c>
       <c r="L38">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="M38" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D39" t="s">
         <v>169</v>
@@ -3232,13 +3109,13 @@
         <v>171</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="I39" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="J39" t="s">
         <v>26</v>
@@ -3247,39 +3124,39 @@
         <v>27</v>
       </c>
       <c r="L39">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="M39" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
         <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
         <v>171</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="I40" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="J40" t="s">
         <v>26</v>
@@ -3288,21 +3165,21 @@
         <v>27</v>
       </c>
       <c r="L40">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
         <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D41" t="s">
         <v>169</v>
@@ -3317,10 +3194,10 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="I41" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="J41" t="s">
         <v>26</v>
@@ -3329,39 +3206,39 @@
         <v>27</v>
       </c>
       <c r="L41">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="M41" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
         <v>169</v>
       </c>
       <c r="E42" t="s">
-        <v>220</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
         <v>171</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="I42" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="J42" t="s">
         <v>26</v>
@@ -3370,39 +3247,39 @@
         <v>27</v>
       </c>
       <c r="L42">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="M42" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D43" t="s">
         <v>169</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>39</v>
       </c>
       <c r="F43" t="s">
         <v>171</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="I43" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="J43" t="s">
         <v>26</v>
@@ -3411,27 +3288,27 @@
         <v>27</v>
       </c>
       <c r="L43">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="M43" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D44" t="s">
         <v>169</v>
       </c>
       <c r="E44" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="F44" t="s">
         <v>171</v>
@@ -3440,10 +3317,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I44" t="s">
-        <v>245</v>
+        <v>184</v>
       </c>
       <c r="J44" t="s">
         <v>26</v>
@@ -3452,39 +3329,39 @@
         <v>27</v>
       </c>
       <c r="L44">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M44" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D45" t="s">
         <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
         <v>171</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I45" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="J45" t="s">
         <v>26</v>
@@ -3493,21 +3370,21 @@
         <v>27</v>
       </c>
       <c r="L45">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D46" t="s">
         <v>169</v>
@@ -3522,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="I46" t="s">
         <v>237</v>
@@ -3537,24 +3414,24 @@
         <v>400</v>
       </c>
       <c r="M46" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D47" t="s">
         <v>169</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="F47" t="s">
         <v>171</v>
@@ -3563,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I47" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="J47" t="s">
         <v>26</v>
@@ -3578,7 +3455,7 @@
         <v>400</v>
       </c>
       <c r="M47" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -3589,25 +3466,25 @@
         <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D48" t="s">
         <v>169</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="F48" t="s">
         <v>171</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="I48" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="J48" t="s">
         <v>26</v>
@@ -3616,21 +3493,21 @@
         <v>27</v>
       </c>
       <c r="L48">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="M48" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D49" t="s">
         <v>169</v>
@@ -3645,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="I49" t="s">
         <v>237</v>
@@ -3660,24 +3537,24 @@
         <v>400</v>
       </c>
       <c r="M49" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D50" t="s">
         <v>169</v>
       </c>
       <c r="E50" t="s">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="F50" t="s">
         <v>171</v>
@@ -3686,10 +3563,10 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I50" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="J50" t="s">
         <v>26</v>
@@ -3698,27 +3575,27 @@
         <v>27</v>
       </c>
       <c r="L50">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B51" t="s">
         <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D51" t="s">
         <v>169</v>
       </c>
       <c r="E51" t="s">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="F51" t="s">
         <v>171</v>
@@ -3727,10 +3604,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="I51" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="J51" t="s">
         <v>26</v>
@@ -3739,27 +3616,27 @@
         <v>27</v>
       </c>
       <c r="L51">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="D52" t="s">
         <v>169</v>
       </c>
       <c r="E52" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="F52" t="s">
         <v>171</v>
@@ -3768,10 +3645,10 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="I52" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="J52" t="s">
         <v>26</v>
@@ -3780,27 +3657,27 @@
         <v>27</v>
       </c>
       <c r="L52">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="D53" t="s">
         <v>169</v>
       </c>
       <c r="E53" t="s">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="F53" t="s">
         <v>171</v>
@@ -3809,10 +3686,10 @@
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="I53" t="s">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="J53" t="s">
         <v>26</v>
@@ -3821,27 +3698,27 @@
         <v>27</v>
       </c>
       <c r="L53">
-        <v>11500</v>
+        <v>1100</v>
       </c>
       <c r="M53" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="B54" t="s">
         <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D54" t="s">
         <v>169</v>
       </c>
       <c r="E54" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="F54" t="s">
         <v>171</v>
@@ -3850,10 +3727,10 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="I54" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="J54" t="s">
         <v>26</v>
@@ -3862,27 +3739,27 @@
         <v>27</v>
       </c>
       <c r="L54">
-        <v>5300</v>
+        <v>2500</v>
       </c>
       <c r="M54" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
         <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D55" t="s">
         <v>169</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>274</v>
       </c>
       <c r="F55" t="s">
         <v>171</v>
@@ -3891,10 +3768,10 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="I55" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J55" t="s">
         <v>26</v>
@@ -3903,10 +3780,10 @@
         <v>27</v>
       </c>
       <c r="L55">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="M55" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -3917,7 +3794,7 @@
         <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D56" t="s">
         <v>169</v>
@@ -3932,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="I56" t="s">
         <v>282</v>
@@ -3944,10 +3821,10 @@
         <v>27</v>
       </c>
       <c r="L56">
-        <v>10800</v>
+        <v>11500</v>
       </c>
       <c r="M56" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -3958,13 +3835,13 @@
         <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D57" t="s">
         <v>169</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="F57" t="s">
         <v>171</v>
@@ -3973,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I57" t="s">
         <v>282</v>
@@ -3985,10 +3862,10 @@
         <v>27</v>
       </c>
       <c r="L57">
-        <v>10100</v>
+        <v>5300</v>
       </c>
       <c r="M57" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -3999,13 +3876,13 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D58" t="s">
         <v>169</v>
       </c>
       <c r="E58" t="s">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
         <v>171</v>
@@ -4014,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I58" t="s">
         <v>282</v>
@@ -4029,7 +3906,7 @@
         <v>12000</v>
       </c>
       <c r="M58" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -4040,7 +3917,7 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D59" t="s">
         <v>169</v>
@@ -4055,10 +3932,10 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="I59" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="J59" t="s">
         <v>26</v>
@@ -4067,10 +3944,10 @@
         <v>27</v>
       </c>
       <c r="L59">
-        <v>2000</v>
+        <v>10800</v>
       </c>
       <c r="M59" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -4081,13 +3958,13 @@
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D60" t="s">
         <v>169</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
         <v>171</v>
@@ -4096,10 +3973,10 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="I60" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="J60" t="s">
         <v>26</v>
@@ -4108,10 +3985,10 @@
         <v>27</v>
       </c>
       <c r="L60">
-        <v>19000</v>
+        <v>10100</v>
       </c>
       <c r="M60" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -4122,13 +3999,13 @@
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D61" t="s">
         <v>169</v>
       </c>
       <c r="E61" t="s">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="F61" t="s">
         <v>171</v>
@@ -4137,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I61" t="s">
         <v>282</v>
@@ -4149,10 +4026,10 @@
         <v>27</v>
       </c>
       <c r="L61">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="M61" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -4163,7 +4040,7 @@
         <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D62" t="s">
         <v>169</v>
@@ -4178,10 +4055,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="I62" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="J62" t="s">
         <v>26</v>
@@ -4190,10 +4067,10 @@
         <v>27</v>
       </c>
       <c r="L62">
-        <v>7400</v>
+        <v>2000</v>
       </c>
       <c r="M62" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -4204,13 +4081,13 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D63" t="s">
         <v>169</v>
       </c>
       <c r="E63" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F63" t="s">
         <v>171</v>
@@ -4219,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I63" t="s">
         <v>217</v>
@@ -4231,39 +4108,39 @@
         <v>27</v>
       </c>
       <c r="L63">
-        <v>1500</v>
+        <v>19000</v>
       </c>
       <c r="M63" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s">
         <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D64" t="s">
         <v>169</v>
       </c>
       <c r="E64" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F64" t="s">
         <v>171</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I64" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="J64" t="s">
         <v>26</v>
@@ -4272,39 +4149,39 @@
         <v>27</v>
       </c>
       <c r="L64">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="M64" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s">
         <v>169</v>
       </c>
       <c r="E65" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="F65" t="s">
         <v>171</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="I65" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="J65" t="s">
         <v>26</v>
@@ -4313,80 +4190,80 @@
         <v>27</v>
       </c>
       <c r="L65">
-        <v>1200</v>
+        <v>7400</v>
       </c>
       <c r="M65" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D66" t="s">
         <v>169</v>
       </c>
       <c r="E66" t="s">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="I66" t="s">
-        <v>324</v>
+        <v>217</v>
       </c>
       <c r="J66" t="s">
-        <v>325</v>
+        <v>26</v>
       </c>
       <c r="K66" t="s">
-        <v>326</v>
+        <v>27</v>
       </c>
       <c r="L66">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="M66" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
         <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D67" t="s">
         <v>169</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F67" t="s">
         <v>171</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="I67" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="J67" t="s">
         <v>26</v>
@@ -4395,39 +4272,39 @@
         <v>27</v>
       </c>
       <c r="L67">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="M67" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
         <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D68" t="s">
         <v>169</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="F68" t="s">
         <v>171</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="I68" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="J68" t="s">
         <v>26</v>
@@ -4436,68 +4313,68 @@
         <v>27</v>
       </c>
       <c r="L68">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="M68" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="B69" t="s">
         <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D69" t="s">
         <v>169</v>
       </c>
       <c r="E69" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F69" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="I69" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="J69" t="s">
-        <v>26</v>
+        <v>325</v>
       </c>
       <c r="K69" t="s">
-        <v>27</v>
+        <v>326</v>
       </c>
       <c r="L69">
-        <v>3600</v>
+        <v>9000</v>
       </c>
       <c r="M69" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>341</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
         <v>23</v>
       </c>
       <c r="C70" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="D70" t="s">
         <v>169</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F70" t="s">
         <v>171</v>
@@ -4506,10 +4383,10 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="I70" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="J70" t="s">
         <v>26</v>
@@ -4518,39 +4395,39 @@
         <v>27</v>
       </c>
       <c r="L70">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="M70" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
         <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="D71" t="s">
         <v>169</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
         <v>171</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="I71" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="J71" t="s">
         <v>26</v>
@@ -4559,39 +4436,39 @@
         <v>27</v>
       </c>
       <c r="L71">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="M71" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="D72" t="s">
         <v>169</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="F72" t="s">
         <v>171</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="I72" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="J72" t="s">
         <v>26</v>
@@ -4600,27 +4477,27 @@
         <v>27</v>
       </c>
       <c r="L72">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="M72" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>341</v>
       </c>
       <c r="B73" t="s">
         <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D73" t="s">
         <v>169</v>
       </c>
       <c r="E73" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F73" t="s">
         <v>171</v>
@@ -4629,10 +4506,10 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="I73" t="s">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="J73" t="s">
         <v>26</v>
@@ -4641,27 +4518,27 @@
         <v>27</v>
       </c>
       <c r="L73">
-        <v>900</v>
+        <v>4000</v>
       </c>
       <c r="M73" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>341</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D74" t="s">
         <v>169</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
         <v>171</v>
@@ -4670,10 +4547,10 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I74" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="J74" t="s">
         <v>26</v>
@@ -4682,10 +4559,10 @@
         <v>27</v>
       </c>
       <c r="L74">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="M74" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -4696,13 +4573,13 @@
         <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D75" t="s">
         <v>169</v>
       </c>
       <c r="E75" t="s">
-        <v>360</v>
+        <v>220</v>
       </c>
       <c r="F75" t="s">
         <v>171</v>
@@ -4711,10 +4588,10 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="I75" t="s">
-        <v>362</v>
+        <v>184</v>
       </c>
       <c r="J75" t="s">
         <v>26</v>
@@ -4723,10 +4600,10 @@
         <v>27</v>
       </c>
       <c r="L75">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="M75" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -4737,13 +4614,13 @@
         <v>23</v>
       </c>
       <c r="C76" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D76" t="s">
         <v>169</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F76" t="s">
         <v>171</v>
@@ -4752,10 +4629,10 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="I76" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J76" t="s">
         <v>26</v>
@@ -4764,10 +4641,10 @@
         <v>27</v>
       </c>
       <c r="L76">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="M76" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -4778,25 +4655,25 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="D77" t="s">
         <v>169</v>
       </c>
       <c r="E77" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
         <v>171</v>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="I77" t="s">
-        <v>369</v>
+        <v>189</v>
       </c>
       <c r="J77" t="s">
         <v>26</v>
@@ -4805,10 +4682,10 @@
         <v>27</v>
       </c>
       <c r="L77">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="M77" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -4819,13 +4696,13 @@
         <v>23</v>
       </c>
       <c r="C78" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D78" t="s">
         <v>169</v>
       </c>
       <c r="E78" t="s">
-        <v>39</v>
+        <v>360</v>
       </c>
       <c r="F78" t="s">
         <v>171</v>
@@ -4834,10 +4711,10 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="I78" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="J78" t="s">
         <v>26</v>
@@ -4846,10 +4723,10 @@
         <v>27</v>
       </c>
       <c r="L78">
-        <v>4800</v>
+        <v>600</v>
       </c>
       <c r="M78" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -4860,13 +4737,13 @@
         <v>23</v>
       </c>
       <c r="C79" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="D79" t="s">
         <v>169</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F79" t="s">
         <v>171</v>
@@ -4875,10 +4752,10 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I79" t="s">
-        <v>373</v>
+        <v>184</v>
       </c>
       <c r="J79" t="s">
         <v>26</v>
@@ -4887,21 +4764,21 @@
         <v>27</v>
       </c>
       <c r="L79">
-        <v>4800</v>
+        <v>500</v>
       </c>
       <c r="M79" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>378</v>
+        <v>87</v>
       </c>
       <c r="B80" t="s">
         <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D80" t="s">
         <v>169</v>
@@ -4913,13 +4790,13 @@
         <v>171</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H80" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="I80" t="s">
-        <v>189</v>
+        <v>369</v>
       </c>
       <c r="J80" t="s">
         <v>26</v>
@@ -4928,27 +4805,27 @@
         <v>27</v>
       </c>
       <c r="L80">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="M80" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
         <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D81" t="s">
         <v>169</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F81" t="s">
         <v>171</v>
@@ -4957,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="I81" t="s">
-        <v>184</v>
+        <v>373</v>
       </c>
       <c r="J81" t="s">
         <v>26</v>
@@ -4969,27 +4846,27 @@
         <v>27</v>
       </c>
       <c r="L81">
-        <v>800</v>
+        <v>4800</v>
       </c>
       <c r="M81" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B82" t="s">
         <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D82" t="s">
         <v>169</v>
       </c>
       <c r="E82" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
         <v>171</v>
@@ -4998,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="I82" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="J82" t="s">
         <v>26</v>
@@ -5010,27 +4887,27 @@
         <v>27</v>
       </c>
       <c r="L82">
-        <v>600</v>
+        <v>4800</v>
       </c>
       <c r="M82" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B83" t="s">
         <v>23</v>
       </c>
       <c r="C83" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="D83" t="s">
         <v>169</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F83" t="s">
         <v>171</v>
@@ -5039,10 +4916,10 @@
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="I83" t="s">
-        <v>392</v>
+        <v>189</v>
       </c>
       <c r="J83" t="s">
         <v>26</v>
@@ -5051,21 +4928,21 @@
         <v>27</v>
       </c>
       <c r="L83">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="M83" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>389</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
       </c>
       <c r="C84" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D84" t="s">
         <v>169</v>
@@ -5080,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="I84" t="s">
-        <v>396</v>
+        <v>184</v>
       </c>
       <c r="J84" t="s">
         <v>26</v>
@@ -5092,27 +4969,27 @@
         <v>27</v>
       </c>
       <c r="L84">
-        <v>2600</v>
+        <v>800</v>
       </c>
       <c r="M84" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>389</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="D85" t="s">
         <v>169</v>
       </c>
       <c r="E85" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F85" t="s">
         <v>171</v>
@@ -5121,10 +4998,10 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="I85" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="J85" t="s">
         <v>26</v>
@@ -5133,21 +5010,21 @@
         <v>27</v>
       </c>
       <c r="L85">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="M85" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="B86" t="s">
         <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D86" t="s">
         <v>169</v>
@@ -5162,10 +5039,10 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="I86" t="s">
-        <v>184</v>
+        <v>392</v>
       </c>
       <c r="J86" t="s">
         <v>26</v>
@@ -5174,21 +5051,21 @@
         <v>27</v>
       </c>
       <c r="L86">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M86" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="B87" t="s">
         <v>23</v>
       </c>
       <c r="C87" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D87" t="s">
         <v>169</v>
@@ -5203,10 +5080,10 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="I87" t="s">
-        <v>189</v>
+        <v>396</v>
       </c>
       <c r="J87" t="s">
         <v>26</v>
@@ -5215,27 +5092,27 @@
         <v>27</v>
       </c>
       <c r="L87">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="M87" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="B88" t="s">
         <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D88" t="s">
         <v>169</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F88" t="s">
         <v>171</v>
@@ -5244,10 +5121,10 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="I88" t="s">
-        <v>184</v>
+        <v>400</v>
       </c>
       <c r="J88" t="s">
         <v>26</v>
@@ -5256,50 +5133,173 @@
         <v>27</v>
       </c>
       <c r="L88">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="M88" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>411</v>
+        <v>111</v>
       </c>
       <c r="B89" t="s">
         <v>23</v>
       </c>
       <c r="C89" t="s">
+        <v>402</v>
+      </c>
+      <c r="D89" t="s">
+        <v>169</v>
+      </c>
+      <c r="E89" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89" t="s">
+        <v>171</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>403</v>
+      </c>
+      <c r="I89" t="s">
+        <v>184</v>
+      </c>
+      <c r="J89" t="s">
+        <v>26</v>
+      </c>
+      <c r="K89" t="s">
+        <v>27</v>
+      </c>
+      <c r="L89">
+        <v>500</v>
+      </c>
+      <c r="M89" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>111</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="s">
+        <v>405</v>
+      </c>
+      <c r="D90" t="s">
+        <v>169</v>
+      </c>
+      <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" t="s">
+        <v>171</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>406</v>
+      </c>
+      <c r="I90" t="s">
+        <v>189</v>
+      </c>
+      <c r="J90" t="s">
+        <v>26</v>
+      </c>
+      <c r="K90" t="s">
+        <v>27</v>
+      </c>
+      <c r="L90">
+        <v>500</v>
+      </c>
+      <c r="M90" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>408</v>
+      </c>
+      <c r="D91" t="s">
+        <v>169</v>
+      </c>
+      <c r="E91" t="s">
+        <v>39</v>
+      </c>
+      <c r="F91" t="s">
+        <v>171</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>409</v>
+      </c>
+      <c r="I91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J91" t="s">
+        <v>26</v>
+      </c>
+      <c r="K91" t="s">
+        <v>27</v>
+      </c>
+      <c r="L91">
+        <v>1200</v>
+      </c>
+      <c r="M91" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>411</v>
+      </c>
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" t="s">
         <v>412</v>
       </c>
-      <c r="D89" t="s">
-        <v>169</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="D92" t="s">
+        <v>169</v>
+      </c>
+      <c r="E92" t="s">
         <v>207</v>
       </c>
-      <c r="F89" t="s">
-        <v>171</v>
-      </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
-      <c r="H89" t="s">
+      <c r="F92" t="s">
+        <v>171</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
         <v>413</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I92" t="s">
         <v>414</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J92" t="s">
         <v>415</v>
       </c>
-      <c r="K89" t="s">
+      <c r="K92" t="s">
         <v>15</v>
       </c>
-      <c r="L89">
+      <c r="L92">
         <v>4200</v>
       </c>
-      <c r="M89" t="s">
+      <c r="M92" t="s">
         <v>416</v>
       </c>
     </row>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF234344-942B-4DAB-86A3-43806BC3B1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FF9538-0860-4346-A312-DE63E0978227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="288">
   <si>
     <t>Data</t>
   </si>
@@ -731,15 +731,6 @@
   </si>
   <si>
     <t>03.07.2026</t>
-  </si>
-  <si>
-    <t>4716506412</t>
-  </si>
-  <si>
-    <t>Novo - serie 0173</t>
-  </si>
-  <si>
-    <t>LP-058943</t>
   </si>
   <si>
     <t>4716511279</t>
@@ -1255,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3831,7 +3822,7 @@
         <v>17</v>
       </c>
       <c r="D68">
-        <v>685484</v>
+        <v>685485</v>
       </c>
       <c r="E68">
         <v>4</v>
@@ -3852,7 +3843,7 @@
         <v>20</v>
       </c>
       <c r="K68">
-        <v>4000</v>
+        <v>3200</v>
       </c>
       <c r="L68" t="s">
         <v>239</v>
@@ -3860,7 +3851,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
         <v>140</v>
@@ -3869,7 +3860,7 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>685485</v>
+        <v>685434</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -3881,19 +3872,19 @@
         <v>240</v>
       </c>
       <c r="H69" t="s">
+        <v>125</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69">
+        <v>400</v>
+      </c>
+      <c r="L69" t="s">
         <v>241</v>
-      </c>
-      <c r="I69" t="s">
-        <v>19</v>
-      </c>
-      <c r="J69" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69">
-        <v>3200</v>
-      </c>
-      <c r="L69" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3907,7 +3898,7 @@
         <v>17</v>
       </c>
       <c r="D70">
-        <v>685434</v>
+        <v>685541</v>
       </c>
       <c r="E70">
         <v>4</v>
@@ -3916,22 +3907,22 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
+        <v>242</v>
+      </c>
+      <c r="H70" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70">
+        <v>900</v>
+      </c>
+      <c r="L70" t="s">
         <v>243</v>
-      </c>
-      <c r="H70" t="s">
-        <v>125</v>
-      </c>
-      <c r="I70" t="s">
-        <v>19</v>
-      </c>
-      <c r="J70" t="s">
-        <v>20</v>
-      </c>
-      <c r="K70">
-        <v>400</v>
-      </c>
-      <c r="L70" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3945,7 +3936,7 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>685541</v>
+        <v>685072</v>
       </c>
       <c r="E71">
         <v>4</v>
@@ -3954,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
@@ -3966,10 +3957,10 @@
         <v>20</v>
       </c>
       <c r="K71">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="L71" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3983,7 +3974,7 @@
         <v>17</v>
       </c>
       <c r="D72">
-        <v>685072</v>
+        <v>685491</v>
       </c>
       <c r="E72">
         <v>4</v>
@@ -3992,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
+        <v>246</v>
+      </c>
+      <c r="H72" t="s">
         <v>247</v>
-      </c>
-      <c r="H72" t="s">
-        <v>18</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -4021,7 +4012,7 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>685491</v>
+        <v>685484</v>
       </c>
       <c r="E73">
         <v>4</v>
@@ -4033,19 +4024,19 @@
         <v>249</v>
       </c>
       <c r="H73" t="s">
+        <v>125</v>
+      </c>
+      <c r="I73" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73">
+        <v>500</v>
+      </c>
+      <c r="L73" t="s">
         <v>250</v>
-      </c>
-      <c r="I73" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" t="s">
-        <v>20</v>
-      </c>
-      <c r="K73">
-        <v>600</v>
-      </c>
-      <c r="L73" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -4059,20 +4050,20 @@
         <v>17</v>
       </c>
       <c r="D74">
-        <v>685484</v>
+        <v>685485</v>
       </c>
       <c r="E74">
         <v>4</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G74" t="s">
+        <v>251</v>
+      </c>
+      <c r="H74" t="s">
         <v>252</v>
       </c>
-      <c r="H74" t="s">
-        <v>125</v>
-      </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
@@ -4080,7 +4071,7 @@
         <v>20</v>
       </c>
       <c r="K74">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="L74" t="s">
         <v>253</v>
@@ -4103,7 +4094,7 @@
         <v>4</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G75" t="s">
         <v>254</v>
@@ -4118,7 +4109,7 @@
         <v>20</v>
       </c>
       <c r="K75">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="L75" t="s">
         <v>256</v>
@@ -4147,7 +4138,7 @@
         <v>257</v>
       </c>
       <c r="H76" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
@@ -4159,12 +4150,12 @@
         <v>4800</v>
       </c>
       <c r="L76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
         <v>140</v>
@@ -4185,7 +4176,7 @@
         <v>260</v>
       </c>
       <c r="H77" t="s">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
@@ -4194,7 +4185,7 @@
         <v>20</v>
       </c>
       <c r="K77">
-        <v>4800</v>
+        <v>2000</v>
       </c>
       <c r="L77" t="s">
         <v>261</v>
@@ -4202,40 +4193,40 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>52</v>
+      </c>
+      <c r="B78" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78">
+        <v>685484</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
         <v>262</v>
       </c>
-      <c r="B78" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78">
-        <v>685485</v>
-      </c>
-      <c r="E78">
-        <v>4</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
+        <v>125</v>
+      </c>
+      <c r="I78" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <v>800</v>
+      </c>
+      <c r="L78" t="s">
         <v>263</v>
-      </c>
-      <c r="H78" t="s">
-        <v>18</v>
-      </c>
-      <c r="I78" t="s">
-        <v>19</v>
-      </c>
-      <c r="J78" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78">
-        <v>2000</v>
-      </c>
-      <c r="L78" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4249,7 +4240,7 @@
         <v>17</v>
       </c>
       <c r="D79">
-        <v>685484</v>
+        <v>685008</v>
       </c>
       <c r="E79">
         <v>4</v>
@@ -4258,11 +4249,11 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
+        <v>264</v>
+      </c>
+      <c r="H79" t="s">
         <v>265</v>
       </c>
-      <c r="H79" t="s">
-        <v>125</v>
-      </c>
       <c r="I79" t="s">
         <v>19</v>
       </c>
@@ -4270,7 +4261,7 @@
         <v>20</v>
       </c>
       <c r="K79">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="L79" t="s">
         <v>266</v>
@@ -4278,7 +4269,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>267</v>
       </c>
       <c r="B80" t="s">
         <v>140</v>
@@ -4287,7 +4278,7 @@
         <v>17</v>
       </c>
       <c r="D80">
-        <v>685008</v>
+        <v>685484</v>
       </c>
       <c r="E80">
         <v>4</v>
@@ -4296,10 +4287,10 @@
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
@@ -4308,15 +4299,15 @@
         <v>20</v>
       </c>
       <c r="K80">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B81" t="s">
         <v>140</v>
@@ -4346,7 +4337,7 @@
         <v>20</v>
       </c>
       <c r="K81">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="L81" t="s">
         <v>273</v>
@@ -4354,7 +4345,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B82" t="s">
         <v>140</v>
@@ -4384,7 +4375,7 @@
         <v>20</v>
       </c>
       <c r="K82">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="L82" t="s">
         <v>276</v>
@@ -4392,7 +4383,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>270</v>
+        <v>70</v>
       </c>
       <c r="B83" t="s">
         <v>140</v>
@@ -4413,19 +4404,19 @@
         <v>277</v>
       </c>
       <c r="H83" t="s">
+        <v>125</v>
+      </c>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83">
+        <v>500</v>
+      </c>
+      <c r="L83" t="s">
         <v>278</v>
-      </c>
-      <c r="I83" t="s">
-        <v>19</v>
-      </c>
-      <c r="J83" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83">
-        <v>1000</v>
-      </c>
-      <c r="L83" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4448,10 +4439,10 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H84" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
@@ -4463,7 +4454,7 @@
         <v>500</v>
       </c>
       <c r="L84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4477,7 +4468,7 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>685484</v>
+        <v>685485</v>
       </c>
       <c r="E85">
         <v>4</v>
@@ -4486,27 +4477,27 @@
         <v>1</v>
       </c>
       <c r="G85" t="s">
+        <v>281</v>
+      </c>
+      <c r="H85" t="s">
+        <v>125</v>
+      </c>
+      <c r="I85" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85">
+        <v>1200</v>
+      </c>
+      <c r="L85" t="s">
         <v>282</v>
-      </c>
-      <c r="H85" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" t="s">
-        <v>19</v>
-      </c>
-      <c r="J85" t="s">
-        <v>20</v>
-      </c>
-      <c r="K85">
-        <v>500</v>
-      </c>
-      <c r="L85" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
         <v>140</v>
@@ -4515,7 +4506,7 @@
         <v>17</v>
       </c>
       <c r="D86">
-        <v>685485</v>
+        <v>685551</v>
       </c>
       <c r="E86">
         <v>4</v>
@@ -4527,57 +4518,19 @@
         <v>284</v>
       </c>
       <c r="H86" t="s">
-        <v>125</v>
+        <v>285</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K86">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="L86" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>286</v>
-      </c>
-      <c r="B87" t="s">
-        <v>140</v>
-      </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87">
-        <v>685551</v>
-      </c>
-      <c r="E87">
-        <v>4</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-      <c r="G87" t="s">
         <v>287</v>
-      </c>
-      <c r="H87" t="s">
-        <v>288</v>
-      </c>
-      <c r="I87" t="s">
-        <v>289</v>
-      </c>
-      <c r="J87" t="s">
-        <v>45</v>
-      </c>
-      <c r="K87">
-        <v>4200</v>
-      </c>
-      <c r="L87" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -538,7 +538,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,7 +592,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -638,7 +646,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -688,7 +700,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -738,7 +754,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -788,7 +808,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -838,7 +862,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -888,7 +916,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -938,7 +970,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -988,7 +1024,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1038,7 +1078,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1088,7 +1132,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1138,7 +1186,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1188,7 +1240,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1238,7 +1294,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1348,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1338,7 +1402,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1388,7 +1456,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1438,7 +1510,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1488,7 +1564,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1538,7 +1618,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1588,7 +1672,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1638,7 +1726,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1688,7 +1780,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1738,7 +1834,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1788,7 +1888,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1838,7 +1942,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1888,7 +1996,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1938,7 +2050,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1988,7 +2104,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2038,7 +2158,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2088,7 +2212,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2138,7 +2266,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2188,7 +2320,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2238,7 +2374,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2288,7 +2428,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2338,7 +2482,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2388,7 +2536,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2438,7 +2590,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2488,7 +2644,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2538,7 +2698,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2588,7 +2752,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2638,7 +2806,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2688,7 +2860,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2738,7 +2914,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2788,7 +2968,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2838,7 +3022,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2888,7 +3076,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2938,7 +3130,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2988,7 +3184,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3038,7 +3238,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3088,7 +3292,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3138,7 +3346,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3188,7 +3400,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3238,7 +3454,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3288,7 +3508,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3338,7 +3562,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3388,7 +3616,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3438,7 +3670,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3488,7 +3724,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3538,7 +3778,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3588,7 +3832,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3638,7 +3886,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3688,7 +3940,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3738,7 +3994,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3788,7 +4048,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3838,7 +4102,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3888,7 +4156,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3938,7 +4210,11 @@
           <t>Cadastrada</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3983,8 +4259,16 @@
           <t>LP-059482</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4029,8 +4313,16 @@
           <t>LP-059481</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4075,8 +4367,16 @@
           <t>LP-059483</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4121,8 +4421,16 @@
           <t>LP-059484</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4167,8 +4475,16 @@
           <t>LP-059485</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4213,8 +4529,16 @@
           <t>LP-059486</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4259,8 +4583,16 @@
           <t>LP-059487</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4305,8 +4637,16 @@
           <t>LP-059488</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4351,8 +4691,16 @@
           <t>LP-059353</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4397,8 +4745,16 @@
           <t>LP-059324</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4443,8 +4799,16 @@
           <t>LP-059354</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4489,8 +4853,16 @@
           <t>LP-059355</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4535,8 +4907,16 @@
           <t>LP-059356</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4581,8 +4961,16 @@
           <t>LP-059360</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4627,8 +5015,16 @@
           <t>LP-059323</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4673,8 +5069,16 @@
           <t>LP-059361</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4719,8 +5123,16 @@
           <t>LP-059322</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4765,8 +5177,16 @@
           <t>LP-059254</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4811,8 +5231,16 @@
           <t>LP-059362</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4857,8 +5285,16 @@
           <t>LP-059349</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4903,8 +5339,16 @@
           <t>LP-059499</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4949,8 +5393,16 @@
           <t>LP-059363</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4995,8 +5447,16 @@
           <t>LP-059366</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5041,8 +5501,16 @@
           <t>LP-059350</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5087,8 +5555,16 @@
           <t>LP-059367</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5133,8 +5609,16 @@
           <t>LP-059368</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5179,8 +5663,16 @@
           <t>LP-059371</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5225,8 +5717,16 @@
           <t>LP-059372</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5271,8 +5771,16 @@
           <t>LP-059373</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5317,8 +5825,16 @@
           <t>LP-059501</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5363,8 +5879,16 @@
           <t>LP-059516</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5409,8 +5933,16 @@
           <t>LP-059508</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5455,8 +5987,16 @@
           <t>LP-059507</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5501,8 +6041,16 @@
           <t>LP-059509</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5547,8 +6095,16 @@
           <t>LP-059510</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5593,8 +6149,16 @@
           <t>LP-059511</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5639,8 +6203,16 @@
           <t>LP-059512</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5685,8 +6257,16 @@
           <t>LP-059515</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5731,8 +6311,16 @@
           <t>LP-059514</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5777,8 +6365,16 @@
           <t>LP-059513</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5823,8 +6419,16 @@
           <t>LP-059456</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Cadastrada</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBB1494-12ED-4B70-81EA-70A62FF210ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9061E7E-2BB1-4FD5-929F-F89488B25601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="887">
   <si>
     <t>Responsável</t>
   </si>
@@ -1750,430 +1750,430 @@
     <t>Edson Bento</t>
   </si>
   <si>
+    <t>685614</t>
+  </si>
+  <si>
+    <t>CONFECÇÃO GARRA DO ROBÔ - 4725800081</t>
+  </si>
+  <si>
+    <t>LP-059619</t>
+  </si>
+  <si>
+    <t>4711401145</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 2</t>
+  </si>
+  <si>
+    <t>SIG8CT</t>
+  </si>
+  <si>
+    <t>LP-059063</t>
+  </si>
+  <si>
+    <t>LP-059123</t>
+  </si>
+  <si>
+    <t>4711300472-PEÇA 0</t>
+  </si>
+  <si>
+    <t>RETRABALHOS DE PINOS DO DISPOSITIVO GM</t>
+  </si>
+  <si>
+    <t>LP-059535</t>
+  </si>
+  <si>
+    <t>LP-059644</t>
+  </si>
+  <si>
+    <t>Thais Fischer</t>
+  </si>
+  <si>
+    <t>685701</t>
+  </si>
+  <si>
+    <t>4711801626</t>
+  </si>
+  <si>
+    <t>HOLDER 626</t>
+  </si>
+  <si>
+    <t>LP-057076</t>
+  </si>
+  <si>
+    <t>4710900938</t>
+  </si>
+  <si>
+    <t>Ponteira prensa</t>
+  </si>
+  <si>
+    <t>JOAO</t>
+  </si>
+  <si>
+    <t>LP-057171</t>
+  </si>
+  <si>
+    <t>S/ NORMA</t>
+  </si>
+  <si>
+    <t>CONTRA PONTO STUDER BRUNIMENTO</t>
+  </si>
+  <si>
+    <t>ANA LUZTEF11</t>
+  </si>
+  <si>
+    <t>LP-057582</t>
+  </si>
+  <si>
+    <t>LP-057727</t>
+  </si>
+  <si>
+    <t>4729109889</t>
+  </si>
+  <si>
+    <t>Posição 13 - Urgente</t>
+  </si>
+  <si>
+    <t>VIM6CT</t>
+  </si>
+  <si>
+    <t>LP-057706</t>
+  </si>
+  <si>
+    <t>Posição 13 - Não Urgente</t>
+  </si>
+  <si>
+    <t>LP-057707</t>
+  </si>
+  <si>
+    <t>4728800791-POS.23</t>
+  </si>
+  <si>
+    <t>Retrabalho disp flex</t>
+  </si>
+  <si>
+    <t>LP-057840</t>
+  </si>
+  <si>
+    <t>Retrabalho disp est.20 válvula</t>
+  </si>
+  <si>
+    <t>LP-057839</t>
+  </si>
+  <si>
+    <t>Retrabalho disp est.30</t>
+  </si>
+  <si>
+    <t>LP-057838</t>
+  </si>
+  <si>
+    <t>CONSERTO ADAPTADOR CAPTO C5 ZOLLER</t>
+  </si>
+  <si>
+    <t>GUILHERME</t>
+  </si>
+  <si>
+    <t>LP-057867</t>
+  </si>
+  <si>
+    <t>Retirar material da face demarcada</t>
+  </si>
+  <si>
+    <t>LP-058586</t>
+  </si>
+  <si>
+    <t>Fazer furo M4 na face marcada em azul</t>
+  </si>
+  <si>
+    <t>LP-058536</t>
+  </si>
+  <si>
+    <t>4728800791- POS23</t>
+  </si>
+  <si>
+    <t>Retrabalho furo p/ 12mm</t>
+  </si>
+  <si>
+    <t>LP-058864</t>
+  </si>
+  <si>
+    <t>LP-059348</t>
+  </si>
+  <si>
+    <t>685618</t>
+  </si>
+  <si>
+    <t>Retrabalhar bit st 50</t>
+  </si>
+  <si>
+    <t>LP-059401</t>
+  </si>
+  <si>
+    <t>LP-059576</t>
+  </si>
+  <si>
+    <t>Fresar suportes - retirar impurezas</t>
+  </si>
+  <si>
+    <t>LP-059637</t>
+  </si>
+  <si>
+    <t>Joao Franca</t>
+  </si>
+  <si>
+    <t>4729.106.486</t>
+  </si>
+  <si>
+    <t>DU 685411 M.PREVENTIVA/MONTAGEM ROLDANA.</t>
+  </si>
+  <si>
+    <t>LP-054434</t>
+  </si>
+  <si>
+    <t>HOLDER S/ NORMA</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>LP-055172</t>
+  </si>
+  <si>
+    <t>LP-055171</t>
+  </si>
+  <si>
+    <t>RETRABALHO HOLDERS 626</t>
+  </si>
+  <si>
+    <t>LP-055479</t>
+  </si>
+  <si>
+    <t>4711801628</t>
+  </si>
+  <si>
+    <t>HOLDER 628</t>
+  </si>
+  <si>
+    <t>LP-055466</t>
+  </si>
+  <si>
+    <t>4711901626</t>
+  </si>
+  <si>
+    <t>LP-055467</t>
+  </si>
+  <si>
+    <t>4702500507_006</t>
+  </si>
+  <si>
+    <t>ELETRODO</t>
+  </si>
+  <si>
+    <t>LP-055971</t>
+  </si>
+  <si>
+    <t>4702500416_006</t>
+  </si>
+  <si>
+    <t>LP-055972</t>
+  </si>
+  <si>
+    <t>4702500594_010</t>
+  </si>
+  <si>
+    <t>LP-055973</t>
+  </si>
+  <si>
+    <t>LP-055557</t>
+  </si>
+  <si>
+    <t>LP-055558</t>
+  </si>
+  <si>
+    <t>LP-056317</t>
+  </si>
+  <si>
+    <t>LP-056316</t>
+  </si>
+  <si>
+    <t>4711500207</t>
+  </si>
+  <si>
+    <t>Placa Chiron n°-190 e n°191</t>
+  </si>
+  <si>
+    <t>LP-056561</t>
+  </si>
+  <si>
     <t>Error</t>
   </si>
   <si>
+    <t>4727501185</t>
+  </si>
+  <si>
+    <t>Dispositivo UP</t>
+  </si>
+  <si>
+    <t>LP-057223</t>
+  </si>
+  <si>
+    <t>4729106486</t>
+  </si>
+  <si>
+    <t>DU 685411 Retrabalho e Montagem Roldanas</t>
+  </si>
+  <si>
+    <t>LP-057285</t>
+  </si>
+  <si>
+    <t>685431</t>
+  </si>
+  <si>
+    <t>4729.108.508</t>
+  </si>
+  <si>
+    <t>DU 685431 ROLDANAS RETIF. CHANFRO BICO S</t>
+  </si>
+  <si>
+    <t>LP-059039</t>
+  </si>
+  <si>
+    <t>DU 685411 Retrab.Montagem Roldana Us.dur</t>
+  </si>
+  <si>
+    <t>LP-059268</t>
+  </si>
+  <si>
+    <t>4711500202</t>
+  </si>
+  <si>
+    <t>Posição 2</t>
+  </si>
+  <si>
+    <t>LP-059494</t>
+  </si>
+  <si>
+    <t>LP-059495</t>
+  </si>
+  <si>
+    <t>LP-059560</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>4710900885</t>
+  </si>
+  <si>
+    <t>Disp. destorque familia 12</t>
+  </si>
+  <si>
+    <t>LP-059552</t>
+  </si>
+  <si>
+    <t>685616</t>
+  </si>
+  <si>
+    <t>4711400741</t>
+  </si>
+  <si>
+    <t>Castanhas do Escovamento</t>
+  </si>
+  <si>
+    <t>LP-059621</t>
+  </si>
+  <si>
+    <t>4741420031</t>
+  </si>
+  <si>
+    <t>Ponteira de MT</t>
+  </si>
+  <si>
+    <t>LP-059609</t>
+  </si>
+  <si>
+    <t>4712003182/POS4</t>
+  </si>
+  <si>
+    <t>Pino Guia da Mesa</t>
+  </si>
+  <si>
+    <t>LP-059603</t>
+  </si>
+  <si>
+    <t>4712002217</t>
+  </si>
+  <si>
+    <t>Separador ATMO</t>
+  </si>
+  <si>
+    <t>LP-059610</t>
+  </si>
+  <si>
+    <t>4729107112</t>
+  </si>
+  <si>
+    <t>Separador Universal Válvula</t>
+  </si>
+  <si>
+    <t>LP-059604</t>
+  </si>
+  <si>
+    <t>4711401002</t>
+  </si>
+  <si>
+    <t>Castanha Supfina - Fabricação</t>
+  </si>
+  <si>
+    <t>LP-059607</t>
+  </si>
+  <si>
+    <t>4711400985</t>
+  </si>
+  <si>
+    <t>LP-059606</t>
+  </si>
+  <si>
+    <t>4711400848</t>
+  </si>
+  <si>
+    <t>LP-059605</t>
+  </si>
+  <si>
+    <t>685491</t>
+  </si>
+  <si>
+    <t>4711202060_POS-9</t>
+  </si>
+  <si>
+    <t>IP-685491 POSIÇÃO 9 Folha 10(Mola Slee.)</t>
+  </si>
+  <si>
+    <t>LP-059528</t>
+  </si>
+  <si>
+    <t>685546</t>
+  </si>
+  <si>
+    <t>4729111841</t>
+  </si>
+  <si>
+    <t>Régua STH</t>
+  </si>
+  <si>
+    <t>LP-059529</t>
+  </si>
+  <si>
+    <t>4712001363</t>
+  </si>
+  <si>
+    <t>BLISTER VALVULA UP - Marrom</t>
+  </si>
+  <si>
+    <t>MARCO VIEIRA</t>
+  </si>
+  <si>
     <t>CtP/MFE11</t>
-  </si>
-  <si>
-    <t>685431</t>
-  </si>
-  <si>
-    <t>685618</t>
-  </si>
-  <si>
-    <t>685616</t>
-  </si>
-  <si>
-    <t>685614</t>
-  </si>
-  <si>
-    <t>CONFECÇÃO GARRA DO ROBÔ - 4725800081</t>
-  </si>
-  <si>
-    <t>LP-059619</t>
-  </si>
-  <si>
-    <t>4711401145</t>
-  </si>
-  <si>
-    <t>POSIÇÃO 2</t>
-  </si>
-  <si>
-    <t>SIG8CT</t>
-  </si>
-  <si>
-    <t>LP-059063</t>
-  </si>
-  <si>
-    <t>LP-059123</t>
-  </si>
-  <si>
-    <t>4711300472-PEÇA 0</t>
-  </si>
-  <si>
-    <t>RETRABALHOS DE PINOS DO DISPOSITIVO GM</t>
-  </si>
-  <si>
-    <t>LP-059535</t>
-  </si>
-  <si>
-    <t>LP-059644</t>
-  </si>
-  <si>
-    <t>Thais Fischer</t>
-  </si>
-  <si>
-    <t>685701</t>
-  </si>
-  <si>
-    <t>4711801626</t>
-  </si>
-  <si>
-    <t>HOLDER 626</t>
-  </si>
-  <si>
-    <t>LP-057076</t>
-  </si>
-  <si>
-    <t>4710900938</t>
-  </si>
-  <si>
-    <t>Ponteira prensa</t>
-  </si>
-  <si>
-    <t>JOAO</t>
-  </si>
-  <si>
-    <t>LP-057171</t>
-  </si>
-  <si>
-    <t>S/ NORMA</t>
-  </si>
-  <si>
-    <t>CONTRA PONTO STUDER BRUNIMENTO</t>
-  </si>
-  <si>
-    <t>ANA LUZTEF11</t>
-  </si>
-  <si>
-    <t>LP-057582</t>
-  </si>
-  <si>
-    <t>LP-057727</t>
-  </si>
-  <si>
-    <t>4729109889</t>
-  </si>
-  <si>
-    <t>Posição 13 - Urgente</t>
-  </si>
-  <si>
-    <t>VIM6CT</t>
-  </si>
-  <si>
-    <t>LP-057706</t>
-  </si>
-  <si>
-    <t>Posição 13 - Não Urgente</t>
-  </si>
-  <si>
-    <t>LP-057707</t>
-  </si>
-  <si>
-    <t>4728800791-POS.23</t>
-  </si>
-  <si>
-    <t>Retrabalho disp flex</t>
-  </si>
-  <si>
-    <t>LP-057840</t>
-  </si>
-  <si>
-    <t>Retrabalho disp est.20 válvula</t>
-  </si>
-  <si>
-    <t>LP-057839</t>
-  </si>
-  <si>
-    <t>Retrabalho disp est.30</t>
-  </si>
-  <si>
-    <t>LP-057838</t>
-  </si>
-  <si>
-    <t>CONSERTO ADAPTADOR CAPTO C5 ZOLLER</t>
-  </si>
-  <si>
-    <t>GUILHERME</t>
-  </si>
-  <si>
-    <t>LP-057867</t>
-  </si>
-  <si>
-    <t>Retirar material da face demarcada</t>
-  </si>
-  <si>
-    <t>LP-058586</t>
-  </si>
-  <si>
-    <t>Fazer furo M4 na face marcada em azul</t>
-  </si>
-  <si>
-    <t>LP-058536</t>
-  </si>
-  <si>
-    <t>4728800791- POS23</t>
-  </si>
-  <si>
-    <t>Retrabalho furo p/ 12mm</t>
-  </si>
-  <si>
-    <t>LP-058864</t>
-  </si>
-  <si>
-    <t>LP-059348</t>
-  </si>
-  <si>
-    <t>Retrabalhar bit st 50</t>
-  </si>
-  <si>
-    <t>LP-059401</t>
-  </si>
-  <si>
-    <t>LP-059576</t>
-  </si>
-  <si>
-    <t>Fresar suportes - retirar impurezas</t>
-  </si>
-  <si>
-    <t>LP-059637</t>
-  </si>
-  <si>
-    <t>Joao Franca</t>
-  </si>
-  <si>
-    <t>4729.106.486</t>
-  </si>
-  <si>
-    <t>DU 685411 M.PREVENTIVA/MONTAGEM ROLDANA.</t>
-  </si>
-  <si>
-    <t>LP-054434</t>
-  </si>
-  <si>
-    <t>HOLDER S/ NORMA</t>
-  </si>
-  <si>
-    <t>REGIMARA</t>
-  </si>
-  <si>
-    <t>LP-055172</t>
-  </si>
-  <si>
-    <t>LP-055171</t>
-  </si>
-  <si>
-    <t>RETRABALHO HOLDERS 626</t>
-  </si>
-  <si>
-    <t>LP-055479</t>
-  </si>
-  <si>
-    <t>4711801628</t>
-  </si>
-  <si>
-    <t>HOLDER 628</t>
-  </si>
-  <si>
-    <t>LP-055466</t>
-  </si>
-  <si>
-    <t>4711901626</t>
-  </si>
-  <si>
-    <t>LP-055467</t>
-  </si>
-  <si>
-    <t>4702500507_006</t>
-  </si>
-  <si>
-    <t>ELETRODO</t>
-  </si>
-  <si>
-    <t>LP-055971</t>
-  </si>
-  <si>
-    <t>4702500416_006</t>
-  </si>
-  <si>
-    <t>LP-055972</t>
-  </si>
-  <si>
-    <t>4702500594_010</t>
-  </si>
-  <si>
-    <t>LP-055973</t>
-  </si>
-  <si>
-    <t>LP-055557</t>
-  </si>
-  <si>
-    <t>LP-055558</t>
-  </si>
-  <si>
-    <t>LP-056317</t>
-  </si>
-  <si>
-    <t>LP-056316</t>
-  </si>
-  <si>
-    <t>4711500207</t>
-  </si>
-  <si>
-    <t>Placa Chiron n°-190 e n°191</t>
-  </si>
-  <si>
-    <t>LP-056561</t>
-  </si>
-  <si>
-    <t>4727501185</t>
-  </si>
-  <si>
-    <t>Dispositivo UP</t>
-  </si>
-  <si>
-    <t>LP-057223</t>
-  </si>
-  <si>
-    <t>4729106486</t>
-  </si>
-  <si>
-    <t>DU 685411 Retrabalho e Montagem Roldanas</t>
-  </si>
-  <si>
-    <t>LP-057285</t>
-  </si>
-  <si>
-    <t>4729.108.508</t>
-  </si>
-  <si>
-    <t>DU 685431 ROLDANAS RETIF. CHANFRO BICO S</t>
-  </si>
-  <si>
-    <t>LP-059039</t>
-  </si>
-  <si>
-    <t>DU 685411 Retrab.Montagem Roldana Us.dur</t>
-  </si>
-  <si>
-    <t>LP-059268</t>
-  </si>
-  <si>
-    <t>4711500202</t>
-  </si>
-  <si>
-    <t>Posição 2</t>
-  </si>
-  <si>
-    <t>LP-059494</t>
-  </si>
-  <si>
-    <t>LP-059495</t>
-  </si>
-  <si>
-    <t>LP-059560</t>
-  </si>
-  <si>
-    <t>Yesica Gonzalez</t>
-  </si>
-  <si>
-    <t>4710900885</t>
-  </si>
-  <si>
-    <t>Disp. destorque familia 12</t>
-  </si>
-  <si>
-    <t>LP-059552</t>
-  </si>
-  <si>
-    <t>4711400741</t>
-  </si>
-  <si>
-    <t>Castanhas do Escovamento</t>
-  </si>
-  <si>
-    <t>LP-059621</t>
-  </si>
-  <si>
-    <t>4741420031</t>
-  </si>
-  <si>
-    <t>Ponteira de MT</t>
-  </si>
-  <si>
-    <t>LP-059609</t>
-  </si>
-  <si>
-    <t>4712003182/POS4</t>
-  </si>
-  <si>
-    <t>Pino Guia da Mesa</t>
-  </si>
-  <si>
-    <t>LP-059603</t>
-  </si>
-  <si>
-    <t>4712002217</t>
-  </si>
-  <si>
-    <t>Separador ATMO</t>
-  </si>
-  <si>
-    <t>LP-059610</t>
-  </si>
-  <si>
-    <t>4729107112</t>
-  </si>
-  <si>
-    <t>Separador Universal Válvula</t>
-  </si>
-  <si>
-    <t>LP-059604</t>
-  </si>
-  <si>
-    <t>4711401002</t>
-  </si>
-  <si>
-    <t>Castanha Supfina - Fabricação</t>
-  </si>
-  <si>
-    <t>LP-059607</t>
-  </si>
-  <si>
-    <t>4711400985</t>
-  </si>
-  <si>
-    <t>LP-059606</t>
-  </si>
-  <si>
-    <t>4711400848</t>
-  </si>
-  <si>
-    <t>LP-059605</t>
-  </si>
-  <si>
-    <t>685491</t>
-  </si>
-  <si>
-    <t>4711202060_POS-9</t>
-  </si>
-  <si>
-    <t>IP-685491 POSIÇÃO 9 Folha 10(Mola Slee.)</t>
-  </si>
-  <si>
-    <t>LP-059528</t>
-  </si>
-  <si>
-    <t>685546</t>
-  </si>
-  <si>
-    <t>4729111841</t>
-  </si>
-  <si>
-    <t>Régua STH</t>
-  </si>
-  <si>
-    <t>LP-059529</t>
-  </si>
-  <si>
-    <t>4712001363</t>
-  </si>
-  <si>
-    <t>BLISTER VALVULA UP - Marrom</t>
-  </si>
-  <si>
-    <t>MARCO VIEIRA</t>
   </si>
   <si>
     <t>LP-059579</t>
@@ -3176,6 +3176,9 @@
       <c r="K2" t="s">
         <v>26</v>
       </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
       <c r="N2" t="s">
         <v>13</v>
       </c>
@@ -3241,6 +3244,9 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
       <c r="N3" t="s">
         <v>13</v>
       </c>
@@ -3306,6 +3312,9 @@
       <c r="K4" t="s">
         <v>26</v>
       </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
       <c r="N4" t="s">
         <v>13</v>
       </c>
@@ -3371,6 +3380,9 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
       <c r="N5" t="s">
         <v>13</v>
       </c>
@@ -3430,6 +3442,9 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
       <c r="N6" t="s">
         <v>13</v>
       </c>
@@ -3495,6 +3510,9 @@
       <c r="K7" t="s">
         <v>26</v>
       </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
       <c r="N7" t="s">
         <v>13</v>
       </c>
@@ -3557,6 +3575,9 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
       <c r="N8" t="s">
         <v>13</v>
       </c>
@@ -3622,6 +3643,9 @@
       <c r="K9" t="s">
         <v>26</v>
       </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
       <c r="N9" t="s">
         <v>13</v>
       </c>
@@ -3684,6 +3708,9 @@
       <c r="K10" t="s">
         <v>26</v>
       </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
       <c r="N10" t="s">
         <v>13</v>
       </c>
@@ -3746,6 +3773,9 @@
       <c r="K11" t="s">
         <v>26</v>
       </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
       <c r="N11" t="s">
         <v>13</v>
       </c>
@@ -3808,6 +3838,9 @@
       <c r="K12" t="s">
         <v>26</v>
       </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
       <c r="N12" t="s">
         <v>13</v>
       </c>
@@ -3873,6 +3906,9 @@
       <c r="K13" t="s">
         <v>26</v>
       </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
       <c r="N13" t="s">
         <v>13</v>
       </c>
@@ -3935,6 +3971,9 @@
       <c r="K14" t="s">
         <v>26</v>
       </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
       <c r="N14" t="s">
         <v>13</v>
       </c>
@@ -3997,6 +4036,9 @@
       <c r="K15" t="s">
         <v>26</v>
       </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
       <c r="N15" t="s">
         <v>13</v>
       </c>
@@ -4059,6 +4101,9 @@
       <c r="K16" t="s">
         <v>26</v>
       </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
       <c r="N16" t="s">
         <v>13</v>
       </c>
@@ -4124,6 +4169,9 @@
       <c r="K17" t="s">
         <v>26</v>
       </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
       <c r="N17" t="s">
         <v>13</v>
       </c>
@@ -4189,6 +4237,9 @@
       <c r="K18" t="s">
         <v>26</v>
       </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
       <c r="N18" t="s">
         <v>13</v>
       </c>
@@ -4254,6 +4305,9 @@
       <c r="K19" t="s">
         <v>26</v>
       </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
       <c r="N19" t="s">
         <v>13</v>
       </c>
@@ -4316,6 +4370,9 @@
       <c r="K20" t="s">
         <v>26</v>
       </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -4351,6 +4408,9 @@
       <c r="K21" t="s">
         <v>26</v>
       </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -4386,6 +4446,9 @@
       <c r="K22" t="s">
         <v>26</v>
       </c>
+      <c r="L22" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -4421,6 +4484,9 @@
       <c r="K23" t="s">
         <v>26</v>
       </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -4456,6 +4522,9 @@
       <c r="K24" t="s">
         <v>26</v>
       </c>
+      <c r="L24" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -4491,6 +4560,9 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
+      <c r="L25" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -4526,6 +4598,9 @@
       <c r="K26" t="s">
         <v>26</v>
       </c>
+      <c r="L26" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -4561,6 +4636,9 @@
       <c r="K27" t="s">
         <v>26</v>
       </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -4596,6 +4674,9 @@
       <c r="K28" t="s">
         <v>26</v>
       </c>
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -4631,6 +4712,9 @@
       <c r="K29" t="s">
         <v>26</v>
       </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -4663,6 +4747,9 @@
       <c r="K30" t="s">
         <v>26</v>
       </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -4698,6 +4785,9 @@
       <c r="K31" t="s">
         <v>26</v>
       </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -4733,8 +4823,11 @@
       <c r="K32" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -4768,8 +4861,11 @@
       <c r="K33" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -4803,8 +4899,11 @@
       <c r="K34" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -4838,8 +4937,11 @@
       <c r="K35" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -4873,8 +4975,11 @@
       <c r="K36" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -4908,8 +5013,11 @@
       <c r="K37" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -4943,8 +5051,11 @@
       <c r="K38" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -4978,8 +5089,11 @@
       <c r="K39" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -5013,8 +5127,11 @@
       <c r="K40" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -5048,8 +5165,11 @@
       <c r="K41" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -5080,8 +5200,11 @@
       <c r="K42" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -5112,8 +5235,11 @@
       <c r="K43" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -5147,8 +5273,11 @@
       <c r="K44" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -5182,8 +5311,11 @@
       <c r="K45" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -5217,8 +5349,11 @@
       <c r="K46" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -5252,8 +5387,11 @@
       <c r="K47" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -5287,8 +5425,11 @@
       <c r="K48" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -5322,8 +5463,11 @@
       <c r="K49" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -5354,8 +5498,11 @@
       <c r="K50" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -5386,8 +5533,11 @@
       <c r="K51" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -5421,8 +5571,11 @@
       <c r="K52" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -5456,8 +5609,11 @@
       <c r="K53" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -5491,8 +5647,11 @@
       <c r="K54" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -5526,8 +5685,11 @@
       <c r="K55" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -5561,8 +5723,11 @@
       <c r="K56" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -5593,8 +5758,11 @@
       <c r="K57" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -5625,8 +5793,11 @@
       <c r="K58" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -5657,8 +5828,11 @@
       <c r="K59" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -5692,8 +5866,11 @@
       <c r="K60" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -5727,8 +5904,11 @@
       <c r="K61" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -5762,8 +5942,11 @@
       <c r="K62" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -5794,8 +5977,11 @@
       <c r="K63" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -5829,8 +6015,11 @@
       <c r="K64" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -5861,8 +6050,11 @@
       <c r="K65" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -5893,8 +6085,11 @@
       <c r="K66" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -5928,8 +6123,11 @@
       <c r="K67" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -5963,8 +6161,11 @@
       <c r="K68" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -5998,8 +6199,11 @@
       <c r="K69" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>13</v>
       </c>
@@ -6033,8 +6237,11 @@
       <c r="K70" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -6065,8 +6272,11 @@
       <c r="K71" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -6100,8 +6310,11 @@
       <c r="K72" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -6135,8 +6348,11 @@
       <c r="K73" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -6170,8 +6386,11 @@
       <c r="K74" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -6205,8 +6424,11 @@
       <c r="K75" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -6240,8 +6462,11 @@
       <c r="K76" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -6275,8 +6500,11 @@
       <c r="K77" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -6310,8 +6538,11 @@
       <c r="K78" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>13</v>
       </c>
@@ -6345,8 +6576,11 @@
       <c r="K79" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>13</v>
       </c>
@@ -6377,8 +6611,11 @@
       <c r="K80" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L80" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>13</v>
       </c>
@@ -6412,8 +6649,11 @@
       <c r="K81" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>13</v>
       </c>
@@ -6447,8 +6687,11 @@
       <c r="K82" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L82" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>13</v>
       </c>
@@ -6482,8 +6725,11 @@
       <c r="K83" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L83" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>13</v>
       </c>
@@ -6517,8 +6763,11 @@
       <c r="K84" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -6552,8 +6801,11 @@
       <c r="K85" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -6587,8 +6839,11 @@
       <c r="K86" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -6622,8 +6877,11 @@
       <c r="K87" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -6657,8 +6915,11 @@
       <c r="K88" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -6692,8 +6953,11 @@
       <c r="K89" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -6727,8 +6991,11 @@
       <c r="K90" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>13</v>
       </c>
@@ -6759,8 +7026,11 @@
       <c r="K91" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -6794,8 +7064,11 @@
       <c r="K92" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -6829,8 +7102,11 @@
       <c r="K93" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>13</v>
       </c>
@@ -6861,8 +7137,11 @@
       <c r="K94" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L94" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>13</v>
       </c>
@@ -6896,8 +7175,11 @@
       <c r="K95" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -6931,8 +7213,11 @@
       <c r="K96" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>13</v>
       </c>
@@ -6966,8 +7251,11 @@
       <c r="K97" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -7001,8 +7289,11 @@
       <c r="K98" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L98" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -7033,8 +7324,11 @@
       <c r="K99" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>13</v>
       </c>
@@ -7068,8 +7362,11 @@
       <c r="K100" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -7103,8 +7400,11 @@
       <c r="K101" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -7138,8 +7438,11 @@
       <c r="K102" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -7170,8 +7473,11 @@
       <c r="K103" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -7202,8 +7508,11 @@
       <c r="K104" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -7237,8 +7546,11 @@
       <c r="K105" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -7272,8 +7584,11 @@
       <c r="K106" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>13</v>
       </c>
@@ -7307,8 +7622,11 @@
       <c r="K107" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -7342,8 +7660,11 @@
       <c r="K108" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>13</v>
       </c>
@@ -7374,8 +7695,11 @@
       <c r="K109" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L109" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -7409,8 +7733,11 @@
       <c r="K110" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -7444,8 +7771,11 @@
       <c r="K111" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -7476,8 +7806,11 @@
       <c r="K112" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L112" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -7511,8 +7844,11 @@
       <c r="K113" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L113" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -7543,8 +7879,11 @@
       <c r="K114" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -7578,8 +7917,11 @@
       <c r="K115" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L115" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -7613,8 +7955,11 @@
       <c r="K116" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L116" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -7648,8 +7993,11 @@
       <c r="K117" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L117" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>13</v>
       </c>
@@ -7680,8 +8028,11 @@
       <c r="K118" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L118" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -7715,8 +8066,11 @@
       <c r="K119" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -7747,8 +8101,11 @@
       <c r="K120" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L120" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>13</v>
       </c>
@@ -7782,8 +8139,11 @@
       <c r="K121" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L121" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -7817,8 +8177,11 @@
       <c r="K122" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L122" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -7852,8 +8215,11 @@
       <c r="K123" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -7887,8 +8253,11 @@
       <c r="K124" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L124" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -7922,8 +8291,11 @@
       <c r="K125" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -7957,8 +8329,11 @@
       <c r="K126" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -7992,8 +8367,11 @@
       <c r="K127" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L127" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -8027,8 +8405,11 @@
       <c r="K128" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L128" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -8062,8 +8443,11 @@
       <c r="K129" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L129" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -8094,8 +8478,11 @@
       <c r="K130" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L130" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -8129,8 +8516,11 @@
       <c r="K131" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L131" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -8164,8 +8554,11 @@
       <c r="K132" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L132" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -8199,8 +8592,11 @@
       <c r="K133" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -8234,8 +8630,11 @@
       <c r="K134" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L134" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -8269,8 +8668,11 @@
       <c r="K135" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L135" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -8301,8 +8703,11 @@
       <c r="K136" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L136" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -8336,8 +8741,11 @@
       <c r="K137" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L137" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -8371,8 +8779,11 @@
       <c r="K138" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L138" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -8406,8 +8817,11 @@
       <c r="K139" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L139" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -8441,8 +8855,11 @@
       <c r="K140" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L140" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -8476,8 +8893,11 @@
       <c r="K141" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L141" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -8511,8 +8931,11 @@
       <c r="K142" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L142" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -8546,8 +8969,11 @@
       <c r="K143" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L143" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -8581,8 +9007,11 @@
       <c r="K144" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L144" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -8616,8 +9045,11 @@
       <c r="K145" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L145" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -8651,8 +9083,11 @@
       <c r="K146" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L146" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -8683,13 +9118,16 @@
       <c r="K147" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L147" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>575</v>
       </c>
       <c r="B148" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C148">
         <v>19</v>
@@ -8701,7 +9139,7 @@
         <v>28</v>
       </c>
       <c r="F148" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="G148" t="s">
         <v>503</v>
@@ -8713,13 +9151,16 @@
         <v>1500</v>
       </c>
       <c r="J148" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="K148" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L148" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>575</v>
       </c>
@@ -8733,13 +9174,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F149" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G149" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H149" t="s">
         <v>95</v>
@@ -8748,13 +9189,16 @@
         <v>500</v>
       </c>
       <c r="J149" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="K149" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L149" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>575</v>
       </c>
@@ -8768,13 +9212,13 @@
         <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F150" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G150" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H150" t="s">
         <v>95</v>
@@ -8783,13 +9227,16 @@
         <v>0.01</v>
       </c>
       <c r="J150" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="K150" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L150" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>575</v>
       </c>
@@ -8803,10 +9250,10 @@
         <v>28</v>
       </c>
       <c r="E151" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="F151" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G151" t="s">
         <v>305</v>
@@ -8818,13 +9265,16 @@
         <v>800</v>
       </c>
       <c r="J151" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="K151" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L151" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>575</v>
       </c>
@@ -8853,18 +9303,21 @@
         <v>1000</v>
       </c>
       <c r="J152" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="K152" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L152" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B153" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C153">
         <v>19</v>
@@ -8873,13 +9326,13 @@
         <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F153" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G153" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H153" t="s">
         <v>52</v>
@@ -8888,15 +9341,18 @@
         <v>5000</v>
       </c>
       <c r="J153" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="K153" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L153" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B154" t="s">
         <v>142</v>
@@ -8908,13 +9364,13 @@
         <v>5</v>
       </c>
       <c r="E154" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="F154" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="G154" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="H154" t="s">
         <v>78</v>
@@ -8923,15 +9379,18 @@
         <v>500</v>
       </c>
       <c r="J154" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="K154" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L154" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s">
         <v>264</v>
@@ -8943,13 +9402,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="F155" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G155" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="H155" t="s">
         <v>37</v>
@@ -8958,15 +9417,18 @@
         <v>300</v>
       </c>
       <c r="J155" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="K155" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L155" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B156" t="s">
         <v>410</v>
@@ -8993,15 +9455,18 @@
         <v>300</v>
       </c>
       <c r="J156" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="K156" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L156" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B157" t="s">
         <v>258</v>
@@ -9013,13 +9478,13 @@
         <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="F157" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G157" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="H157" t="s">
         <v>95</v>
@@ -9028,15 +9493,18 @@
         <v>500</v>
       </c>
       <c r="J157" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="K157" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L157" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B158" t="s">
         <v>258</v>
@@ -9048,13 +9516,13 @@
         <v>10</v>
       </c>
       <c r="E158" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="F158" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G158" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="H158" t="s">
         <v>95</v>
@@ -9063,15 +9531,18 @@
         <v>500</v>
       </c>
       <c r="J158" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="K158" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L158" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B159" t="s">
         <v>113</v>
@@ -9083,10 +9554,10 @@
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F159" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G159" t="s">
         <v>135</v>
@@ -9098,15 +9569,18 @@
         <v>300</v>
       </c>
       <c r="J159" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="K159" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L159" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B160" t="s">
         <v>113</v>
@@ -9118,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G160" t="s">
         <v>135</v>
@@ -9130,15 +9604,18 @@
         <v>300</v>
       </c>
       <c r="J160" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="K160" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L160" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B161" t="s">
         <v>113</v>
@@ -9150,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="G161" t="s">
         <v>135</v>
@@ -9162,15 +9639,18 @@
         <v>300</v>
       </c>
       <c r="J161" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="K161" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L161" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B162" t="s">
         <v>465</v>
@@ -9182,10 +9662,10 @@
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="G162" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="H162" t="s">
         <v>37</v>
@@ -9194,15 +9674,18 @@
         <v>500</v>
       </c>
       <c r="J162" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="K162" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L162" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B163" t="s">
         <v>113</v>
@@ -9214,7 +9697,7 @@
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="G163" t="s">
         <v>135</v>
@@ -9226,15 +9709,18 @@
         <v>500</v>
       </c>
       <c r="J163" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="K163" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L163" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B164" t="s">
         <v>113</v>
@@ -9246,7 +9732,7 @@
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G164" t="s">
         <v>135</v>
@@ -9258,15 +9744,18 @@
         <v>500</v>
       </c>
       <c r="J164" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="K164" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L164" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B165" t="s">
         <v>113</v>
@@ -9278,10 +9767,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="F165" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G165" t="s">
         <v>135</v>
@@ -9293,15 +9782,18 @@
         <v>300</v>
       </c>
       <c r="J165" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="K165" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B166" t="s">
         <v>168</v>
@@ -9328,18 +9820,21 @@
         <v>600</v>
       </c>
       <c r="J166" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K166" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L166" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B167" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -9348,7 +9843,7 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G167" t="s">
         <v>135</v>
@@ -9360,15 +9855,18 @@
         <v>600</v>
       </c>
       <c r="J167" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="K167" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L167" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B168" t="s">
         <v>92</v>
@@ -9395,15 +9893,18 @@
         <v>700</v>
       </c>
       <c r="J168" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="K168" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L168" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B169" t="s">
         <v>113</v>
@@ -9415,7 +9916,7 @@
         <v>3</v>
       </c>
       <c r="F169" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="G169" t="s">
         <v>135</v>
@@ -9427,15 +9928,18 @@
         <v>500</v>
       </c>
       <c r="J169" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="K169" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L169" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B170" t="s">
         <v>230</v>
@@ -9447,10 +9951,10 @@
         <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="F170" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G170" t="s">
         <v>392</v>
@@ -9462,18 +9966,21 @@
         <v>2500</v>
       </c>
       <c r="J170" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="K170" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L170" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B171" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C171">
         <v>19</v>
@@ -9482,10 +9989,10 @@
         <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G171" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H171" t="s">
         <v>37</v>
@@ -9494,18 +10001,21 @@
         <v>2500</v>
       </c>
       <c r="J171" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="K171" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L171" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B172" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C172">
         <v>19</v>
@@ -9514,10 +10024,10 @@
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G172" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H172" t="s">
         <v>37</v>
@@ -9526,18 +10036,21 @@
         <v>2500</v>
       </c>
       <c r="J172" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="K172" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L172" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B173" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C173">
         <v>19</v>
@@ -9546,13 +10059,13 @@
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F173" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="G173" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H173" t="s">
         <v>52</v>
@@ -9561,18 +10074,21 @@
         <v>1500</v>
       </c>
       <c r="J173" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="K173" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L173" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B174" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C174">
         <v>19</v>
@@ -9581,13 +10097,13 @@
         <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="F174" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G174" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H174" t="s">
         <v>52</v>
@@ -9596,18 +10112,21 @@
         <v>1500</v>
       </c>
       <c r="J174" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="K174" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L174" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B175" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C175">
         <v>19</v>
@@ -9616,13 +10135,13 @@
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F175" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G175" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H175" t="s">
         <v>52</v>
@@ -9631,15 +10150,18 @@
         <v>1500</v>
       </c>
       <c r="J175" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="K175" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L175" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B176" t="s">
         <v>482</v>
@@ -9651,10 +10173,10 @@
         <v>100</v>
       </c>
       <c r="E176" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F176" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G176" t="s">
         <v>70</v>
@@ -9666,15 +10188,18 @@
         <v>5100</v>
       </c>
       <c r="J176" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="K176" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L176" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B177" t="s">
         <v>482</v>
@@ -9686,10 +10211,10 @@
         <v>100</v>
       </c>
       <c r="E177" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F177" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G177" t="s">
         <v>70</v>
@@ -9701,15 +10226,18 @@
         <v>5100</v>
       </c>
       <c r="J177" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="K177" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L177" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B178" t="s">
         <v>482</v>
@@ -9721,10 +10249,10 @@
         <v>100</v>
       </c>
       <c r="E178" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="F178" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G178" t="s">
         <v>70</v>
@@ -9736,18 +10264,21 @@
         <v>6000</v>
       </c>
       <c r="J178" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="K178" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L178" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B179" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C179">
         <v>19</v>
@@ -9756,13 +10287,13 @@
         <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="F179" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G179" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H179" t="s">
         <v>52</v>
@@ -9771,18 +10302,21 @@
         <v>1000</v>
       </c>
       <c r="J179" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="K179" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L179" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B180" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C180">
         <v>19</v>
@@ -9791,13 +10325,13 @@
         <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F180" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G180" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H180" t="s">
         <v>52</v>
@@ -9806,18 +10340,21 @@
         <v>1000</v>
       </c>
       <c r="J180" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="K180" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L180" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B181" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C181">
         <v>19</v>
@@ -9826,13 +10363,13 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F181" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G181" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H181" t="s">
         <v>52</v>
@@ -9841,18 +10378,21 @@
         <v>1500</v>
       </c>
       <c r="J181" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="K181" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L181" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B182" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C182">
         <v>19</v>
@@ -9861,13 +10401,13 @@
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="F182" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G182" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H182" t="s">
         <v>52</v>
@@ -9876,15 +10416,18 @@
         <v>1500</v>
       </c>
       <c r="J182" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="K182" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L182" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B183" t="s">
         <v>291</v>
@@ -9896,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F183" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="G183" t="s">
         <v>44</v>
@@ -9911,15 +10454,18 @@
         <v>2500</v>
       </c>
       <c r="J183" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K183" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+      <c r="L183" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B184" t="s">
         <v>291</v>
@@ -9931,13 +10477,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F184" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="G184" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H184" t="s">
         <v>37</v>
@@ -9946,15 +10492,18 @@
         <v>2500</v>
       </c>
       <c r="J184" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="K184" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L184" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B185" t="s">
         <v>230</v>
@@ -9966,10 +10515,10 @@
         <v>10</v>
       </c>
       <c r="E185" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F185" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="G185" t="s">
         <v>392</v>
@@ -9981,18 +10530,21 @@
         <v>2500</v>
       </c>
       <c r="J185" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="K185" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L185" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B186" t="s">
-        <v>578</v>
+        <v>668</v>
       </c>
       <c r="C186">
         <v>20</v>
@@ -10001,10 +10553,10 @@
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F186" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G186" t="s">
         <v>392</v>
@@ -10016,15 +10568,18 @@
         <v>1500</v>
       </c>
       <c r="J186" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K186" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L186" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B187" t="s">
         <v>230</v>
@@ -10036,10 +10591,10 @@
         <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="F187" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G187" t="s">
         <v>392</v>
@@ -10051,15 +10606,18 @@
         <v>1500</v>
       </c>
       <c r="J187" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="K187" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L187" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B188" t="s">
         <v>291</v>
@@ -10071,10 +10629,10 @@
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F188" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G188" t="s">
         <v>44</v>
@@ -10086,15 +10644,18 @@
         <v>500</v>
       </c>
       <c r="J188" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K188" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L188" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B189" t="s">
         <v>291</v>
@@ -10106,10 +10667,10 @@
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F189" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G189" t="s">
         <v>44</v>
@@ -10121,15 +10682,18 @@
         <v>500</v>
       </c>
       <c r="J189" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K189" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L189" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B190" t="s">
         <v>291</v>
@@ -10141,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F190" t="s">
         <v>309</v>
@@ -10156,15 +10720,18 @@
         <v>500</v>
       </c>
       <c r="J190" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K190" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L190" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B191" t="s">
         <v>113</v>
@@ -10176,10 +10743,10 @@
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F191" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G191" t="s">
         <v>135</v>
@@ -10191,18 +10758,21 @@
         <v>2500</v>
       </c>
       <c r="J191" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K191" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L191" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B192" t="s">
-        <v>580</v>
+        <v>683</v>
       </c>
       <c r="C192">
         <v>19</v>
@@ -10211,10 +10781,10 @@
         <v>9</v>
       </c>
       <c r="E192" t="s">
+        <v>684</v>
+      </c>
+      <c r="F192" t="s">
         <v>685</v>
-      </c>
-      <c r="F192" t="s">
-        <v>686</v>
       </c>
       <c r="G192" t="s">
         <v>70</v>
@@ -10226,15 +10796,18 @@
         <v>5880</v>
       </c>
       <c r="J192" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K192" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L192" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B193" t="s">
         <v>67</v>
@@ -10246,10 +10819,10 @@
         <v>24</v>
       </c>
       <c r="E193" t="s">
+        <v>687</v>
+      </c>
+      <c r="F193" t="s">
         <v>688</v>
-      </c>
-      <c r="F193" t="s">
-        <v>689</v>
       </c>
       <c r="G193" t="s">
         <v>70</v>
@@ -10261,15 +10834,18 @@
         <v>6720</v>
       </c>
       <c r="J193" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K193" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L193" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B194" t="s">
         <v>67</v>
@@ -10281,10 +10857,10 @@
         <v>20</v>
       </c>
       <c r="E194" t="s">
+        <v>690</v>
+      </c>
+      <c r="F194" t="s">
         <v>691</v>
-      </c>
-      <c r="F194" t="s">
-        <v>692</v>
       </c>
       <c r="G194" t="s">
         <v>70</v>
@@ -10296,15 +10872,18 @@
         <v>7600</v>
       </c>
       <c r="J194" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K194" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L194" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B195" t="s">
         <v>149</v>
@@ -10316,10 +10895,10 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
+        <v>693</v>
+      </c>
+      <c r="F195" t="s">
         <v>694</v>
-      </c>
-      <c r="F195" t="s">
-        <v>695</v>
       </c>
       <c r="G195" t="s">
         <v>70</v>
@@ -10331,15 +10910,18 @@
         <v>6600</v>
       </c>
       <c r="J195" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K195" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L195" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B196" t="s">
         <v>149</v>
@@ -10351,10 +10933,10 @@
         <v>1</v>
       </c>
       <c r="E196" t="s">
+        <v>696</v>
+      </c>
+      <c r="F196" t="s">
         <v>697</v>
-      </c>
-      <c r="F196" t="s">
-        <v>698</v>
       </c>
       <c r="G196" t="s">
         <v>70</v>
@@ -10366,15 +10948,18 @@
         <v>5000</v>
       </c>
       <c r="J196" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K196" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L196" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B197" t="s">
         <v>482</v>
@@ -10386,10 +10971,10 @@
         <v>8</v>
       </c>
       <c r="E197" t="s">
+        <v>699</v>
+      </c>
+      <c r="F197" t="s">
         <v>700</v>
-      </c>
-      <c r="F197" t="s">
-        <v>701</v>
       </c>
       <c r="G197" t="s">
         <v>511</v>
@@ -10401,15 +10986,18 @@
         <v>6160</v>
       </c>
       <c r="J197" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K197" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L197" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B198" t="s">
         <v>482</v>
@@ -10421,10 +11009,10 @@
         <v>8</v>
       </c>
       <c r="E198" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G198" t="s">
         <v>511</v>
@@ -10436,15 +11024,18 @@
         <v>6160</v>
       </c>
       <c r="J198" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K198" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L198" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B199" t="s">
         <v>482</v>
@@ -10456,10 +11047,10 @@
         <v>8</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F199" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G199" t="s">
         <v>511</v>
@@ -10471,18 +11062,21 @@
         <v>6640</v>
       </c>
       <c r="J199" t="s">
+        <v>705</v>
+      </c>
+      <c r="K199" t="s">
+        <v>26</v>
+      </c>
+      <c r="L199" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>679</v>
+      </c>
+      <c r="B200" t="s">
         <v>706</v>
-      </c>
-      <c r="K199" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>681</v>
-      </c>
-      <c r="B200" t="s">
-        <v>707</v>
       </c>
       <c r="C200">
         <v>19</v>
@@ -10491,10 +11085,10 @@
         <v>12</v>
       </c>
       <c r="E200" t="s">
+        <v>707</v>
+      </c>
+      <c r="F200" t="s">
         <v>708</v>
-      </c>
-      <c r="F200" t="s">
-        <v>709</v>
       </c>
       <c r="G200" t="s">
         <v>392</v>
@@ -10506,18 +11100,21 @@
         <v>600</v>
       </c>
       <c r="J200" t="s">
+        <v>709</v>
+      </c>
+      <c r="K200" t="s">
+        <v>26</v>
+      </c>
+      <c r="L200" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>679</v>
+      </c>
+      <c r="B201" t="s">
         <v>710</v>
-      </c>
-      <c r="K200" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>681</v>
-      </c>
-      <c r="B201" t="s">
-        <v>711</v>
       </c>
       <c r="C201">
         <v>19</v>
@@ -10526,10 +11123,10 @@
         <v>6</v>
       </c>
       <c r="E201" t="s">
+        <v>711</v>
+      </c>
+      <c r="F201" t="s">
         <v>712</v>
-      </c>
-      <c r="F201" t="s">
-        <v>713</v>
       </c>
       <c r="G201" t="s">
         <v>44</v>
@@ -10541,15 +11138,18 @@
         <v>1800</v>
       </c>
       <c r="J201" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K201" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L201" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B202" t="s">
         <v>410</v>
@@ -10561,16 +11161,16 @@
         <v>60</v>
       </c>
       <c r="E202" t="s">
+        <v>714</v>
+      </c>
+      <c r="F202" t="s">
         <v>715</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>716</v>
       </c>
-      <c r="G202" t="s">
+      <c r="H202" t="s">
         <v>717</v>
-      </c>
-      <c r="H202" t="s">
-        <v>577</v>
       </c>
       <c r="I202">
         <v>2100</v>
@@ -10581,10 +11181,13 @@
       <c r="K202" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L202" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B203" t="s">
         <v>410</v>
@@ -10596,16 +11199,16 @@
         <v>30</v>
       </c>
       <c r="E203" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F203" t="s">
         <v>719</v>
       </c>
       <c r="G203" t="s">
+        <v>716</v>
+      </c>
+      <c r="H203" t="s">
         <v>717</v>
-      </c>
-      <c r="H203" t="s">
-        <v>577</v>
       </c>
       <c r="I203">
         <v>1050</v>
@@ -10616,10 +11219,13 @@
       <c r="K203" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L203" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B204" t="s">
         <v>410</v>
@@ -10631,16 +11237,16 @@
         <v>30</v>
       </c>
       <c r="E204" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F204" t="s">
         <v>721</v>
       </c>
       <c r="G204" t="s">
+        <v>716</v>
+      </c>
+      <c r="H204" t="s">
         <v>717</v>
-      </c>
-      <c r="H204" t="s">
-        <v>577</v>
       </c>
       <c r="I204">
         <v>1050</v>
@@ -10651,10 +11257,13 @@
       <c r="K204" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L204" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B205" t="s">
         <v>374</v>
@@ -10669,7 +11278,7 @@
         <v>723</v>
       </c>
       <c r="F205" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G205" t="s">
         <v>44</v>
@@ -10686,10 +11295,13 @@
       <c r="K205" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L205" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B206" t="s">
         <v>725</v>
@@ -10721,10 +11333,13 @@
       <c r="K206" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L206" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B207" t="s">
         <v>725</v>
@@ -10756,10 +11371,13 @@
       <c r="K207" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L207" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B208" t="s">
         <v>725</v>
@@ -10791,10 +11409,13 @@
       <c r="K208" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L208" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B209" t="s">
         <v>410</v>
@@ -10826,10 +11447,13 @@
       <c r="K209" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L209" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B210" t="s">
         <v>410</v>
@@ -10861,10 +11485,13 @@
       <c r="K210" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L210" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B211" t="s">
         <v>187</v>
@@ -10896,10 +11523,13 @@
       <c r="K211" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L211" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B212" t="s">
         <v>212</v>
@@ -10931,10 +11561,13 @@
       <c r="K212" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L212" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B213" t="s">
         <v>294</v>
@@ -10966,10 +11599,13 @@
       <c r="K213" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L213" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B214" t="s">
         <v>382</v>
@@ -11001,10 +11637,13 @@
       <c r="K214" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L214" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B215" t="s">
         <v>297</v>
@@ -11036,10 +11675,13 @@
       <c r="K215" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L215" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B216" t="s">
         <v>297</v>
@@ -11071,10 +11713,13 @@
       <c r="K216" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L216" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B217" t="s">
         <v>258</v>
@@ -11106,10 +11751,13 @@
       <c r="K217" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L217" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B218" t="s">
         <v>258</v>
@@ -11141,10 +11789,13 @@
       <c r="K218" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L218" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B219" t="s">
         <v>374</v>
@@ -11176,10 +11827,13 @@
       <c r="K219" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L219" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B220" t="s">
         <v>187</v>
@@ -11211,10 +11865,13 @@
       <c r="K220" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L220" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B221" t="s">
         <v>187</v>
@@ -11246,10 +11903,13 @@
       <c r="K221" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L221" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B222" t="s">
         <v>157</v>
@@ -11281,10 +11941,13 @@
       <c r="K222" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L222" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B223" t="s">
         <v>482</v>
@@ -11316,10 +11979,13 @@
       <c r="K223" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L223" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B224" t="s">
         <v>258</v>
@@ -11351,10 +12017,13 @@
       <c r="K224" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L224" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B225" t="s">
         <v>258</v>
@@ -11386,10 +12055,13 @@
       <c r="K225" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L225" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B226" t="s">
         <v>258</v>
@@ -11421,8 +12093,11 @@
       <c r="K226" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L226" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>784</v>
       </c>
@@ -11456,13 +12131,16 @@
       <c r="K227" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L227" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>784</v>
       </c>
       <c r="B228" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="C228">
         <v>4</v>
@@ -11491,8 +12169,11 @@
       <c r="K228" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L228" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>784</v>
       </c>
@@ -11526,8 +12207,11 @@
       <c r="K229" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L229" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>784</v>
       </c>
@@ -11561,8 +12245,11 @@
       <c r="K230" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L230" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>784</v>
       </c>
@@ -11596,8 +12283,11 @@
       <c r="K231" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L231" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>784</v>
       </c>
@@ -11631,8 +12321,11 @@
       <c r="K232" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L232" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>784</v>
       </c>
@@ -11666,8 +12359,11 @@
       <c r="K233" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L233" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>784</v>
       </c>
@@ -11701,8 +12397,11 @@
       <c r="K234" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L234" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>784</v>
       </c>
@@ -11736,8 +12435,11 @@
       <c r="K235" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L235" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>784</v>
       </c>
@@ -11771,8 +12473,11 @@
       <c r="K236" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L236" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>784</v>
       </c>
@@ -11806,8 +12511,11 @@
       <c r="K237" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L237" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>784</v>
       </c>
@@ -11841,8 +12549,11 @@
       <c r="K238" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L238" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>784</v>
       </c>
@@ -11876,8 +12587,11 @@
       <c r="K239" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L239" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>784</v>
       </c>
@@ -11911,8 +12625,11 @@
       <c r="K240" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L240" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>784</v>
       </c>
@@ -11946,8 +12663,11 @@
       <c r="K241" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L241" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>784</v>
       </c>
@@ -11981,8 +12701,11 @@
       <c r="K242" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L242" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>784</v>
       </c>
@@ -12016,8 +12739,11 @@
       <c r="K243" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L243" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>784</v>
       </c>
@@ -12051,8 +12777,11 @@
       <c r="K244" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L244" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>784</v>
       </c>
@@ -12084,15 +12813,18 @@
         <v>836</v>
       </c>
       <c r="K245" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+      <c r="L245" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>784</v>
       </c>
       <c r="B246" t="s">
-        <v>580</v>
+        <v>683</v>
       </c>
       <c r="C246">
         <v>4</v>
@@ -12118,8 +12850,14 @@
       <c r="J246" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K246" t="s">
+        <v>26</v>
+      </c>
+      <c r="L246" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>784</v>
       </c>
@@ -12150,8 +12888,14 @@
       <c r="J247" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K247" t="s">
+        <v>26</v>
+      </c>
+      <c r="L247" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>784</v>
       </c>
@@ -12182,8 +12926,14 @@
       <c r="J248" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K248" t="s">
+        <v>26</v>
+      </c>
+      <c r="L248" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>784</v>
       </c>
@@ -12214,8 +12964,14 @@
       <c r="J249" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K249" t="s">
+        <v>26</v>
+      </c>
+      <c r="L249" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>784</v>
       </c>
@@ -12246,8 +13002,14 @@
       <c r="J250" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K250" t="s">
+        <v>26</v>
+      </c>
+      <c r="L250" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>784</v>
       </c>
@@ -12278,8 +13040,14 @@
       <c r="J251" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K251" t="s">
+        <v>26</v>
+      </c>
+      <c r="L251" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>784</v>
       </c>
@@ -12310,8 +13078,14 @@
       <c r="J252" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K252" t="s">
+        <v>26</v>
+      </c>
+      <c r="L252" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>784</v>
       </c>
@@ -12342,8 +13116,14 @@
       <c r="J253" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K253" t="s">
+        <v>26</v>
+      </c>
+      <c r="L253" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>784</v>
       </c>
@@ -12374,8 +13154,14 @@
       <c r="J254" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K254" t="s">
+        <v>26</v>
+      </c>
+      <c r="L254" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>784</v>
       </c>
@@ -12406,8 +13192,14 @@
       <c r="J255" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K255" t="s">
+        <v>26</v>
+      </c>
+      <c r="L255" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>784</v>
       </c>
@@ -12438,8 +13230,14 @@
       <c r="J256" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K256" t="s">
+        <v>26</v>
+      </c>
+      <c r="L256" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>784</v>
       </c>
@@ -12470,8 +13268,14 @@
       <c r="J257" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K257" t="s">
+        <v>26</v>
+      </c>
+      <c r="L257" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>784</v>
       </c>
@@ -12502,8 +13306,14 @@
       <c r="J258" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K258" t="s">
+        <v>26</v>
+      </c>
+      <c r="L258" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>784</v>
       </c>
@@ -12534,8 +13344,14 @@
       <c r="J259" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K259" t="s">
+        <v>26</v>
+      </c>
+      <c r="L259" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>784</v>
       </c>
@@ -12566,8 +13382,14 @@
       <c r="J260" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K260" t="s">
+        <v>26</v>
+      </c>
+      <c r="L260" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>784</v>
       </c>
@@ -12598,8 +13420,14 @@
       <c r="J261" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K261" t="s">
+        <v>26</v>
+      </c>
+      <c r="L261" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>784</v>
       </c>
@@ -12630,8 +13458,14 @@
       <c r="J262" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K262" t="s">
+        <v>26</v>
+      </c>
+      <c r="L262" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>784</v>
       </c>
@@ -12662,13 +13496,19 @@
       <c r="J263" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K263" t="s">
+        <v>26</v>
+      </c>
+      <c r="L263" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>784</v>
       </c>
       <c r="B264" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C264">
         <v>4</v>
@@ -12694,8 +13534,14 @@
       <c r="J264" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K264" t="s">
+        <v>26</v>
+      </c>
+      <c r="L264" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>784</v>
       </c>
@@ -12726,8 +13572,14 @@
       <c r="J265" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K265" t="s">
+        <v>26</v>
+      </c>
+      <c r="L265" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>784</v>
       </c>
@@ -12758,8 +13610,14 @@
       <c r="J266" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K266" t="s">
+        <v>26</v>
+      </c>
+      <c r="L266" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>784</v>
       </c>
@@ -12789,6 +13647,12 @@
       </c>
       <c r="J267" t="s">
         <v>886</v>
+      </c>
+      <c r="K267" t="s">
+        <v>661</v>
+      </c>
+      <c r="L267" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68F0BD1-A7F0-4EBD-B461-4093D88F80BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FB07BD-8825-4F75-A461-1690C04C3C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="71">
   <si>
     <t>Responsável</t>
   </si>
@@ -61,24 +74,6 @@
     <t>Marcelo Simoes</t>
   </si>
   <si>
-    <t>BM-00108513_002_00000030</t>
-  </si>
-  <si>
-    <t>Unnamed: 17</t>
-  </si>
-  <si>
-    <t>Retrabalho das capas</t>
-  </si>
-  <si>
-    <t>ALL7CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS22-BR</t>
-  </si>
-  <si>
-    <t>LP-055872</t>
-  </si>
-  <si>
     <t>BM-00040171_002_00000015</t>
   </si>
   <si>
@@ -109,15 +104,9 @@
     <t>LP-056194</t>
   </si>
   <si>
-    <t>Retrabalho Capas Térmicas</t>
-  </si>
-  <si>
     <t>CtP/ETS</t>
   </si>
   <si>
-    <t>LP-056443</t>
-  </si>
-  <si>
     <t>BM-00040171_001_00000019</t>
   </si>
   <si>
@@ -166,12 +155,6 @@
     <t>LP-057075</t>
   </si>
   <si>
-    <t>Retrabalho parte inferior capas térmicas</t>
-  </si>
-  <si>
-    <t>LP-057204</t>
-  </si>
-  <si>
     <t>BM-00108513_002_00000018</t>
   </si>
   <si>
@@ -260,6 +243,9 @@
   </si>
   <si>
     <t>LP-059504</t>
+  </si>
+  <si>
+    <t>Cadastrado</t>
   </si>
 </sst>
 </file>
@@ -622,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -635,7 +621,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -685,10 +671,10 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -703,42 +689,54 @@
         <v>17</v>
       </c>
       <c r="I2">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
+      <c r="K2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3">
+        <v>500</v>
+      </c>
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>300</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -746,7 +744,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -755,22 +753,28 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>500</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -778,32 +782,38 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
       </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -813,57 +823,72 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>96</v>
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
       </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>3500</v>
-      </c>
-      <c r="J7" t="s">
-        <v>36</v>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -871,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -886,10 +911,10 @@
         <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I8">
         <v>1000</v>
@@ -897,37 +922,46 @@
       <c r="J8" t="s">
         <v>39</v>
       </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -935,22 +969,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
         <v>45</v>
       </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>23</v>
@@ -959,7 +993,13 @@
         <v>1000</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -970,25 +1010,34 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="K11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -996,28 +1045,37 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
       </c>
       <c r="F12" t="s">
         <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
         <v>23</v>
       </c>
       <c r="I12">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1025,31 +1083,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1057,31 +1121,37 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I14">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1089,31 +1159,37 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I15">
         <v>1000</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1121,159 +1197,75 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I16">
         <v>500</v>
       </c>
       <c r="J16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
         <v>68</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="s">
         <v>69</v>
       </c>
-      <c r="G17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19">
-        <v>500</v>
-      </c>
-      <c r="J19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20">
-        <v>500</v>
-      </c>
-      <c r="J20" t="s">
-        <v>79</v>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FB07BD-8825-4F75-A461-1690C04C3C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6E75D6-73D7-4751-82EA-7A0E724482ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="366">
   <si>
     <t>Responsável</t>
   </si>
@@ -80,81 +80,21 @@
     <t>-</t>
   </si>
   <si>
-    <t>Prensagem pino</t>
-  </si>
-  <si>
     <t>RAFAELA</t>
   </si>
   <si>
     <t>PS-DC/ENP1-LA</t>
   </si>
   <si>
-    <t>LP-056190</t>
-  </si>
-  <si>
-    <t>Retrabalho 0414y0053-01</t>
-  </si>
-  <si>
-    <t>LP-056193</t>
-  </si>
-  <si>
-    <t>Retrabalho 0414y00349-01</t>
-  </si>
-  <si>
-    <t>LP-056194</t>
-  </si>
-  <si>
     <t>CtP/ETS</t>
   </si>
   <si>
-    <t>BM-00040171_001_00000019</t>
-  </si>
-  <si>
-    <t>F002.C64.008-01</t>
-  </si>
-  <si>
-    <t>Pino de pressão instrumentado</t>
-  </si>
-  <si>
-    <t>ANDRÉ</t>
-  </si>
-  <si>
-    <t>LP-056853</t>
-  </si>
-  <si>
-    <t>0414Y10182-01</t>
-  </si>
-  <si>
-    <t>Perforated plate - 0.311 mm</t>
-  </si>
-  <si>
-    <t>LP-057073</t>
-  </si>
-  <si>
-    <t>0414Y10183-01</t>
-  </si>
-  <si>
-    <t>Perforated plate - 0.322 mm</t>
-  </si>
-  <si>
-    <t>LP-057074</t>
-  </si>
-  <si>
     <t>N.A</t>
   </si>
   <si>
     <t>PS-DC/ENP3-LA</t>
   </si>
   <si>
-    <t>0414Y10184-01</t>
-  </si>
-  <si>
-    <t>Perforated plate - 0.333 mm</t>
-  </si>
-  <si>
-    <t>LP-057075</t>
-  </si>
-  <si>
     <t>BM-00108513_002_00000018</t>
   </si>
   <si>
@@ -236,16 +176,961 @@
     <t>LP-059306</t>
   </si>
   <si>
-    <t>0414Y10212-01</t>
-  </si>
-  <si>
-    <t>RETRABALHO DISPOSITIVO</t>
-  </si>
-  <si>
-    <t>LP-059504</t>
-  </si>
-  <si>
-    <t>Cadastrado</t>
+    <t>Joao Franca</t>
+  </si>
+  <si>
+    <t>685552</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>4711500240</t>
+  </si>
+  <si>
+    <t>PLACA DA LCMV Nº01</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>CtP/TEF11</t>
+  </si>
+  <si>
+    <t>LP-057267</t>
+  </si>
+  <si>
+    <t>685609</t>
+  </si>
+  <si>
+    <t>71880070FC_073</t>
+  </si>
+  <si>
+    <t>Stavax</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>LP-059660</t>
+  </si>
+  <si>
+    <t>71880071FC_028</t>
+  </si>
+  <si>
+    <t>LP-059661</t>
+  </si>
+  <si>
+    <t>4702500760_001</t>
+  </si>
+  <si>
+    <t>REPOSIÇÃO ELETRODO</t>
+  </si>
+  <si>
+    <t>LP-059664</t>
+  </si>
+  <si>
+    <t>4702500760_003</t>
+  </si>
+  <si>
+    <t>LP-059665</t>
+  </si>
+  <si>
+    <t>4702500760_004</t>
+  </si>
+  <si>
+    <t>LP-059666</t>
+  </si>
+  <si>
+    <t>4702500762_001</t>
+  </si>
+  <si>
+    <t>LP-059667</t>
+  </si>
+  <si>
+    <t>4702500762_003</t>
+  </si>
+  <si>
+    <t>LP-059668</t>
+  </si>
+  <si>
+    <t>4702500762_004</t>
+  </si>
+  <si>
+    <t>LP-059669</t>
+  </si>
+  <si>
+    <t>4702500758_001</t>
+  </si>
+  <si>
+    <t>LP-059670</t>
+  </si>
+  <si>
+    <t>4702500758-003</t>
+  </si>
+  <si>
+    <t>LP-059671</t>
+  </si>
+  <si>
+    <t>4702500758_004</t>
+  </si>
+  <si>
+    <t>LP-059672</t>
+  </si>
+  <si>
+    <t>4702500758_009</t>
+  </si>
+  <si>
+    <t>LP-059673</t>
+  </si>
+  <si>
+    <t>4702500803_001</t>
+  </si>
+  <si>
+    <t>LP-059674</t>
+  </si>
+  <si>
+    <t>4702500803_004</t>
+  </si>
+  <si>
+    <t>LP-059675</t>
+  </si>
+  <si>
+    <t>4702500757_001</t>
+  </si>
+  <si>
+    <t>LP-059676</t>
+  </si>
+  <si>
+    <t>4702500757_003</t>
+  </si>
+  <si>
+    <t>LP-059677</t>
+  </si>
+  <si>
+    <t>4702500757_004</t>
+  </si>
+  <si>
+    <t>LP-059678</t>
+  </si>
+  <si>
+    <t>4702500759_001</t>
+  </si>
+  <si>
+    <t>LP-059679</t>
+  </si>
+  <si>
+    <t>4702500759_003</t>
+  </si>
+  <si>
+    <t>LP-059680</t>
+  </si>
+  <si>
+    <t>4702500625_001</t>
+  </si>
+  <si>
+    <t>LP-059681</t>
+  </si>
+  <si>
+    <t>4702500625_005</t>
+  </si>
+  <si>
+    <t>LP-059682</t>
+  </si>
+  <si>
+    <t>4702500625_010</t>
+  </si>
+  <si>
+    <t>LP-059683</t>
+  </si>
+  <si>
+    <t>4702500795_001</t>
+  </si>
+  <si>
+    <t>LP-059684</t>
+  </si>
+  <si>
+    <t>4702500795_003</t>
+  </si>
+  <si>
+    <t>LP-059685</t>
+  </si>
+  <si>
+    <t>4702500795_004</t>
+  </si>
+  <si>
+    <t>LP-059686</t>
+  </si>
+  <si>
+    <t>4702500863_002</t>
+  </si>
+  <si>
+    <t>LP-059687</t>
+  </si>
+  <si>
+    <t>4702500863_004</t>
+  </si>
+  <si>
+    <t>LP-059688</t>
+  </si>
+  <si>
+    <t>4702500836_001</t>
+  </si>
+  <si>
+    <t>LP-059689</t>
+  </si>
+  <si>
+    <t>4702500836_004</t>
+  </si>
+  <si>
+    <t>LP-059690</t>
+  </si>
+  <si>
+    <t>4702500838_001</t>
+  </si>
+  <si>
+    <t>LP-059691</t>
+  </si>
+  <si>
+    <t>4702500838_004</t>
+  </si>
+  <si>
+    <t>LP-059692</t>
+  </si>
+  <si>
+    <t>685551</t>
+  </si>
+  <si>
+    <t>4711500202</t>
+  </si>
+  <si>
+    <t>FLANGE</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-059702</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>4715900482-0002</t>
+  </si>
+  <si>
+    <t>LS - conserto</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-059696</t>
+  </si>
+  <si>
+    <t>685421</t>
+  </si>
+  <si>
+    <t>4716502764</t>
+  </si>
+  <si>
+    <t>Novo - series 0034 e 0035</t>
+  </si>
+  <si>
+    <t>LP-059650</t>
+  </si>
+  <si>
+    <t>685412</t>
+  </si>
+  <si>
+    <t>4716511334</t>
+  </si>
+  <si>
+    <t>Novo - series 0005 e 0006</t>
+  </si>
+  <si>
+    <t>LP-059651</t>
+  </si>
+  <si>
+    <t>685554</t>
+  </si>
+  <si>
+    <t>4715900574-0001</t>
+  </si>
+  <si>
+    <t>LP-059694</t>
+  </si>
+  <si>
+    <t>685541</t>
+  </si>
+  <si>
+    <t>4716403030-0007</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>LP-059710</t>
+  </si>
+  <si>
+    <t>685545</t>
+  </si>
+  <si>
+    <t>4716402549-0002</t>
+  </si>
+  <si>
+    <t>LP-059715</t>
+  </si>
+  <si>
+    <t>685533</t>
+  </si>
+  <si>
+    <t>4714900223</t>
+  </si>
+  <si>
+    <t>Novo - serie 0009</t>
+  </si>
+  <si>
+    <t>LP-059714</t>
+  </si>
+  <si>
+    <t>4314200234</t>
+  </si>
+  <si>
+    <t>Novo - serie 0010</t>
+  </si>
+  <si>
+    <t>LP-059713</t>
+  </si>
+  <si>
+    <t>685485</t>
+  </si>
+  <si>
+    <t>4716406052-0001</t>
+  </si>
+  <si>
+    <t>LP-059712</t>
+  </si>
+  <si>
+    <t>685704</t>
+  </si>
+  <si>
+    <t>4716405381-0001</t>
+  </si>
+  <si>
+    <t>LP-059699</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 685552</t>
+  </si>
+  <si>
+    <t>4716511525</t>
+  </si>
+  <si>
+    <t>Novo - series 0032 e 0033</t>
+  </si>
+  <si>
+    <t>LP-059698</t>
+  </si>
+  <si>
+    <t>4716404776-0006</t>
+  </si>
+  <si>
+    <t>LP-059697</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 685541</t>
+  </si>
+  <si>
+    <t>4715900489-0001</t>
+  </si>
+  <si>
+    <t>LP-059711</t>
+  </si>
+  <si>
+    <t>685113</t>
+  </si>
+  <si>
+    <t>4716405724-0005</t>
+  </si>
+  <si>
+    <t>LP-059695</t>
+  </si>
+  <si>
+    <t>685484</t>
+  </si>
+  <si>
+    <t>4715600076</t>
+  </si>
+  <si>
+    <t>Novo - serie 0006</t>
+  </si>
+  <si>
+    <t>LP-059707</t>
+  </si>
+  <si>
+    <t>685700</t>
+  </si>
+  <si>
+    <t>4737990011-0003</t>
+  </si>
+  <si>
+    <t>Prisma - conserto</t>
+  </si>
+  <si>
+    <t>LP-059693</t>
+  </si>
+  <si>
+    <t>4716500352-0016</t>
+  </si>
+  <si>
+    <t>LY - conserto</t>
+  </si>
+  <si>
+    <t>LP-059709</t>
+  </si>
+  <si>
+    <t>4716500353-0015</t>
+  </si>
+  <si>
+    <t>LP-059708</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>685487</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>4710101257</t>
+  </si>
+  <si>
+    <t>IP 685487 Pinça cilindro MW ⌀10</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>LP-059757</t>
+  </si>
+  <si>
+    <t>685606</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>4729110417</t>
+  </si>
+  <si>
+    <t>Tubo de teste KIENE - FDL</t>
+  </si>
+  <si>
+    <t>ZAK2CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-059722</t>
+  </si>
+  <si>
+    <t>4729110244</t>
+  </si>
+  <si>
+    <t>Tubo de teste KIENE - EVO</t>
+  </si>
+  <si>
+    <t>LP-059723</t>
+  </si>
+  <si>
+    <t>4712004047</t>
+  </si>
+  <si>
+    <t>Posição 2</t>
+  </si>
+  <si>
+    <t>LP-059767</t>
+  </si>
+  <si>
+    <t>685605</t>
+  </si>
+  <si>
+    <t>4711300549 POS1</t>
+  </si>
+  <si>
+    <t>Pino Guia</t>
+  </si>
+  <si>
+    <t>LP-059659</t>
+  </si>
+  <si>
+    <t>4728800288</t>
+  </si>
+  <si>
+    <t>Pino prensa</t>
+  </si>
+  <si>
+    <t>LP-059768</t>
+  </si>
+  <si>
+    <t>685008</t>
+  </si>
+  <si>
+    <t>4722805111</t>
+  </si>
+  <si>
+    <t>Carimbo HPC</t>
+  </si>
+  <si>
+    <t>LP-059761</t>
+  </si>
+  <si>
+    <t>4722805112</t>
+  </si>
+  <si>
+    <t>LP-059766</t>
+  </si>
+  <si>
+    <t>4722805113</t>
+  </si>
+  <si>
+    <t>LP-059765</t>
+  </si>
+  <si>
+    <t>4722805114</t>
+  </si>
+  <si>
+    <t>LP-059760</t>
+  </si>
+  <si>
+    <t>4729108882_POS 4</t>
+  </si>
+  <si>
+    <t>DU 685421 POSIÇÃO 4  do cabeçote AGIE</t>
+  </si>
+  <si>
+    <t>LP-059719</t>
+  </si>
+  <si>
+    <t>4722805115</t>
+  </si>
+  <si>
+    <t>LP-059762</t>
+  </si>
+  <si>
+    <t>4722805116</t>
+  </si>
+  <si>
+    <t>LP-059763</t>
+  </si>
+  <si>
+    <t>4722805117</t>
+  </si>
+  <si>
+    <t>LP-059764</t>
+  </si>
+  <si>
+    <t>4711300114</t>
+  </si>
+  <si>
+    <t>IP 685485 Base do Pallet P3 &amp; S3 brunid.</t>
+  </si>
+  <si>
+    <t>LP-059756</t>
+  </si>
+  <si>
+    <t>4711401053</t>
+  </si>
+  <si>
+    <t>Jogo de castanha</t>
+  </si>
+  <si>
+    <t>LP-059758</t>
+  </si>
+  <si>
+    <t>4711400621</t>
+  </si>
+  <si>
+    <t>LP-059759</t>
+  </si>
+  <si>
+    <t>685433</t>
+  </si>
+  <si>
+    <t>4730502878</t>
+  </si>
+  <si>
+    <t>DU 685433 Arruela bancada de montag Bico</t>
+  </si>
+  <si>
+    <t>LP-059721</t>
+  </si>
+  <si>
+    <t>4729111137_POS 1</t>
+  </si>
+  <si>
+    <t>DU 685421 POSIÇÃO 1 da Bucha roscada</t>
+  </si>
+  <si>
+    <t>LP-059720</t>
+  </si>
+  <si>
+    <t>685557</t>
+  </si>
+  <si>
+    <t>4729110395</t>
+  </si>
+  <si>
+    <t>Régua</t>
+  </si>
+  <si>
+    <t>LP-059724</t>
+  </si>
+  <si>
+    <t>685531</t>
+  </si>
+  <si>
+    <t>4722804317</t>
+  </si>
+  <si>
+    <t>Carimbo</t>
+  </si>
+  <si>
+    <t>LP-059740</t>
+  </si>
+  <si>
+    <t>4722804314</t>
+  </si>
+  <si>
+    <t>LP-059742</t>
+  </si>
+  <si>
+    <t>4722804313</t>
+  </si>
+  <si>
+    <t>LP-059741</t>
+  </si>
+  <si>
+    <t>4722804310</t>
+  </si>
+  <si>
+    <t>LP-059743</t>
+  </si>
+  <si>
+    <t>4322801562</t>
+  </si>
+  <si>
+    <t>LP-059744</t>
+  </si>
+  <si>
+    <t>CROQUI PINÇA MW</t>
+  </si>
+  <si>
+    <t>IP 685485 CROQUI de Pinça cil MW</t>
+  </si>
+  <si>
+    <t>LP-059738</t>
+  </si>
+  <si>
+    <t>4322801565</t>
+  </si>
+  <si>
+    <t>LP-059739</t>
+  </si>
+  <si>
+    <t>685615</t>
+  </si>
+  <si>
+    <t>4730100080</t>
+  </si>
+  <si>
+    <t>Porca do Bloco Superior</t>
+  </si>
+  <si>
+    <t>ANF2CT</t>
+  </si>
+  <si>
+    <t>LP-059774</t>
+  </si>
+  <si>
+    <t>685411</t>
+  </si>
+  <si>
+    <t>4710800192</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste rebaixada</t>
+  </si>
+  <si>
+    <t>LP-059734</t>
+  </si>
+  <si>
+    <t>4710800193</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste cheia U.D</t>
+  </si>
+  <si>
+    <t>LP-059735</t>
+  </si>
+  <si>
+    <t>4729105899</t>
+  </si>
+  <si>
+    <t>DU 685411 Tampa de lavadora 2...3564 U.D</t>
+  </si>
+  <si>
+    <t>LP-059736</t>
+  </si>
+  <si>
+    <t>4712004409</t>
+  </si>
+  <si>
+    <t>DU 685411 Garra d aliment. HTT 3352/3362</t>
+  </si>
+  <si>
+    <t>LP-059733</t>
+  </si>
+  <si>
+    <t>4710800277</t>
+  </si>
+  <si>
+    <t>Contra ponto</t>
+  </si>
+  <si>
+    <t>LP-059728</t>
+  </si>
+  <si>
+    <t>Thais Fischer</t>
+  </si>
+  <si>
+    <t>685401</t>
+  </si>
+  <si>
+    <t>4729111564</t>
+  </si>
+  <si>
+    <t>PEÇA DESCARREGAMENTO</t>
+  </si>
+  <si>
+    <t>JULIANA MELO</t>
+  </si>
+  <si>
+    <t>LP-059705</t>
+  </si>
+  <si>
+    <t>Edson Bento</t>
+  </si>
+  <si>
+    <t>685070</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>4710200831</t>
+  </si>
+  <si>
+    <t>Retrabalho Pinça 13mm  | Zema 62005</t>
+  </si>
+  <si>
+    <t>FRM4CT</t>
+  </si>
+  <si>
+    <t>LP-059706</t>
+  </si>
+  <si>
+    <t>4310800263</t>
+  </si>
+  <si>
+    <t>Ponto fixação pistão</t>
+  </si>
+  <si>
+    <t>SAL5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW11-D</t>
+  </si>
+  <si>
+    <t>LP-059746</t>
+  </si>
+  <si>
+    <t>685050</t>
+  </si>
+  <si>
+    <t>4712004980</t>
+  </si>
+  <si>
+    <t>Posição 1</t>
+  </si>
+  <si>
+    <t>VIM6CT</t>
+  </si>
+  <si>
+    <t>LP-055445</t>
+  </si>
+  <si>
+    <t>BM-00108513_002_00000030</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Retrabalho das capas</t>
+  </si>
+  <si>
+    <t>ALL7CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS22-BR</t>
+  </si>
+  <si>
+    <t>LP-055872</t>
+  </si>
+  <si>
+    <t>Prensagem bucha</t>
+  </si>
+  <si>
+    <t>LP-056191</t>
+  </si>
+  <si>
+    <t>Retrabalho Capas Térmicas</t>
+  </si>
+  <si>
+    <t>LP-056443</t>
+  </si>
+  <si>
+    <t>Retrabalho parte inferior capas térmicas</t>
+  </si>
+  <si>
+    <t>LP-057204</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>685608</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Batente de Dispo. Placa Quebrada - USDUR</t>
+  </si>
+  <si>
+    <t>LP-059662</t>
+  </si>
+  <si>
+    <t>4729104510</t>
+  </si>
+  <si>
+    <t>Disp. Nagel</t>
+  </si>
+  <si>
+    <t>LP-058456</t>
+  </si>
+  <si>
+    <t>fabricar tampa conforme desenho</t>
+  </si>
+  <si>
+    <t>CRI4CT</t>
+  </si>
+  <si>
+    <t>LP-059648</t>
+  </si>
+  <si>
+    <t>RAIL</t>
+  </si>
+  <si>
+    <t>0804277455</t>
+  </si>
+  <si>
+    <t>RAIL CI 4000</t>
+  </si>
+  <si>
+    <t>IGO3CT</t>
+  </si>
+  <si>
+    <t>LP-059140</t>
+  </si>
+  <si>
+    <t>685009</t>
+  </si>
+  <si>
+    <t>4729112310</t>
+  </si>
+  <si>
+    <t>Bucha supfina DHK</t>
+  </si>
+  <si>
+    <t>MMA5CT</t>
+  </si>
+  <si>
+    <t>CtP/MFW12-B</t>
+  </si>
+  <si>
+    <t>LP-059769</t>
+  </si>
+  <si>
+    <t>4710800358</t>
+  </si>
+  <si>
+    <t>685552 - Ponteira Studer LE</t>
+  </si>
+  <si>
+    <t>VIM2CT</t>
+  </si>
+  <si>
+    <t>CtP/MFE11</t>
+  </si>
+  <si>
+    <t>LP-059654</t>
+  </si>
+  <si>
+    <t>4710100396</t>
+  </si>
+  <si>
+    <t>IP-685485-Brunidora d preparar.CIL P3⌀12</t>
+  </si>
+  <si>
+    <t>LP-059750</t>
+  </si>
+  <si>
+    <t>LP-055633-00-02</t>
+  </si>
+  <si>
+    <t>F00043R26T-01</t>
+  </si>
+  <si>
+    <t>Fabricação agulhas All Makes amostra A2</t>
+  </si>
+  <si>
+    <t>EDERSON LENH</t>
+  </si>
+  <si>
+    <t>LP-059737</t>
+  </si>
+  <si>
+    <t>suporte prensagem</t>
+  </si>
+  <si>
+    <t>LP-059775</t>
+  </si>
+  <si>
+    <t>pino guia roscado</t>
+  </si>
+  <si>
+    <t>LP-059776</t>
   </si>
 </sst>
 </file>
@@ -608,20 +1493,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -665,607 +1550,3522 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I9">
-        <v>500</v>
+        <v>3200</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I11">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" t="s">
-        <v>70</v>
-      </c>
-      <c r="L12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I13">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
         <v>58</v>
       </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="J14" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L14" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
         <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="J15" t="s">
-        <v>64</v>
-      </c>
-      <c r="K15" t="s">
-        <v>70</v>
-      </c>
-      <c r="L15" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16">
+        <v>2500</v>
+      </c>
+      <c r="J16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17">
+        <v>4000</v>
+      </c>
+      <c r="J17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18">
+        <v>3200</v>
+      </c>
+      <c r="J18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19">
+        <v>2500</v>
+      </c>
+      <c r="J19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20">
+        <v>4000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21">
+        <v>3200</v>
+      </c>
+      <c r="J21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22">
+        <v>4000</v>
+      </c>
+      <c r="J22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23">
+        <v>3200</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24">
+        <v>2500</v>
+      </c>
+      <c r="J24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25">
+        <v>4000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26">
+        <v>3200</v>
+      </c>
+      <c r="J26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27">
+        <v>2500</v>
+      </c>
+      <c r="J27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H28" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28">
+        <v>4000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29">
+        <v>2500</v>
+      </c>
+      <c r="J29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30">
+        <v>2000</v>
+      </c>
+      <c r="J30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31">
+        <v>50</v>
+      </c>
+      <c r="E31" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31">
+        <v>2000</v>
+      </c>
+      <c r="J31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32">
+        <v>50</v>
+      </c>
+      <c r="E32" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32">
+        <v>2000</v>
+      </c>
+      <c r="J32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" t="s">
+        <v>53</v>
+      </c>
+      <c r="I33">
+        <v>2000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I35">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36">
+        <v>3500</v>
+      </c>
+      <c r="J36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37">
+        <v>3000</v>
+      </c>
+      <c r="J37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" t="s">
+        <v>131</v>
+      </c>
+      <c r="I38">
+        <v>1000</v>
+      </c>
+      <c r="J38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" t="s">
+        <v>130</v>
+      </c>
+      <c r="H40" t="s">
+        <v>131</v>
+      </c>
+      <c r="I40">
+        <v>1200</v>
+      </c>
+      <c r="J40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" t="s">
+        <v>131</v>
+      </c>
+      <c r="I41">
+        <v>2500</v>
+      </c>
+      <c r="J41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" t="s">
+        <v>156</v>
+      </c>
+      <c r="G42" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" t="s">
+        <v>131</v>
+      </c>
+      <c r="I42">
+        <v>2000</v>
+      </c>
+      <c r="J42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43">
+        <v>500</v>
+      </c>
+      <c r="J43" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" t="s">
+        <v>146</v>
+      </c>
+      <c r="G44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44">
+        <v>500</v>
+      </c>
+      <c r="J44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" t="s">
+        <v>131</v>
+      </c>
+      <c r="I45">
+        <v>2000</v>
+      </c>
+      <c r="J45" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>168</v>
+      </c>
+      <c r="F46" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" t="s">
+        <v>130</v>
+      </c>
+      <c r="H46" t="s">
+        <v>131</v>
+      </c>
+      <c r="I46">
+        <v>1000</v>
+      </c>
+      <c r="J46" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" t="s">
+        <v>170</v>
+      </c>
+      <c r="C47" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" t="s">
+        <v>130</v>
+      </c>
+      <c r="H47" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47">
+        <v>4000</v>
+      </c>
+      <c r="J47" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" t="s">
+        <v>173</v>
+      </c>
+      <c r="C48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" t="s">
+        <v>130</v>
+      </c>
+      <c r="H48" t="s">
+        <v>131</v>
+      </c>
+      <c r="I48">
+        <v>600</v>
+      </c>
+      <c r="J48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" t="s">
+        <v>178</v>
+      </c>
+      <c r="G49" t="s">
+        <v>130</v>
+      </c>
+      <c r="H49" t="s">
+        <v>131</v>
+      </c>
+      <c r="I49">
+        <v>800</v>
+      </c>
+      <c r="J49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s">
+        <v>180</v>
+      </c>
+      <c r="C50" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>181</v>
+      </c>
+      <c r="F50" t="s">
+        <v>182</v>
+      </c>
+      <c r="G50" t="s">
+        <v>130</v>
+      </c>
+      <c r="H50" t="s">
+        <v>131</v>
+      </c>
+      <c r="I50">
+        <v>400</v>
+      </c>
+      <c r="J50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" t="s">
+        <v>185</v>
+      </c>
+      <c r="G51" t="s">
+        <v>130</v>
+      </c>
+      <c r="H51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I51">
+        <v>1200</v>
+      </c>
+      <c r="J51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>187</v>
+      </c>
+      <c r="F52" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" t="s">
+        <v>130</v>
+      </c>
+      <c r="H52" t="s">
+        <v>131</v>
+      </c>
+      <c r="I52">
+        <v>1200</v>
+      </c>
+      <c r="J52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" t="s">
+        <v>193</v>
+      </c>
+      <c r="G53" t="s">
+        <v>194</v>
+      </c>
+      <c r="H53" t="s">
+        <v>53</v>
+      </c>
+      <c r="I53">
+        <v>1280</v>
+      </c>
+      <c r="J53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" t="s">
+        <v>197</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" t="s">
+        <v>200</v>
+      </c>
+      <c r="H54" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54">
+        <v>12000</v>
+      </c>
+      <c r="J54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>203</v>
+      </c>
+      <c r="F55" t="s">
+        <v>204</v>
+      </c>
+      <c r="G55" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" t="s">
+        <v>201</v>
+      </c>
+      <c r="I55">
+        <v>12000</v>
+      </c>
+      <c r="J55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56">
+        <v>60</v>
+      </c>
+      <c r="E56" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" t="s">
+        <v>207</v>
+      </c>
+      <c r="G56" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" t="s">
+        <v>53</v>
+      </c>
+      <c r="I56">
+        <v>3300</v>
+      </c>
+      <c r="J56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57">
+        <v>30</v>
+      </c>
+      <c r="E57" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" t="s">
+        <v>211</v>
+      </c>
+      <c r="G57" t="s">
+        <v>58</v>
+      </c>
+      <c r="H57" t="s">
+        <v>53</v>
+      </c>
+      <c r="I57">
+        <v>5700</v>
+      </c>
+      <c r="J57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" t="s">
+        <v>214</v>
+      </c>
+      <c r="G58" t="s">
+        <v>124</v>
+      </c>
+      <c r="H58" t="s">
+        <v>53</v>
+      </c>
+      <c r="I58">
+        <v>2910</v>
+      </c>
+      <c r="J58" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>217</v>
+      </c>
+      <c r="F59" t="s">
+        <v>218</v>
+      </c>
+      <c r="G59" t="s">
+        <v>124</v>
+      </c>
+      <c r="H59" t="s">
+        <v>53</v>
+      </c>
+      <c r="I59">
+        <v>1620</v>
+      </c>
+      <c r="J59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>220</v>
+      </c>
+      <c r="F60" t="s">
+        <v>218</v>
+      </c>
+      <c r="G60" t="s">
+        <v>124</v>
+      </c>
+      <c r="H60" t="s">
+        <v>53</v>
+      </c>
+      <c r="I60">
+        <v>1620</v>
+      </c>
+      <c r="J60" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" t="s">
+        <v>218</v>
+      </c>
+      <c r="G61" t="s">
+        <v>124</v>
+      </c>
+      <c r="H61" t="s">
+        <v>53</v>
+      </c>
+      <c r="I61">
+        <v>1500</v>
+      </c>
+      <c r="J61" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
+        <v>216</v>
+      </c>
+      <c r="C62" t="s">
+        <v>49</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>224</v>
+      </c>
+      <c r="F62" t="s">
+        <v>218</v>
+      </c>
+      <c r="G62" t="s">
+        <v>124</v>
+      </c>
+      <c r="H62" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62">
+        <v>1500</v>
+      </c>
+      <c r="J62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" t="s">
+        <v>49</v>
+      </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+      <c r="E63" t="s">
+        <v>226</v>
+      </c>
+      <c r="F63" t="s">
+        <v>227</v>
+      </c>
+      <c r="G63" t="s">
+        <v>194</v>
+      </c>
+      <c r="H63" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63">
+        <v>600</v>
+      </c>
+      <c r="J63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>229</v>
+      </c>
+      <c r="F64" t="s">
+        <v>218</v>
+      </c>
+      <c r="G64" t="s">
+        <v>124</v>
+      </c>
+      <c r="H64" t="s">
+        <v>53</v>
+      </c>
+      <c r="I64">
+        <v>1620</v>
+      </c>
+      <c r="J64" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" t="s">
+        <v>49</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" t="s">
+        <v>218</v>
+      </c>
+      <c r="G65" t="s">
+        <v>124</v>
+      </c>
+      <c r="H65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I65">
+        <v>1620</v>
+      </c>
+      <c r="J65" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>233</v>
+      </c>
+      <c r="F66" t="s">
+        <v>218</v>
+      </c>
+      <c r="G66" t="s">
+        <v>124</v>
+      </c>
+      <c r="H66" t="s">
+        <v>53</v>
+      </c>
+      <c r="I66">
+        <v>1230</v>
+      </c>
+      <c r="J66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" t="s">
+        <v>236</v>
+      </c>
+      <c r="G67" t="s">
+        <v>194</v>
+      </c>
+      <c r="H67" t="s">
+        <v>53</v>
+      </c>
+      <c r="I67">
+        <v>10000</v>
+      </c>
+      <c r="J67" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>238</v>
+      </c>
+      <c r="F68" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H68" t="s">
+        <v>53</v>
+      </c>
+      <c r="I68">
+        <v>6600</v>
+      </c>
+      <c r="J68" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>241</v>
+      </c>
+      <c r="F69" t="s">
+        <v>239</v>
+      </c>
+      <c r="G69" t="s">
+        <v>124</v>
+      </c>
+      <c r="H69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I69">
+        <v>6600</v>
+      </c>
+      <c r="J69" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>243</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70" t="s">
+        <v>244</v>
+      </c>
+      <c r="F70" t="s">
+        <v>245</v>
+      </c>
+      <c r="G70" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" t="s">
+        <v>53</v>
+      </c>
+      <c r="I70">
+        <v>1300</v>
+      </c>
+      <c r="J70" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71" t="s">
+        <v>247</v>
+      </c>
+      <c r="F71" t="s">
+        <v>248</v>
+      </c>
+      <c r="G71" t="s">
+        <v>194</v>
+      </c>
+      <c r="H71" t="s">
+        <v>53</v>
+      </c>
+      <c r="I71">
+        <v>1100</v>
+      </c>
+      <c r="J71" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
+        <v>250</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>251</v>
+      </c>
+      <c r="F72" t="s">
+        <v>252</v>
+      </c>
+      <c r="G72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H72" t="s">
+        <v>53</v>
+      </c>
+      <c r="I72">
+        <v>3500</v>
+      </c>
+      <c r="J72" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" t="s">
+        <v>254</v>
+      </c>
+      <c r="C73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73" t="s">
+        <v>255</v>
+      </c>
+      <c r="F73" t="s">
+        <v>256</v>
+      </c>
+      <c r="G73" t="s">
+        <v>124</v>
+      </c>
+      <c r="H73" t="s">
+        <v>53</v>
+      </c>
+      <c r="I73">
+        <v>3200</v>
+      </c>
+      <c r="J73" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>189</v>
+      </c>
+      <c r="B74" t="s">
+        <v>254</v>
+      </c>
+      <c r="C74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74">
+        <v>10</v>
+      </c>
+      <c r="E74" t="s">
+        <v>258</v>
+      </c>
+      <c r="F74" t="s">
+        <v>256</v>
+      </c>
+      <c r="G74" t="s">
+        <v>124</v>
+      </c>
+      <c r="H74" t="s">
+        <v>53</v>
+      </c>
+      <c r="I74">
+        <v>3600</v>
+      </c>
+      <c r="J74" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" t="s">
+        <v>254</v>
+      </c>
+      <c r="C75" t="s">
+        <v>49</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75" t="s">
+        <v>260</v>
+      </c>
+      <c r="F75" t="s">
+        <v>256</v>
+      </c>
+      <c r="G75" t="s">
+        <v>124</v>
+      </c>
+      <c r="H75" t="s">
+        <v>53</v>
+      </c>
+      <c r="I75">
+        <v>3600</v>
+      </c>
+      <c r="J75" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" t="s">
+        <v>254</v>
+      </c>
+      <c r="C76" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+      <c r="E76" t="s">
+        <v>262</v>
+      </c>
+      <c r="F76" t="s">
+        <v>256</v>
+      </c>
+      <c r="G76" t="s">
+        <v>124</v>
+      </c>
+      <c r="H76" t="s">
+        <v>53</v>
+      </c>
+      <c r="I76">
+        <v>3600</v>
+      </c>
+      <c r="J76" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" t="s">
+        <v>254</v>
+      </c>
+      <c r="C77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+      <c r="E77" t="s">
+        <v>264</v>
+      </c>
+      <c r="F77" t="s">
+        <v>256</v>
+      </c>
+      <c r="G77" t="s">
+        <v>124</v>
+      </c>
+      <c r="H77" t="s">
+        <v>53</v>
+      </c>
+      <c r="I77">
+        <v>3600</v>
+      </c>
+      <c r="J77" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>189</v>
+      </c>
+      <c r="B78" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" t="s">
+        <v>49</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>266</v>
+      </c>
+      <c r="F78" t="s">
+        <v>267</v>
+      </c>
+      <c r="G78" t="s">
+        <v>194</v>
+      </c>
+      <c r="H78" t="s">
+        <v>53</v>
+      </c>
+      <c r="I78">
+        <v>3200</v>
+      </c>
+      <c r="J78" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>189</v>
+      </c>
+      <c r="B79" t="s">
+        <v>254</v>
+      </c>
+      <c r="C79" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79">
+        <v>10</v>
+      </c>
+      <c r="E79" t="s">
+        <v>269</v>
+      </c>
+      <c r="F79" t="s">
+        <v>256</v>
+      </c>
+      <c r="G79" t="s">
+        <v>124</v>
+      </c>
+      <c r="H79" t="s">
+        <v>53</v>
+      </c>
+      <c r="I79">
+        <v>3200</v>
+      </c>
+      <c r="J79" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B80" t="s">
+        <v>271</v>
+      </c>
+      <c r="C80" t="s">
+        <v>49</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>272</v>
+      </c>
+      <c r="F80" t="s">
+        <v>273</v>
+      </c>
+      <c r="G80" t="s">
+        <v>274</v>
+      </c>
+      <c r="H80" t="s">
+        <v>53</v>
+      </c>
+      <c r="I80">
+        <v>700</v>
+      </c>
+      <c r="J80" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" t="s">
+        <v>276</v>
+      </c>
+      <c r="C81" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81" t="s">
+        <v>277</v>
+      </c>
+      <c r="F81" t="s">
+        <v>278</v>
+      </c>
+      <c r="G81" t="s">
+        <v>194</v>
+      </c>
+      <c r="H81" t="s">
+        <v>53</v>
+      </c>
+      <c r="I81">
+        <v>4400</v>
+      </c>
+      <c r="J81" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>189</v>
+      </c>
+      <c r="B82" t="s">
+        <v>276</v>
+      </c>
+      <c r="C82" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82" t="s">
+        <v>280</v>
+      </c>
+      <c r="F82" t="s">
+        <v>281</v>
+      </c>
+      <c r="G82" t="s">
+        <v>194</v>
+      </c>
+      <c r="H82" t="s">
+        <v>53</v>
+      </c>
+      <c r="I82">
+        <v>4400</v>
+      </c>
+      <c r="J82" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>189</v>
+      </c>
+      <c r="B83" t="s">
+        <v>276</v>
+      </c>
+      <c r="C83" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>283</v>
+      </c>
+      <c r="F83" t="s">
+        <v>284</v>
+      </c>
+      <c r="G83" t="s">
+        <v>194</v>
+      </c>
+      <c r="H83" t="s">
+        <v>53</v>
+      </c>
+      <c r="I83">
+        <v>9680</v>
+      </c>
+      <c r="J83" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" t="s">
+        <v>276</v>
+      </c>
+      <c r="C84" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84" t="s">
+        <v>286</v>
+      </c>
+      <c r="F84" t="s">
+        <v>287</v>
+      </c>
+      <c r="G84" t="s">
+        <v>194</v>
+      </c>
+      <c r="H84" t="s">
+        <v>53</v>
+      </c>
+      <c r="I84">
+        <v>4410</v>
+      </c>
+      <c r="J84" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>289</v>
+      </c>
+      <c r="F85" t="s">
+        <v>290</v>
+      </c>
+      <c r="G85" t="s">
+        <v>124</v>
+      </c>
+      <c r="H85" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85">
+        <v>660</v>
+      </c>
+      <c r="J85" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>292</v>
+      </c>
+      <c r="B86" t="s">
+        <v>293</v>
+      </c>
+      <c r="C86" t="s">
+        <v>191</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>294</v>
+      </c>
+      <c r="F86" t="s">
+        <v>295</v>
+      </c>
+      <c r="G86" t="s">
+        <v>296</v>
+      </c>
+      <c r="H86" t="s">
+        <v>201</v>
+      </c>
+      <c r="I86">
+        <v>400</v>
+      </c>
+      <c r="J86" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>298</v>
+      </c>
+      <c r="B87" t="s">
+        <v>299</v>
+      </c>
+      <c r="C87" t="s">
+        <v>300</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87" t="s">
+        <v>301</v>
+      </c>
+      <c r="F87" t="s">
+        <v>302</v>
+      </c>
+      <c r="G87" t="s">
+        <v>303</v>
+      </c>
+      <c r="H87" t="s">
+        <v>201</v>
+      </c>
+      <c r="I87">
+        <v>1000</v>
+      </c>
+      <c r="J87" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>298</v>
+      </c>
+      <c r="B88" t="s">
+        <v>299</v>
+      </c>
+      <c r="C88" t="s">
+        <v>300</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>305</v>
+      </c>
+      <c r="F88" t="s">
+        <v>306</v>
+      </c>
+      <c r="G88" t="s">
+        <v>307</v>
+      </c>
+      <c r="H88" t="s">
+        <v>308</v>
+      </c>
+      <c r="I88">
+        <v>500</v>
+      </c>
+      <c r="J88" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B89" t="s">
+        <v>310</v>
+      </c>
+      <c r="C89" t="s">
+        <v>197</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89" t="s">
+        <v>311</v>
+      </c>
+      <c r="F89" t="s">
+        <v>312</v>
+      </c>
+      <c r="G89" t="s">
+        <v>313</v>
+      </c>
+      <c r="H89" t="s">
+        <v>201</v>
+      </c>
+      <c r="I89">
+        <v>1000</v>
+      </c>
+      <c r="J89" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>315</v>
+      </c>
+      <c r="C90" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90">
+        <v>30</v>
+      </c>
+      <c r="E90" t="s">
+        <v>316</v>
+      </c>
+      <c r="F90" t="s">
+        <v>317</v>
+      </c>
+      <c r="G90" t="s">
+        <v>318</v>
+      </c>
+      <c r="H90" t="s">
+        <v>319</v>
+      </c>
+      <c r="I90">
+        <v>1800</v>
+      </c>
+      <c r="J90" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" t="s">
+        <v>300</v>
+      </c>
+      <c r="D91">
+        <v>4</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" t="s">
+        <v>321</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91">
+        <v>300</v>
+      </c>
+      <c r="J91" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>315</v>
+      </c>
+      <c r="C92" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92">
+        <v>96</v>
+      </c>
+      <c r="E92" t="s">
+        <v>316</v>
+      </c>
+      <c r="F92" t="s">
+        <v>323</v>
+      </c>
+      <c r="G92" t="s">
+        <v>318</v>
+      </c>
+      <c r="H92" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92">
+        <v>6000</v>
+      </c>
+      <c r="J92" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>315</v>
+      </c>
+      <c r="C93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D93">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>316</v>
+      </c>
+      <c r="F93" t="s">
+        <v>325</v>
+      </c>
+      <c r="G93" t="s">
+        <v>318</v>
+      </c>
+      <c r="H93" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93">
+        <v>1000</v>
+      </c>
+      <c r="J93" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>316</v>
+      </c>
+      <c r="F94" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94">
+        <v>500</v>
+      </c>
+      <c r="J94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" t="s">
+        <v>327</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95">
+        <v>1000</v>
+      </c>
+      <c r="J95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" t="s">
+        <v>300</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" t="s">
+        <v>29</v>
+      </c>
+      <c r="H96" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96">
+        <v>800</v>
+      </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>328</v>
+      </c>
+      <c r="C97" t="s">
+        <v>49</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>329</v>
+      </c>
+      <c r="F97" t="s">
+        <v>330</v>
+      </c>
+      <c r="G97" t="s">
+        <v>58</v>
+      </c>
+      <c r="H97" t="s">
+        <v>53</v>
+      </c>
+      <c r="I97">
+        <v>1000</v>
+      </c>
+      <c r="J97" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>144</v>
+      </c>
+      <c r="C98" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>332</v>
+      </c>
+      <c r="F98" t="s">
+        <v>333</v>
+      </c>
+      <c r="G98" t="s">
+        <v>124</v>
+      </c>
+      <c r="H98" t="s">
+        <v>53</v>
+      </c>
+      <c r="I98">
+        <v>1000</v>
+      </c>
+      <c r="J98" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" t="s">
+        <v>327</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99">
+        <v>1000</v>
+      </c>
+      <c r="J99" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
+        <v>133</v>
+      </c>
+      <c r="C100" t="s">
+        <v>49</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>283</v>
+      </c>
+      <c r="F100" t="s">
+        <v>335</v>
+      </c>
+      <c r="G100" t="s">
+        <v>336</v>
+      </c>
+      <c r="H100" t="s">
+        <v>201</v>
+      </c>
+      <c r="I100">
+        <v>8000</v>
+      </c>
+      <c r="J100" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" t="s">
+        <v>300</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101" t="s">
+        <v>34</v>
+      </c>
+      <c r="F101" t="s">
+        <v>35</v>
+      </c>
+      <c r="G101" t="s">
+        <v>36</v>
+      </c>
+      <c r="H101" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101">
+        <v>500</v>
+      </c>
+      <c r="J101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" t="s">
+        <v>338</v>
+      </c>
+      <c r="C102" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102" t="s">
+        <v>339</v>
+      </c>
+      <c r="F102" t="s">
+        <v>340</v>
+      </c>
+      <c r="G102" t="s">
+        <v>341</v>
+      </c>
+      <c r="H102" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102">
+        <v>400</v>
+      </c>
+      <c r="J102" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" t="s">
+        <v>327</v>
+      </c>
+      <c r="D103">
+        <v>6</v>
+      </c>
+      <c r="E103" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" t="s">
+        <v>39</v>
+      </c>
+      <c r="G103" t="s">
         <v>40</v>
       </c>
-      <c r="C16">
+      <c r="H103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103">
+        <v>1000</v>
+      </c>
+      <c r="J103" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" t="s">
+        <v>327</v>
+      </c>
+      <c r="D104">
         <v>6</v>
       </c>
-      <c r="D16">
+      <c r="E104" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" t="s">
+        <v>40</v>
+      </c>
+      <c r="H104" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104">
+        <v>1000</v>
+      </c>
+      <c r="J104" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>12</v>
       </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16">
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>327</v>
+      </c>
+      <c r="D105">
+        <v>12</v>
+      </c>
+      <c r="E105" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" t="s">
+        <v>45</v>
+      </c>
+      <c r="G105" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105">
         <v>500</v>
       </c>
-      <c r="J16" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="J105" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>12</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B106" t="s">
+        <v>343</v>
+      </c>
+      <c r="C106" t="s">
+        <v>49</v>
+      </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
+      <c r="E106" t="s">
+        <v>344</v>
+      </c>
+      <c r="F106" t="s">
+        <v>345</v>
+      </c>
+      <c r="G106" t="s">
+        <v>346</v>
+      </c>
+      <c r="H106" t="s">
+        <v>347</v>
+      </c>
+      <c r="I106">
+        <v>1200</v>
+      </c>
+      <c r="J106" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" t="s">
+        <v>197</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>349</v>
+      </c>
+      <c r="F107" t="s">
+        <v>350</v>
+      </c>
+      <c r="G107" t="s">
+        <v>351</v>
+      </c>
+      <c r="H107" t="s">
+        <v>352</v>
+      </c>
+      <c r="I107">
+        <v>4000</v>
+      </c>
+      <c r="J107" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" t="s">
+        <v>158</v>
+      </c>
+      <c r="C108" t="s">
+        <v>49</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" t="s">
+        <v>354</v>
+      </c>
+      <c r="F108" t="s">
+        <v>355</v>
+      </c>
+      <c r="G108" t="s">
+        <v>194</v>
+      </c>
+      <c r="H108" t="s">
+        <v>53</v>
+      </c>
+      <c r="I108">
+        <v>5000</v>
+      </c>
+      <c r="J108" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
+        <v>357</v>
+      </c>
+      <c r="C109" t="s">
+        <v>197</v>
+      </c>
+      <c r="D109">
         <v>40</v>
       </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
-      <c r="D17">
+      <c r="E109" t="s">
+        <v>358</v>
+      </c>
+      <c r="F109" t="s">
+        <v>359</v>
+      </c>
+      <c r="G109" t="s">
+        <v>360</v>
+      </c>
+      <c r="H109" t="s">
+        <v>201</v>
+      </c>
+      <c r="I109">
+        <v>35000</v>
+      </c>
+      <c r="J109" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" t="s">
+        <v>327</v>
+      </c>
+      <c r="D110">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="E110" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" t="s">
+        <v>362</v>
+      </c>
+      <c r="G110" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" t="s">
         <v>17</v>
       </c>
-      <c r="I17">
-        <v>500</v>
-      </c>
-      <c r="J17" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" t="s">
-        <v>70</v>
-      </c>
-      <c r="L17" t="s">
-        <v>70</v>
+      <c r="I110">
+        <v>3000</v>
+      </c>
+      <c r="J110" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="s">
+        <v>327</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+      <c r="E111" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" t="s">
+        <v>364</v>
+      </c>
+      <c r="G111" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>800</v>
+      </c>
+      <c r="J111" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5E1CD-BC67-4E1F-8C2E-CB79D3D3160D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Objeto de Liquidação</t>
+  </si>
+  <si>
+    <t>Esquema de Alocação</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Part Number</t>
+  </si>
+  <si>
+    <t>Denominação</t>
+  </si>
+  <si>
+    <t>Entregar para</t>
+  </si>
+  <si>
+    <t>Departamento Emissor</t>
+  </si>
+  <si>
+    <t>Custo estimado</t>
+  </si>
+  <si>
+    <t>Elemento PEP</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Rodrigo Melo</t>
+  </si>
+  <si>
+    <t>4716404802-0002</t>
+  </si>
+  <si>
+    <t>LX - Conserto</t>
+  </si>
+  <si>
+    <t>QMM</t>
+  </si>
+  <si>
+    <t>PS/QMM7-CtP</t>
+  </si>
+  <si>
+    <t>LP-059795</t>
+  </si>
+  <si>
+    <t>Liberado</t>
+  </si>
+  <si>
+    <t>4716405323-0001</t>
+  </si>
+  <si>
+    <t>LP-059796</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>4738360386-0001</t>
+  </si>
+  <si>
+    <t>Ogiva - conserto</t>
+  </si>
+  <si>
+    <t>LP-059797</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,216 +430,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Responsável</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Objeto de Liquidação</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Esquema de Alocação</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Quantidade</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Denominação</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Entregar para</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Departamento Emissor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Custo estimado</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Elemento PEP</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rodrigo Melo</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
         <v>685421</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4716404802-0002</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>LX - Conserto</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>QMM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PS/QMM7-CtP</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
         <v>2000</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>LP-059795</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Liberado</t>
-        </is>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rodrigo Melo</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
         <v>685434</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4716405323-0001</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>LX - Conserto</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>QMM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PS/QMM7-CtP</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3">
         <v>500</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>LP-059796</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Encerrado</t>
-        </is>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rodrigo Melo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
         <v>685433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4738360386-0001</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ogiva - conserto</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>QMM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PS/QMM7-CtP</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4">
         <v>2500</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>LP-059797</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Encerrado</t>
-        </is>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5E1CD-BC67-4E1F-8C2E-CB79D3D3160D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7700A3-6B0F-40A8-B648-599348A93644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Responsável</t>
   </si>
@@ -55,43 +55,46 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Rodrigo Melo</t>
-  </si>
-  <si>
-    <t>4716404802-0002</t>
-  </si>
-  <si>
-    <t>LX - Conserto</t>
-  </si>
-  <si>
-    <t>QMM</t>
-  </si>
-  <si>
-    <t>PS/QMM7-CtP</t>
-  </si>
-  <si>
-    <t>LP-059795</t>
-  </si>
-  <si>
-    <t>Liberado</t>
-  </si>
-  <si>
-    <t>4716405323-0001</t>
-  </si>
-  <si>
-    <t>LP-059796</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>4738360386-0001</t>
-  </si>
-  <si>
-    <t>Ogiva - conserto</t>
-  </si>
-  <si>
-    <t>LP-059797</t>
+    <t>Marcelo Simoes</t>
+  </si>
+  <si>
+    <t>4711401378_P002</t>
+  </si>
+  <si>
+    <t>Posição dois do conjunto de garra</t>
+  </si>
+  <si>
+    <t>SNA2CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS23-BR</t>
+  </si>
+  <si>
+    <t>LP-059829</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>Conjunto de garra (par)</t>
+  </si>
+  <si>
+    <t>LP-059830</t>
+  </si>
+  <si>
+    <t>LP-056842</t>
+  </si>
+  <si>
+    <t>Caçapa HE - Bico LE</t>
+  </si>
+  <si>
+    <t>QUJ1CT</t>
+  </si>
+  <si>
+    <t>SO/OPM-TS21-BR</t>
+  </si>
+  <si>
+    <t>LP-059827</t>
   </si>
 </sst>
 </file>
@@ -434,17 +437,17 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -487,10 +490,10 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>685421</v>
+        <v>685609</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -508,33 +511,30 @@
         <v>15</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>685434</v>
+        <v>685609</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>4711401378</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -543,48 +543,39 @@
         <v>15</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>2890</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
-        <v>685433</v>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I4">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/LP-Register.xlsx
+++ b/98 - Excels/LP-Register.xlsx
@@ -1,124 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7700A3-6B0F-40A8-B648-599348A93644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Objeto de Liquidação</t>
-  </si>
-  <si>
-    <t>Esquema de Alocação</t>
-  </si>
-  <si>
-    <t>Quantidade</t>
-  </si>
-  <si>
-    <t>Part Number</t>
-  </si>
-  <si>
-    <t>Denominação</t>
-  </si>
-  <si>
-    <t>Entregar para</t>
-  </si>
-  <si>
-    <t>Departamento Emissor</t>
-  </si>
-  <si>
-    <t>Custo estimado</t>
-  </si>
-  <si>
-    <t>Elemento PEP</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Marcelo Simoes</t>
-  </si>
-  <si>
-    <t>4711401378_P002</t>
-  </si>
-  <si>
-    <t>Posição dois do conjunto de garra</t>
-  </si>
-  <si>
-    <t>SNA2CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS23-BR</t>
-  </si>
-  <si>
-    <t>LP-059829</t>
-  </si>
-  <si>
-    <t>Yesica Gonzalez</t>
-  </si>
-  <si>
-    <t>Conjunto de garra (par)</t>
-  </si>
-  <si>
-    <t>LP-059830</t>
-  </si>
-  <si>
-    <t>LP-056842</t>
-  </si>
-  <si>
-    <t>Caçapa HE - Bico LE</t>
-  </si>
-  <si>
-    <t>QUJ1CT</t>
-  </si>
-  <si>
-    <t>SO/OPM-TS21-BR</t>
-  </si>
-  <si>
-    <t>LP-059827</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -126,26 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -433,149 +420,212 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Objeto de Liquidação</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Esquema de Alocação</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Denominação</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Entregar para</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Departamento Emissor</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Custo estimado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento PEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marcelo Simoes</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>685609</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4711401378_P002</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Posição dois do conjunto de garra</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SNA2CT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SO/OPM-TS23-BR</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>LP-059829</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Yesica Gonzalez</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>685609</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4711401378</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Conjunto de garra (par)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SNA2CT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SO/OPM-TS23-BR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2890</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>LP-059830</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Marcelo Simoes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LP-056842</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>685609</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>1600</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>685609</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4711401378</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3">
-        <v>2890</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Caçapa HE - Bico LE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>QUJ1CT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SO/OPM-TS21-BR</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>500</v>
       </c>
-      <c r="J4" t="s">
-        <v>24</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LP-059827</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
       </c>
     </row>
   </sheetData>
